--- a/Luban/Config/Datas/#HeartMethodConfig.xlsx
+++ b/Luban/Config/Datas/#HeartMethodConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{616DA494-DC84-4F2B-9B51-53FCAB7DC4DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C968F09-D9D3-4607-BB21-684E8462600E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
+    <workbookView xWindow="1395" yWindow="1650" windowWidth="28800" windowHeight="15345" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="35">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -87,26 +87,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>CalculateActionWheelMoment</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>StartActionWheelMoment</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AsTargetActionMoment</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>BeforeClashMoment</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>UnderHitMoment</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>AfterClashMoment</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -131,18 +115,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>计算息的时候调用</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>息开始扳机</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>被作为目标时扳机</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>释放成功后扳机</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -151,10 +123,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>命中后扳机</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>交锋后扳机</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -168,6 +136,34 @@
   </si>
   <si>
     <t>ReleaseSkillActionMoment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(list#sep=,),int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BeforeActionMoment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BeforeUnderActionMoment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AfterUnderActionMoment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>行动前</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>受到行动前调用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>受到行动后调用扳机</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -532,21 +528,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
-  <dimension ref="A1:P5"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="5" max="8" width="41.25" customWidth="1"/>
-    <col min="9" max="9" width="24.125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22.375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="22.25" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.75" customWidth="1"/>
-    <col min="13" max="13" width="16.375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="18.625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="17.75" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="41.25" customWidth="1"/>
+    <col min="8" max="8" width="24.125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.75" customWidth="1"/>
+    <col min="11" max="11" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.25" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="27.5" customWidth="1"/>
+    <col min="14" max="14" width="18.625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -560,43 +556,40 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1" t="s">
         <v>12</v>
       </c>
-      <c r="F1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G1" t="s">
-        <v>14</v>
-      </c>
       <c r="H1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1" t="s">
         <v>15</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>16</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" t="s">
+        <v>31</v>
+      </c>
+      <c r="N1" t="s">
         <v>17</v>
       </c>
-      <c r="K1" t="s">
-        <v>35</v>
-      </c>
-      <c r="L1" t="s">
+      <c r="O1" t="s">
         <v>18</v>
       </c>
-      <c r="M1" t="s">
-        <v>19</v>
-      </c>
-      <c r="N1" t="s">
-        <v>20</v>
-      </c>
-      <c r="O1" t="s">
-        <v>21</v>
-      </c>
-      <c r="P1" t="s">
-        <v>22</v>
-      </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -610,43 +603,40 @@
         <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="F2" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="G2" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="H2" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="I2" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="J2" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="K2" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="L2" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="M2" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="N2" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="O2" t="s">
-        <v>5</v>
-      </c>
-      <c r="P2" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -660,43 +650,40 @@
         <v>9</v>
       </c>
       <c r="E3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J3" t="s">
         <v>23</v>
       </c>
-      <c r="F3" t="s">
+      <c r="K3" t="s">
         <v>24</v>
       </c>
-      <c r="G3" t="s">
+      <c r="L3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3" t="s">
+        <v>34</v>
+      </c>
+      <c r="N3" t="s">
         <v>25</v>
       </c>
-      <c r="H3" t="s">
+      <c r="O3" t="s">
         <v>26</v>
       </c>
-      <c r="I3" t="s">
-        <v>27</v>
-      </c>
-      <c r="J3" t="s">
-        <v>28</v>
-      </c>
-      <c r="K3" t="s">
-        <v>29</v>
-      </c>
-      <c r="L3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N3" t="s">
-        <v>32</v>
-      </c>
-      <c r="O3" t="s">
-        <v>33</v>
-      </c>
-      <c r="P3" t="s">
-        <v>34</v>
-      </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B4">
         <v>1</v>
       </c>
@@ -739,11 +726,8 @@
       <c r="O4">
         <v>1</v>
       </c>
-      <c r="P4">
-        <v>1</v>
-      </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B5">
         <v>2</v>
       </c>
@@ -784,9 +768,6 @@
         <v>1</v>
       </c>
       <c r="O5">
-        <v>1</v>
-      </c>
-      <c r="P5">
         <v>1</v>
       </c>
     </row>

--- a/Luban/Config/Datas/#HeartMethodConfig.xlsx
+++ b/Luban/Config/Datas/#HeartMethodConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C968F09-D9D3-4607-BB21-684E8462600E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03A1C1FE-FCED-49CE-94FC-E756A9AD4F0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1395" yWindow="1650" windowWidth="28800" windowHeight="15345" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
+    <workbookView xWindow="4995" yWindow="4455" windowWidth="28800" windowHeight="15345" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -171,7 +171,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -186,6 +186,13 @@
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -210,9 +217,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -529,245 +539,247 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
   <dimension ref="A1:O5"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="5" max="7" width="41.25" customWidth="1"/>
-    <col min="8" max="8" width="24.125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="22.375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.75" customWidth="1"/>
-    <col min="11" max="11" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="22.25" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="27.5" customWidth="1"/>
-    <col min="14" max="14" width="18.625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17.75" bestFit="1" customWidth="1"/>
+    <col min="1" max="4" width="9" style="1"/>
+    <col min="5" max="7" width="41.25" style="1" customWidth="1"/>
+    <col min="8" max="8" width="24.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.75" style="1" customWidth="1"/>
+    <col min="11" max="11" width="17.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="27.5" style="1" customWidth="1"/>
+    <col min="14" max="14" width="18.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H2" t="s">
-        <v>28</v>
-      </c>
-      <c r="I2" t="s">
-        <v>28</v>
-      </c>
-      <c r="J2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K2" t="s">
-        <v>28</v>
-      </c>
-      <c r="L2" t="s">
-        <v>28</v>
-      </c>
-      <c r="M2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O2" t="s">
+      <c r="E2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O2" s="1" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+      <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="B3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="K3" t="s">
+      <c r="K3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="L3" t="s">
+      <c r="L3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="M3" t="s">
+      <c r="M3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="N3" t="s">
+      <c r="N3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="O3" t="s">
+      <c r="O3" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="B4" s="1">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-      <c r="N4">
-        <v>1</v>
-      </c>
-      <c r="O4">
+      <c r="E4" s="1">
+        <v>1</v>
+      </c>
+      <c r="F4" s="1">
+        <v>1</v>
+      </c>
+      <c r="G4" s="1">
+        <v>1</v>
+      </c>
+      <c r="H4" s="1">
+        <v>1</v>
+      </c>
+      <c r="I4" s="1">
+        <v>1</v>
+      </c>
+      <c r="J4" s="1">
+        <v>1</v>
+      </c>
+      <c r="K4" s="1">
+        <v>1</v>
+      </c>
+      <c r="L4" s="1">
+        <v>1</v>
+      </c>
+      <c r="M4" s="1">
+        <v>1</v>
+      </c>
+      <c r="N4" s="1">
+        <v>1</v>
+      </c>
+      <c r="O4" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="B5">
+      <c r="B5" s="1">
         <v>2</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-      <c r="N5">
-        <v>1</v>
-      </c>
-      <c r="O5">
+      <c r="E5" s="1">
+        <v>1</v>
+      </c>
+      <c r="F5" s="1">
+        <v>1</v>
+      </c>
+      <c r="G5" s="1">
+        <v>1</v>
+      </c>
+      <c r="H5" s="1">
+        <v>1</v>
+      </c>
+      <c r="I5" s="1">
+        <v>1</v>
+      </c>
+      <c r="J5" s="1">
+        <v>1</v>
+      </c>
+      <c r="K5" s="1">
+        <v>1</v>
+      </c>
+      <c r="L5" s="1">
+        <v>1</v>
+      </c>
+      <c r="M5" s="1">
+        <v>1</v>
+      </c>
+      <c r="N5" s="1">
+        <v>1</v>
+      </c>
+      <c r="O5" s="1">
         <v>1</v>
       </c>
     </row>

--- a/Luban/Config/Datas/#HeartMethodConfig.xlsx
+++ b/Luban/Config/Datas/#HeartMethodConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03A1C1FE-FCED-49CE-94FC-E756A9AD4F0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EE3E780-D0E5-47DA-B1D9-4B866E10E66B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4995" yWindow="4455" windowWidth="28800" windowHeight="15345" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="39">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -164,6 +164,22 @@
   </si>
   <si>
     <t>受到行动后调用扳机</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>息开始的扳机</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ActionWheelStartMoment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CalculateActionWheelMoment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>计算息的时候扳机调用</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -171,7 +187,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -193,6 +209,12 @@
       <name val="微软雅黑"/>
       <family val="2"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -217,11 +239,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -538,23 +563,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:Q5"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
-    <col min="5" max="7" width="41.25" style="1" customWidth="1"/>
-    <col min="8" max="8" width="24.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="22.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.75" style="1" customWidth="1"/>
-    <col min="11" max="11" width="17.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="22.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="27.5" style="1" customWidth="1"/>
-    <col min="14" max="14" width="18.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9" style="1"/>
+    <col min="5" max="5" width="20.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="31.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="27.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="22.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="29.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="28" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="27.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="21.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="20" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -573,35 +602,41 @@
       <c r="F1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -620,7 +655,7 @@
       <c r="F2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="2" t="s">
         <v>28</v>
       </c>
       <c r="H2" s="1" t="s">
@@ -647,8 +682,14 @@
       <c r="O2" s="1" t="s">
         <v>28</v>
       </c>
+      <c r="P2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -667,35 +708,41 @@
       <c r="F3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="M3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="N3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="O3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="P3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="O3" s="1" t="s">
+      <c r="Q3" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B4" s="1">
         <v>1</v>
       </c>
@@ -705,41 +752,8 @@
       <c r="D4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="1">
-        <v>1</v>
-      </c>
-      <c r="F4" s="1">
-        <v>1</v>
-      </c>
-      <c r="G4" s="1">
-        <v>1</v>
-      </c>
-      <c r="H4" s="1">
-        <v>1</v>
-      </c>
-      <c r="I4" s="1">
-        <v>1</v>
-      </c>
-      <c r="J4" s="1">
-        <v>1</v>
-      </c>
-      <c r="K4" s="1">
-        <v>1</v>
-      </c>
-      <c r="L4" s="1">
-        <v>1</v>
-      </c>
-      <c r="M4" s="1">
-        <v>1</v>
-      </c>
-      <c r="N4" s="1">
-        <v>1</v>
-      </c>
-      <c r="O4" s="1">
-        <v>1</v>
-      </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B5" s="1">
         <v>2</v>
       </c>
@@ -748,39 +762,6 @@
       </c>
       <c r="D5" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="E5" s="1">
-        <v>1</v>
-      </c>
-      <c r="F5" s="1">
-        <v>1</v>
-      </c>
-      <c r="G5" s="1">
-        <v>1</v>
-      </c>
-      <c r="H5" s="1">
-        <v>1</v>
-      </c>
-      <c r="I5" s="1">
-        <v>1</v>
-      </c>
-      <c r="J5" s="1">
-        <v>1</v>
-      </c>
-      <c r="K5" s="1">
-        <v>1</v>
-      </c>
-      <c r="L5" s="1">
-        <v>1</v>
-      </c>
-      <c r="M5" s="1">
-        <v>1</v>
-      </c>
-      <c r="N5" s="1">
-        <v>1</v>
-      </c>
-      <c r="O5" s="1">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Luban/Config/Datas/#HeartMethodConfig.xlsx
+++ b/Luban/Config/Datas/#HeartMethodConfig.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EE3E780-D0E5-47DA-B1D9-4B866E10E66B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F65116F6-3BB8-4B49-90F9-DC6F2FC42500}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
@@ -20,12 +20,21 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="358">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -67,119 +76,1141 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>心法1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>心法2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DoDesitionMoment</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BattleStartMoment</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RoundStartMoment</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BeforeClashMoment</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AfterClashMoment</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AfterActionMoment</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RoundEndMoment</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>行动决定后扳机</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>战斗开始扳机</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>回合开始扳机</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>释放成功后扳机</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>交锋前扳机</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>交锋后扳机</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>行动后扳机</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>回合结束扳机</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ReleaseSkillActionMoment</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(list#sep=,),int</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BeforeActionMoment</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BeforeUnderActionMoment</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AfterUnderActionMoment</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>行动前</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>受到行动前调用</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>受到行动后调用扳机</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>息开始的扳机</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ActionWheelStartMoment</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CalculateActionWheelMoment</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>计算息的时候扳机调用</t>
+    <t>冯河</t>
+  </si>
+  <si>
+    <t>术杀式直接伤害额外增加10%</t>
+  </si>
+  <si>
+    <t>药理贯通</t>
+  </si>
+  <si>
+    <t>药力相关增益状态效果增强%负面状态效果减弱%</t>
+  </si>
+  <si>
+    <t>药炼体</t>
+  </si>
+  <si>
+    <t>损失体时获得损失体30%的护体</t>
+  </si>
+  <si>
+    <t>清梦醉眀</t>
+  </si>
+  <si>
+    <t>侵略如火</t>
+  </si>
+  <si>
+    <t>杀式包含2个↑键则加成提高5的百分比</t>
+  </si>
+  <si>
+    <t>其疾如风</t>
+  </si>
+  <si>
+    <t>招式包含2个→键则本次行动加快1息</t>
+  </si>
+  <si>
+    <t>交锋时招式至少与对手有两个等位键方向相反则获得一层交鸣</t>
+  </si>
+  <si>
+    <t>其徐如林</t>
+  </si>
+  <si>
+    <t>招式包含2个↓键</t>
+  </si>
+  <si>
+    <t>不动如山</t>
+  </si>
+  <si>
+    <t>招式包含2个←键</t>
+  </si>
+  <si>
+    <t>难知如阴</t>
+  </si>
+  <si>
+    <t>招式包含至少3个不同的键则行动无法被揭示</t>
+  </si>
+  <si>
+    <t>动如雷震</t>
+  </si>
+  <si>
+    <t>招式包含至少4个键直接伤害额外增加10%</t>
+  </si>
+  <si>
+    <t>业生心功</t>
+  </si>
+  <si>
+    <t>业生派系的招式刚炁消耗减少15%、玄炁消耗减少15%</t>
+  </si>
+  <si>
+    <t>百难呒苛</t>
+  </si>
+  <si>
+    <t>每回合开始获得一个负面，减少再次获得的负面带来的影响</t>
+  </si>
+  <si>
+    <t>猊煞变</t>
+  </si>
+  <si>
+    <t>每回合获得1层猊煞</t>
+  </si>
+  <si>
+    <t>↓键可以作为↑键</t>
+  </si>
+  <si>
+    <t>以攻为守</t>
+  </si>
+  <si>
+    <t>获得的←键全部变为→键，战斗中防的提升效果全部变为力的提升，破的提升变为技的提升</t>
+  </si>
+  <si>
+    <t>↑键可以作为↓键，巧+（10+0.33*GR）</t>
+  </si>
+  <si>
+    <t>猿臂之势</t>
+  </si>
+  <si>
+    <t>→键可以作为←键，←键可以作为→键</t>
+  </si>
+  <si>
+    <t>万象森罗</t>
+  </si>
+  <si>
+    <t>非派系的招式在本场战斗首次使用后获得一个随机的键</t>
+  </si>
+  <si>
+    <t>回合开始时若累计消耗至少10个键则清空累计获得1次行动次数</t>
+  </si>
+  <si>
+    <t>先发制人</t>
+  </si>
+  <si>
+    <t>预先行动阶段决定的行动至少会加快1息</t>
+  </si>
+  <si>
+    <t>强键</t>
+  </si>
+  <si>
+    <t>体+x（100+20*GR）</t>
+  </si>
+  <si>
+    <t>法然敷宵</t>
+  </si>
+  <si>
+    <t>敷宵剑状态不会扣除</t>
+  </si>
+  <si>
+    <t>护身剑</t>
+  </si>
+  <si>
+    <t>战斗开始时获得3层敷宵剑</t>
+  </si>
+  <si>
+    <t>傲锋</t>
+  </si>
+  <si>
+    <t>每回合首次行动决定后若为杀式，则本次行动在命中时增加30%伤害</t>
+  </si>
+  <si>
+    <t>锐心</t>
+  </si>
+  <si>
+    <t>与杀式交锋成功后根据二者威力差距5:1固定增加刚炁</t>
+  </si>
+  <si>
+    <t>百折不挠</t>
+  </si>
+  <si>
+    <t>交锋失败后下次刚炁或玄炁恢复额外增加3~8，该效果不可叠加</t>
+  </si>
+  <si>
+    <t>鬼蜮</t>
+  </si>
+  <si>
+    <t>每息首个行动的敌手根据其行动的类型及其最后一个键给予对应的留劲状态，在敌手每回合首次获得留劲状态时在本回合获得1次行动次数</t>
+  </si>
+  <si>
+    <t>虚无缥缈·甲</t>
+  </si>
+  <si>
+    <t>虚无缥缈·乙</t>
+  </si>
+  <si>
+    <t>虚无缥缈·丙</t>
+  </si>
+  <si>
+    <t>防+200%破+200%，受到攻击后各减少20%至回合结束</t>
+  </si>
+  <si>
+    <t>虚无缥缈·丁</t>
+  </si>
+  <si>
+    <t>不会受到武杀式/术杀式的直接伤害，每回合变化</t>
+  </si>
+  <si>
+    <t>失重</t>
+  </si>
+  <si>
+    <t>妖毒</t>
+  </si>
+  <si>
+    <t>污覆·甲</t>
+  </si>
+  <si>
+    <t>只会受到未消耗妖毒污染的键的招式造成的伤害</t>
+  </si>
+  <si>
+    <t>污覆·乙</t>
+  </si>
+  <si>
+    <t>防+120%破+120%，受击时攻击的敌手每有1层妖毒侵蚀状态穿透20%防20%破</t>
+  </si>
+  <si>
+    <t>污覆·丙</t>
+  </si>
+  <si>
+    <t>污覆·丁</t>
+  </si>
+  <si>
+    <t>毒雾弥漫</t>
+  </si>
+  <si>
+    <t>回合开始时向全部敌手随机施加一种毒向状态</t>
+  </si>
+  <si>
+    <t>玄窍</t>
+  </si>
+  <si>
+    <t>增加玄炁上限5</t>
+  </si>
+  <si>
+    <t>月华玄功</t>
+  </si>
+  <si>
+    <t>增加玄炁上限5减少刚炁上限5</t>
+  </si>
+  <si>
+    <t>蛟血之体</t>
+  </si>
+  <si>
+    <t>玄炁永远不会低于10</t>
+  </si>
+  <si>
+    <t>满欲</t>
+  </si>
+  <si>
+    <t>敌手一次移除了超过4层的妖毒状态或妖毒侵蚀状态则在本回合获得1次行动次数</t>
+  </si>
+  <si>
+    <t>勾牌人</t>
+  </si>
+  <si>
+    <t>存在其余友方角色时每回合首次被破招后获得1次行动次数</t>
+  </si>
+  <si>
+    <t>不遂之躯</t>
+  </si>
+  <si>
+    <t>不存在其余友方角色时进入击破状态</t>
+  </si>
+  <si>
+    <t>登台子午相</t>
+  </si>
+  <si>
+    <t>进入战斗时获得的键从10个随机的键变为不同方向的键各2个，回合开始时获得3个随机的键变为获得4个不同方向的键</t>
+  </si>
+  <si>
+    <t>庄家</t>
+  </si>
+  <si>
+    <t>行动意图揭示，交锋时若威力相同则视为交锋胜利</t>
+  </si>
+  <si>
+    <t>捕醉仙</t>
+  </si>
+  <si>
+    <t>非决定的杀式行动威力增加10</t>
+  </si>
+  <si>
+    <t>异体</t>
+  </si>
+  <si>
+    <t>自身存在的状态无法重复获得，每个回合首次行动减缓0~2息</t>
+  </si>
+  <si>
+    <t>大妖</t>
+  </si>
+  <si>
+    <t>回合开始获得1次行动次数，3个回合内只能被施加1次招式限制类状态且至多1层（6类）</t>
+  </si>
+  <si>
+    <t>抓千</t>
+  </si>
+  <si>
+    <t>在场角色的宝器都不会生效，行动所在息外敌手使用招式获得炁、键或是使用道具则对其施加2层残缺状态</t>
+  </si>
+  <si>
+    <t>处于未行动的息时防+30%破+30%</t>
+  </si>
+  <si>
+    <t>每回合首次行动次数耗尽后获得1层回避状态</t>
+  </si>
+  <si>
+    <t>无垢之体</t>
+  </si>
+  <si>
+    <t>回合结束时清除全部增益状态和异常状态</t>
+  </si>
+  <si>
+    <t>烈阳经</t>
+  </si>
+  <si>
+    <t>增加刚炁上限5</t>
+  </si>
+  <si>
+    <t>阳满待盈</t>
+  </si>
+  <si>
+    <t>使用招式直接恢复体时额外恢复5%技的体</t>
+  </si>
+  <si>
+    <t>阴满待凝</t>
+  </si>
+  <si>
+    <t>回合开始时玄炁至少100则获得1次行动次数</t>
+  </si>
+  <si>
+    <t>键为0时立即获得1个随机的键</t>
+  </si>
+  <si>
+    <t>脚底抹油</t>
+  </si>
+  <si>
+    <t>键的上限变为5。消耗键后消耗全部的键然后补充到上限。累计获得15个键后在本回合获得1次行动次数。</t>
+  </si>
+  <si>
+    <t>交锋胜利随机获得1个随机的键</t>
+  </si>
+  <si>
+    <t>体低于一半时回合开始额外获得1个随机的键</t>
+  </si>
+  <si>
+    <t>毅定风波</t>
+  </si>
+  <si>
+    <t>每回合首次受到直接攻击的伤害后获得1个随机的键</t>
+  </si>
+  <si>
+    <t>战斗中首次键为0时补充随机的键到达持有上限</t>
+  </si>
+  <si>
+    <t>驻位机关造物</t>
+  </si>
+  <si>
+    <t>回合开始，消耗刚炁与玄炁中最高的一项0.5%：1补充随机的键到达持有上限。刚炁与玄炁皆为0时直接进入击破状态。无法自然恢复炁。</t>
+  </si>
+  <si>
+    <t>强攻防护机关</t>
+  </si>
+  <si>
+    <t>豁免每回合首次受到的威力大于100的杀式直接伤害</t>
+  </si>
+  <si>
+    <t>自衍式机关造物</t>
+  </si>
+  <si>
+    <t>每息刚炁+3，玄炁+3，获得1个随机的键。</t>
+  </si>
+  <si>
+    <t>动炁感知</t>
+  </si>
+  <si>
+    <t>行动次数为0则在其余角色使用招式后获得1次行动次数，1回合至多触发1次。</t>
+  </si>
+  <si>
+    <t>机关造物</t>
+  </si>
+  <si>
+    <t>刚炁与玄炁皆为0时直接进入击破状态。无法自然恢复炁。</t>
+  </si>
+  <si>
+    <t>杀机无相</t>
+  </si>
+  <si>
+    <t>未成为敌手行动目标时不会暴露行动所在息与意图</t>
+  </si>
+  <si>
+    <t>力破万法</t>
+  </si>
+  <si>
+    <t>以武杀式交锋时也不会被实际伤害低于自身的招式破招</t>
+  </si>
+  <si>
+    <t>水骨不折</t>
+  </si>
+  <si>
+    <t>受到武杀式攻击后防+30%直到下次行动</t>
+  </si>
+  <si>
+    <t>载面</t>
+  </si>
+  <si>
+    <t>战斗开始获得戴面状态，每个回合首次获得戴面状态后在本回合获得1次行动次数</t>
+  </si>
+  <si>
+    <t>体低于一半时兽化身层数不会低于4层</t>
+  </si>
+  <si>
+    <t>累计经过4个回合后禽化身层数不会低于4层</t>
+  </si>
+  <si>
+    <t>累计有2人被击破时鬼化身层数不会低于4层</t>
+  </si>
+  <si>
+    <t>兽化身状态下不会被施加力衰、武衰状态</t>
+  </si>
+  <si>
+    <t>祖化身状态下不会被施加缓速、失衡状态</t>
+  </si>
+  <si>
+    <t>沉重吐息</t>
+  </si>
+  <si>
+    <t>行动后恢复10%刚炁</t>
+  </si>
+  <si>
+    <t>饱餍</t>
+  </si>
+  <si>
+    <t>每有一个角色被击破时恢复20%体并获得3层武增状态和3层力增状态</t>
+  </si>
+  <si>
+    <t>摆踱乘势</t>
+  </si>
+  <si>
+    <t>交锋成功/失败后获得一项增益状态（力增、武增、反击、迅速、巧增），效果每回合切换</t>
+  </si>
+  <si>
+    <t>跮踱乘势</t>
+  </si>
+  <si>
+    <t>交锋成功/失败后获得一项增益状态（力增、武增、反击、迅速、巧增），每次行动后切换</t>
+  </si>
+  <si>
+    <t>收到单方面攻击后增加10+RG*1力</t>
+  </si>
+  <si>
+    <t>抢占先机</t>
+  </si>
+  <si>
+    <t>首次自然恢复刚炁时额外恢复10</t>
+  </si>
+  <si>
+    <t>未雨绸缪</t>
+  </si>
+  <si>
+    <t>首次自然恢复玄炁时额外恢复10</t>
+  </si>
+  <si>
+    <t>中瘴者</t>
+  </si>
+  <si>
+    <t>回合开始获得1层毒瘴状态，若毒瘴状态层数不少于5则还会获得一次行动次数，释放法咒式与杀式后对目标施加1层毒瘴状态，释放技御式后获得1层毒瘴状态</t>
+  </si>
+  <si>
+    <t>侵蚀</t>
+  </si>
+  <si>
+    <t>带有瘴毒的角色被击破时恢复100+RG*10体，每层增加10%</t>
+  </si>
+  <si>
+    <t>刺激肉体</t>
+  </si>
+  <si>
+    <t>每获得1层毒瘴状态后随机获得1个键并恢复10刚炁10玄炁</t>
+  </si>
+  <si>
+    <t>雨割</t>
+  </si>
+  <si>
+    <t>雨天时受到招式的直接伤害变为等量的体上限扣除，以杀式造成直接伤害时也会扣除目标等量的体上限</t>
+  </si>
+  <si>
+    <t>金城铁壁</t>
+  </si>
+  <si>
+    <t>回合开始获得1层岳环状态</t>
+  </si>
+  <si>
+    <t>战斗开始获得1层岳环状态，回合开始若回合数为5则获得1层岳环状态</t>
+  </si>
+  <si>
+    <t>每回合首次术杀式释放成功后若刚炁大于50则在下一息向目标释放玄炁消耗最低的术杀式并清空刚炁，</t>
+  </si>
+  <si>
+    <t>福鸿</t>
+  </si>
+  <si>
+    <t>战斗开始时获得1层藏身状态和1层隐魂状态</t>
+  </si>
+  <si>
+    <t>命中行动已揭示的敌手获得随机增益（迅速/力增/技增/术增/武增/巧增）或一个随机的键或者5刚炁或者5玄炁</t>
+  </si>
+  <si>
+    <t>每累计损失x（20%面板基础）体时在本回合获得1次行动次数</t>
+  </si>
+  <si>
+    <t>若本回合已行动，受到杀式攻击时距离上一次行动所在息超过2息则受到的伤害越低（从相隔三息开始0.9的次方）</t>
+  </si>
+  <si>
+    <t>北帝先玄</t>
+  </si>
+  <si>
+    <t>刚炁可以作为玄炁使用</t>
+  </si>
+  <si>
+    <t>引电甲</t>
+  </si>
+  <si>
+    <t>受到攻击后若行动次数为0则对攻击者造成%术的伤害（距离上一次行动所在息越远则伤害越高，至多在5息到达2.5倍）</t>
+  </si>
+  <si>
+    <t>回合内行过1次加快至少1息的行动，则在下次受到攻击时获得1层反击状态。该效果每次触发的条件将在触发后增加1息，反之若进行过不满足加快程度的行动则减少1息（雾天减少2息）</t>
+  </si>
+  <si>
+    <t>交锋失败时若存在猊煞变状态，则消耗1层抵免破招效果</t>
+  </si>
+  <si>
+    <t>刚炁消耗减少不会低于3，回合开始时切换为玄炁消耗减少</t>
+  </si>
+  <si>
+    <t>昂膀</t>
+  </si>
+  <si>
+    <t>受到攻击后在本回合增加15+GR*1.5力</t>
+  </si>
+  <si>
+    <t>水生之道</t>
+  </si>
+  <si>
+    <t>受到武杀式攻击后下个回合开始获得1层迅速状态</t>
+  </si>
+  <si>
+    <t>梦为自如真</t>
+  </si>
+  <si>
+    <t>累计进行5次非决定的行动后获得3层武增3层术增状态，清除醉气状态获得等量迅速状态层数，并在下一息向随机敌手使用武杀式：惊鸿</t>
+  </si>
+  <si>
+    <t>酒痴</t>
+  </si>
+  <si>
+    <t>战斗外若存在酒类增益状态，战斗开始获得3层醉气状态并使酒类增益状态效果加倍。</t>
+  </si>
+  <si>
+    <t>武师职能</t>
+  </si>
+  <si>
+    <t>术士职能</t>
+  </si>
+  <si>
+    <t>玄炁越多，炁拶类术杀式伤害越高（30~100+，伤害1~2倍）</t>
+  </si>
+  <si>
+    <t>铁卫职能</t>
+  </si>
+  <si>
+    <t>承受行动目标的杀式攻击或杀式命中以自身为目标的敌手增加1层交鸣，杀式与杀式交锋则额外增加1层交鸣</t>
+  </si>
+  <si>
+    <t>影候职能</t>
+  </si>
+  <si>
+    <t>刚炁恢复额外增加10，玄炁不会自然恢复</t>
+  </si>
+  <si>
+    <t>艺者职能</t>
+  </si>
+  <si>
+    <t>玄炁恢复额外增加10，刚炁不会自然恢复</t>
+  </si>
+  <si>
+    <t>卸功拆招·丁</t>
+  </si>
+  <si>
+    <t>每个杀式交锋过1次对其增加承受该招式时破+50%防+50%的效果，至多2层。</t>
+  </si>
+  <si>
+    <t>卸功拆招·丙</t>
+  </si>
+  <si>
+    <t>每个杀式承受过1次对其增加承受该招式时破+30%防+30%的效果，至多2层。</t>
+  </si>
+  <si>
+    <t>卸功拆招·乙</t>
+  </si>
+  <si>
+    <t>每个杀式交锋或承受过1次对其增加承受该招式时破+20%防+20%的效果，至多4层。</t>
+  </si>
+  <si>
+    <t>卸功拆招·甲</t>
+  </si>
+  <si>
+    <t>破+50%防+50%</t>
+  </si>
+  <si>
+    <t>常时架势·御守</t>
+  </si>
+  <si>
+    <t>行动结束获得御守架势状态</t>
+  </si>
+  <si>
+    <t>妙术三手</t>
+  </si>
+  <si>
+    <t>每个回合首次使用物品后在本回合获得1次行动次数</t>
+  </si>
+  <si>
+    <t>以战养战</t>
+  </si>
+  <si>
+    <t>击破敌人获得1次行动次数并且玄炁+25、刚炁+25</t>
+  </si>
+  <si>
+    <t>日反暂明</t>
+  </si>
+  <si>
+    <t>回合开始时若体低于一半在本回合获得1次行动次数</t>
+  </si>
+  <si>
+    <t>鏖军百炼</t>
+  </si>
+  <si>
+    <t>回合开始时若回合超过4则在本回合获得1次行动次数</t>
+  </si>
+  <si>
+    <t>一气如雷</t>
+  </si>
+  <si>
+    <t>回合开始时若回合不超过3则在本回合获得1次行动次数</t>
+  </si>
+  <si>
+    <t>无往蹈锋</t>
+  </si>
+  <si>
+    <t>回合结束时若本回合有角色被击破过则在下回合获得1次行动次数</t>
+  </si>
+  <si>
+    <t>入武·巧劲</t>
+  </si>
+  <si>
+    <t>每回合首次释放武杀式加成提高5的百分比</t>
+  </si>
+  <si>
+    <t>入武·巧功</t>
+  </si>
+  <si>
+    <t>每回合首次释放武杀式加成提高10的百分比</t>
+  </si>
+  <si>
+    <t>入术·巧法</t>
+  </si>
+  <si>
+    <t>每回合首次释放术杀式加成提高5的百分比</t>
+  </si>
+  <si>
+    <t>入术·巧咒</t>
+  </si>
+  <si>
+    <t>每回合首次释放术杀式加成提高10的百分比</t>
+  </si>
+  <si>
+    <t>入武·下级</t>
+  </si>
+  <si>
+    <t>武杀式加成提高5的百分比</t>
+  </si>
+  <si>
+    <t>入武·上级</t>
+  </si>
+  <si>
+    <t>武杀式加成提高10的百分比</t>
+  </si>
+  <si>
+    <t>入术·下级</t>
+  </si>
+  <si>
+    <t>术杀式加成提高5的百分比</t>
+  </si>
+  <si>
+    <t>入术·上级</t>
+  </si>
+  <si>
+    <t>术杀式加成提高10的百分比</t>
+  </si>
+  <si>
+    <t>徐疾百踪</t>
+  </si>
+  <si>
+    <t>回合开始时获得1层迅速或缓速，速额外增加x（20+0.66*GR）</t>
+  </si>
+  <si>
+    <t>千招</t>
+  </si>
+  <si>
+    <t>累加三次不同式的行动使下一次行动的杀式威力提高10的百分比</t>
+  </si>
+  <si>
+    <t>百式</t>
+  </si>
+  <si>
+    <t>全部招式携带的技巧点占用减少1</t>
+  </si>
+  <si>
+    <t>武宗</t>
+  </si>
+  <si>
+    <t>武杀式的技巧点占用减少1，刚炁消耗减少2</t>
+  </si>
+  <si>
+    <t>术宗</t>
+  </si>
+  <si>
+    <t>术杀式的技巧点占用减少1，玄炁消耗减少2</t>
+  </si>
+  <si>
+    <t>入武·炁炼</t>
+  </si>
+  <si>
+    <t>行动决定后若刚炁超过50获得1~2层武增</t>
+  </si>
+  <si>
+    <t>入术·炁炼</t>
+  </si>
+  <si>
+    <t>行动决定后若玄炁超过50获得1~2层术增</t>
+  </si>
+  <si>
+    <t>翱涟</t>
+  </si>
+  <si>
+    <t>每有1层交鸣，武杀式加成提高5的百分比</t>
+  </si>
+  <si>
+    <t>遁形</t>
+  </si>
+  <si>
+    <t>即将受到使体低于30%的伤害时防+200%破+200%，触发后从下一回合开始无法再触发</t>
+  </si>
+  <si>
+    <t>碧月藏空</t>
+  </si>
+  <si>
+    <t>胜气·缓息</t>
+  </si>
+  <si>
+    <t>交锋胜利体+x（30+3*GR）</t>
+  </si>
+  <si>
+    <t>胜气·缓势</t>
+  </si>
+  <si>
+    <t>交锋胜利固定增加4刚炁</t>
+  </si>
+  <si>
+    <t>胜气·缓神</t>
+  </si>
+  <si>
+    <t>交锋胜利固定增加4玄炁</t>
+  </si>
+  <si>
+    <t>展锋</t>
+  </si>
+  <si>
+    <t>烙魂</t>
+  </si>
+  <si>
+    <t>术杀式直接伤害额外增加x（30+3*GR）</t>
+  </si>
+  <si>
+    <t>暴虎</t>
+  </si>
+  <si>
+    <t>武杀式直接伤害额外增加10%</t>
+  </si>
+  <si>
+    <t>ParamEx</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(list#sep=,),float</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>额外参数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.3,1,0,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10009</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.5,0.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10012</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,25,25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.5,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.05</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10017</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,20,0.66</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>50,1,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10032</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.3,2,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>体低于一半时受到攻击获得1层隐匿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>30,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>允许2个药力增益状态的存在</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4,0.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10060</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10,0.33</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10071</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3,8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>200008</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10083</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回合开始时向全部敌手施加2层妖毒状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5,-5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10090</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10092</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10096</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.3,0.3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10097</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10099</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>单方面攻击后目标未带有力衰状态则施加1层力衰状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回合开始时刚炁至少100则获得1次行动次数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10101</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10108</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10104</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3,3,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.5,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10121</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10123</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>禽化身状态下不会被施加技衰、术衰状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10126</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.2,3,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10127</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10130</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10,0.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴躁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,5,1,1,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10134</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100,10,0.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10135</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,10,10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,5,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10141</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>杀式命中时目标未带有破绽则施加1层</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第一回合首次行动，武杀式：投掷的伤害与施加的效果双倍</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10146</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15,1.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5,3,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10153</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3,0.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10016</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刚炁越多，炁拶类武杀式伤害越高（30~100+，伤害1~2倍）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武杀式直接伤害额外增加x（30+3*GR）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>允许装配相同键的招式，使用时随机释放其一</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10044</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10047</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>与行动的目标交锋成功后随机扣除目标一个键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>洞爻八象</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>体上限+60%，进入战斗时命扣除70%以上的部分</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10064</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>只会在回合其中一息受到直接伤害，每回合变化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>只会受到敌手在单个回合连续第4次行动所造成的伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>敌手无法通过状态、招式、心法效果获得键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10105</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回合开始若有过未所用招式的行动则获得次数等量的迅速</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -187,7 +1218,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -210,19 +1241,37 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -239,14 +1288,23 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -563,27 +1621,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
-  <dimension ref="A1:Q5"/>
+  <dimension ref="A1:E184"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="4" width="9" style="1"/>
-    <col min="5" max="5" width="20.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="31.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="27.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="29.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="21.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="28" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="27.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="21.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="20" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9" style="1"/>
+    <col min="1" max="2" width="9" style="1"/>
+    <col min="3" max="3" width="15.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="170.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -597,46 +1645,10 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -650,46 +1662,10 @@
         <v>6</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -703,65 +1679,1977 @@
         <v>9</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="3">
+        <v>10001</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="3">
+        <v>10002</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B6" s="1">
+        <v>10003</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B7" s="1">
+        <v>10004</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B8" s="1">
+        <v>10005</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="2">
+        <v>10006</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="2">
+        <v>10007</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="2">
+        <v>10008</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B12" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="1">
+        <v>10010</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="2">
+        <v>10011</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B15" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B16" s="1">
+        <v>10013</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B17" s="1">
+        <v>10014</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B18" s="1">
+        <v>10015</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B19" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B20" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B21" s="1">
+        <v>10018</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B22" s="1">
+        <v>10019</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B23" s="1">
+        <v>10020</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B24" s="1">
+        <v>10021</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B25" s="1">
+        <v>10022</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B26" s="1">
+        <v>10023</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B27" s="1">
+        <v>10024</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B28" s="1">
+        <v>10025</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B29" s="4">
+        <v>10026</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B30" s="2">
+        <v>10027</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B31" s="2">
+        <v>10028</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B32" s="2">
+        <v>10029</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B33" s="1">
+        <v>10030</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="34" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B34" s="1">
+        <v>10031</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B35" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="36" spans="2:5" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B36" s="3">
+        <v>10033</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="37" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B37" s="1">
+        <v>10034</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="38" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B38" s="1">
+        <v>10035</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="39" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B39" s="1">
+        <v>10036</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="40" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B40" s="1">
+        <v>10037</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="41" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B41" s="2">
+        <v>10038</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="42" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B42" s="2">
+        <v>10039</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="43" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B43" s="1">
+        <v>10040</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="44" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B44" s="1">
+        <v>10041</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="45" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B45" s="2">
+        <v>10042</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="46" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B46" s="2">
+        <v>10043</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="47" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B47" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="48" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B48" s="2">
+        <v>10045</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="49" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B49" s="1">
+        <v>10046</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="50" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B50" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D50" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="E50" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="51" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B51" s="2">
+        <v>10048</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="52" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B52" s="1">
+        <v>10049</v>
+      </c>
+      <c r="D52" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="E52" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="53" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B53" s="2">
+        <v>10050</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="54" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B54" s="2">
+        <v>10051</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="55" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B55" s="2">
+        <v>10052</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="56" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B56" s="2">
+        <v>10053</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="57" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B57" s="1">
+        <v>10054</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="58" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B58" s="2">
+        <v>10055</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="59" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B59" s="2">
+        <v>10056</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="60" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B60" s="2">
+        <v>10057</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="61" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B61" s="1">
+        <v>10058</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="62" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B62" s="4">
+        <v>10059</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="63" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B63" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D63" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B4" s="1">
-        <v>1</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B5" s="1">
-        <v>2</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>11</v>
+    </row>
+    <row r="64" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B64" s="1">
+        <v>10061</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="65" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B65" s="1">
+        <v>10062</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="66" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B66" s="5">
+        <v>10063</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D66" s="5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="67" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B67" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="D67" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E67" s="5" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="68" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B68" s="5">
+        <v>10065</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D68" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="69" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B69" s="5">
+        <v>10066</v>
+      </c>
+      <c r="C69" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D69" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="70" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B70" s="5">
+        <v>10067</v>
+      </c>
+      <c r="C70" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D70" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="71" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B71" s="1">
+        <v>10068</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="72" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B72" s="1">
+        <v>10069</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="73" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B73" s="1">
+        <v>10070</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="74" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B74" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="75" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B75" s="5">
+        <v>10072</v>
+      </c>
+      <c r="C75" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D75" s="5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="76" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B76" s="5">
+        <v>10073</v>
+      </c>
+      <c r="C76" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D76" s="5" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="77" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B77" s="5">
+        <v>10074</v>
+      </c>
+      <c r="C77" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D77" s="5" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="78" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B78" s="5">
+        <v>10075</v>
+      </c>
+      <c r="C78" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D78" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="79" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B79" s="5">
+        <v>10076</v>
+      </c>
+      <c r="C79" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D79" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="80" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B80" s="5">
+        <v>10077</v>
+      </c>
+      <c r="C80" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D80" s="5" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="81" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B81" s="4">
+        <v>10078</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="E81" s="4" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="82" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B82" s="5">
+        <v>10079</v>
+      </c>
+      <c r="C82" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="D82" s="5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="83" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B83" s="5">
+        <v>10080</v>
+      </c>
+      <c r="C83" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D83" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="84" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B84" s="5">
+        <v>10081</v>
+      </c>
+      <c r="C84" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="85" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B85" s="5">
+        <v>10082</v>
+      </c>
+      <c r="C85" s="5" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="86" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B86" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D86" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E86" s="4" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="87" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B87" s="1">
+        <v>10084</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="88" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B88" s="1">
+        <v>10085</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="89" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B89" s="1">
+        <v>10086</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="90" spans="2:5" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B90" s="3">
+        <v>10087</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="91" spans="2:5" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B91" s="3">
+        <v>10088</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="92" spans="2:5" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B92" s="3">
+        <v>10089</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="93" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B93" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="94" spans="2:5" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B94" s="3">
+        <v>10091</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="95" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B95" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="96" spans="2:5" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B96" s="3">
+        <v>10093</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="97" spans="2:5" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B97" s="3">
+        <v>10094</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="98" spans="2:5" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B98" s="3">
+        <v>10095</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="99" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B99" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="100" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B100" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="101" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B101" s="1">
+        <v>10098</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="102" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B102" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="103" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B103" s="1">
+        <v>10100</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="104" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B104" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="105" spans="2:5" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B105" s="3">
+        <v>10102</v>
+      </c>
+      <c r="D105" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="106" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B106" s="1">
+        <v>10103</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="107" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B107" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="108" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B108" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="109" spans="2:5" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B109" s="3">
+        <v>10106</v>
+      </c>
+      <c r="D109" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="110" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B110" s="1">
+        <v>10107</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="111" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B111" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="112" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B112" s="1">
+        <v>10109</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="113" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B113" s="1">
+        <v>10110</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="114" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B114" s="2">
+        <v>10111</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="115" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B115" s="2">
+        <v>10112</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="116" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B116" s="1">
+        <v>10113</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E116" s="1" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="117" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B117" s="2">
+        <v>10114</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="118" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B118" s="1">
+        <v>10115</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="119" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B119" s="2">
+        <v>10116</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="120" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B120" s="2">
+        <v>10117</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="121" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B121" s="1">
+        <v>10118</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="E121" s="1" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="122" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B122" s="1">
+        <v>10119</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="123" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B123" s="1">
+        <v>10120</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="124" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B124" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="125" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B125" s="1">
+        <v>10122</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="E125" s="1" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="126" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B126" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="127" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B127" s="1">
+        <v>10124</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="128" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B128" s="1">
+        <v>10125</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="129" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B129" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E129" s="1" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="130" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B130" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="E130" s="1" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="131" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B131" s="2">
+        <v>10128</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="132" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B132" s="2">
+        <v>10129</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="133" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B133" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="E133" s="1" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="134" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B134" s="1">
+        <v>10131</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="E134" s="1" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="135" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B135" s="1">
+        <v>10132</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E135" s="1" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="136" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B136" s="1">
+        <v>10133</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E136" s="1" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="137" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B137" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E137" s="1" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="138" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B138" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="139" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B139" s="2">
+        <v>10136</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D139" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="140" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B140" s="1">
+        <v>10137</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="E140" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="141" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B141" s="1">
+        <v>10138</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="E141" s="1" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="142" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B142" s="2">
+        <v>10139</v>
+      </c>
+      <c r="D142" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="143" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B143" s="1">
+        <v>10140</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="E143" s="1" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="144" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B144" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="D144" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="E144" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="145" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B145" s="2">
+        <v>10142</v>
+      </c>
+      <c r="D145" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="146" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B146" s="2">
+        <v>10143</v>
+      </c>
+      <c r="D146" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="147" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B147" s="1">
+        <v>10144</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="148" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B148" s="2">
+        <v>10145</v>
+      </c>
+      <c r="D148" s="2" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="149" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B149" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="D149" s="1" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="150" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B150" s="2">
+        <v>10147</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D150" s="2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="151" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B151" s="2">
+        <v>10148</v>
+      </c>
+      <c r="D151" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="152" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B152" s="2">
+        <v>10149</v>
+      </c>
+      <c r="D152" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="153" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B153" s="2">
+        <v>10150</v>
+      </c>
+      <c r="D153" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="154" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B154" s="1">
+        <v>10151</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D154" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E154" s="1" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="155" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B155" s="1">
+        <v>10152</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="D155" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="E155" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="156" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B156" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="D156" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="E156" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="157" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B157" s="2">
+        <v>10154</v>
+      </c>
+      <c r="C157" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="D157" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="158" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B158" s="1">
+        <v>10155</v>
+      </c>
+    </row>
+    <row r="159" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B159" s="1">
+        <v>10156</v>
+      </c>
+    </row>
+    <row r="160" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B160" s="1">
+        <v>10157</v>
+      </c>
+    </row>
+    <row r="161" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B161" s="1">
+        <v>10158</v>
+      </c>
+    </row>
+    <row r="162" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B162" s="1">
+        <v>10159</v>
+      </c>
+    </row>
+    <row r="163" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B163" s="1">
+        <v>10160</v>
+      </c>
+    </row>
+    <row r="164" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B164" s="1">
+        <v>10161</v>
+      </c>
+    </row>
+    <row r="165" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B165" s="1">
+        <v>10162</v>
+      </c>
+    </row>
+    <row r="166" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B166" s="1">
+        <v>10163</v>
+      </c>
+    </row>
+    <row r="167" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B167" s="1">
+        <v>10164</v>
+      </c>
+    </row>
+    <row r="168" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B168" s="1">
+        <v>10165</v>
+      </c>
+    </row>
+    <row r="169" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B169" s="1">
+        <v>10166</v>
+      </c>
+    </row>
+    <row r="170" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B170" s="1">
+        <v>10167</v>
+      </c>
+    </row>
+    <row r="171" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B171" s="1">
+        <v>10168</v>
+      </c>
+    </row>
+    <row r="172" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B172" s="1">
+        <v>10169</v>
+      </c>
+    </row>
+    <row r="173" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B173" s="1">
+        <v>10170</v>
+      </c>
+    </row>
+    <row r="174" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B174" s="1">
+        <v>10171</v>
+      </c>
+    </row>
+    <row r="175" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B175" s="1">
+        <v>10172</v>
+      </c>
+    </row>
+    <row r="176" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B176" s="1">
+        <v>10173</v>
+      </c>
+    </row>
+    <row r="177" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B177" s="1">
+        <v>10174</v>
+      </c>
+    </row>
+    <row r="178" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B178" s="1">
+        <v>10175</v>
+      </c>
+    </row>
+    <row r="179" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B179" s="1">
+        <v>10176</v>
+      </c>
+    </row>
+    <row r="180" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B180" s="1">
+        <v>10177</v>
+      </c>
+    </row>
+    <row r="181" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B181" s="1">
+        <v>10178</v>
+      </c>
+    </row>
+    <row r="182" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B182" s="1">
+        <v>10179</v>
+      </c>
+    </row>
+    <row r="183" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B183" s="1">
+        <v>10180</v>
+      </c>
+    </row>
+    <row r="184" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B184" s="1">
+        <v>10181</v>
       </c>
     </row>
   </sheetData>

--- a/Luban/Config/Datas/#HeartMethodConfig.xlsx
+++ b/Luban/Config/Datas/#HeartMethodConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F65116F6-3BB8-4B49-90F9-DC6F2FC42500}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B006A112-B425-4681-AD6B-0AE0CE411E87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="363">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1211,6 +1211,26 @@
   </si>
   <si>
     <t>回合开始若有过未所用招式的行动则获得次数等量的迅速</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.5,0.5,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.3,0.3,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.2,0.2,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10038</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10043</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1682,31 +1702,31 @@
         <v>266</v>
       </c>
     </row>
-    <row r="4" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B4" s="1">
         <v>10001</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="1" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="5" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B5" s="1">
         <v>10002</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="1" t="s">
         <v>267</v>
       </c>
     </row>
@@ -1749,37 +1769,46 @@
         <v>268</v>
       </c>
     </row>
-    <row r="9" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B9" s="1">
         <v>10006</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="1" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="2">
+      <c r="E9" s="1" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B10" s="1">
         <v>10007</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="1" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="2">
+      <c r="E10" s="1" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B11" s="1">
         <v>10008</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="1" t="s">
         <v>201</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>360</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
@@ -2182,26 +2211,32 @@
         <v>287</v>
       </c>
     </row>
-    <row r="41" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B41" s="2">
-        <v>10038</v>
-      </c>
-      <c r="C41" s="2" t="s">
+    <row r="41" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B41" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="C41" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="D41" s="2" t="s">
+      <c r="D41" s="1" t="s">
         <v>345</v>
       </c>
-    </row>
-    <row r="42" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B42" s="2">
+      <c r="E41" s="1" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="42" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B42" s="1">
         <v>10039</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="C42" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="D42" s="2" t="s">
+      <c r="D42" s="1" t="s">
         <v>261</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="43" spans="2:5" x14ac:dyDescent="0.2">
@@ -2243,15 +2278,18 @@
         <v>13</v>
       </c>
     </row>
-    <row r="46" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B46" s="2">
-        <v>10043</v>
-      </c>
-      <c r="C46" s="2" t="s">
+    <row r="46" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B46" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="C46" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D46" s="2" t="s">
+      <c r="D46" s="1" t="s">
         <v>288</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="47" spans="2:5" x14ac:dyDescent="0.2">

--- a/Luban/Config/Datas/#HeartMethodConfig.xlsx
+++ b/Luban/Config/Datas/#HeartMethodConfig.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B006A112-B425-4681-AD6B-0AE0CE411E87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A942CA7-2830-42F6-922E-202A2D08CCC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="401">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -235,1002 +235,1175 @@
     <t>虚无缥缈·乙</t>
   </si>
   <si>
+    <t>失重</t>
+  </si>
+  <si>
+    <t>妖毒</t>
+  </si>
+  <si>
+    <t>污覆·甲</t>
+  </si>
+  <si>
+    <t>污覆·乙</t>
+  </si>
+  <si>
+    <t>污覆·丙</t>
+  </si>
+  <si>
+    <t>污覆·丁</t>
+  </si>
+  <si>
+    <t>毒雾弥漫</t>
+  </si>
+  <si>
+    <t>回合开始时向全部敌手随机施加一种毒向状态</t>
+  </si>
+  <si>
+    <t>玄窍</t>
+  </si>
+  <si>
+    <t>增加玄炁上限5</t>
+  </si>
+  <si>
+    <t>月华玄功</t>
+  </si>
+  <si>
+    <t>增加玄炁上限5减少刚炁上限5</t>
+  </si>
+  <si>
+    <t>蛟血之体</t>
+  </si>
+  <si>
+    <t>玄炁永远不会低于10</t>
+  </si>
+  <si>
+    <t>不存在其余友方角色时进入击破状态</t>
+  </si>
+  <si>
+    <t>登台子午相</t>
+  </si>
+  <si>
+    <t>进入战斗时获得的键从10个随机的键变为不同方向的键各2个，回合开始时获得3个随机的键变为获得4个不同方向的键</t>
+  </si>
+  <si>
+    <t>庄家</t>
+  </si>
+  <si>
+    <t>捕醉仙</t>
+  </si>
+  <si>
+    <t>非决定的杀式行动威力增加10</t>
+  </si>
+  <si>
+    <t>异体</t>
+  </si>
+  <si>
+    <t>自身存在的状态无法重复获得，每个回合首次行动减缓0~2息</t>
+  </si>
+  <si>
+    <t>大妖</t>
+  </si>
+  <si>
+    <t>回合开始获得1次行动次数，3个回合内只能被施加1次招式限制类状态且至多1层（6类）</t>
+  </si>
+  <si>
+    <t>抓千</t>
+  </si>
+  <si>
+    <t>处于未行动的息时防+30%破+30%</t>
+  </si>
+  <si>
+    <t>每回合首次行动次数耗尽后获得1层回避状态</t>
+  </si>
+  <si>
+    <t>无垢之体</t>
+  </si>
+  <si>
+    <t>回合结束时清除全部增益状态和异常状态</t>
+  </si>
+  <si>
+    <t>烈阳经</t>
+  </si>
+  <si>
+    <t>增加刚炁上限5</t>
+  </si>
+  <si>
+    <t>阳满待盈</t>
+  </si>
+  <si>
+    <t>阴满待凝</t>
+  </si>
+  <si>
+    <t>回合开始时玄炁至少100则获得1次行动次数</t>
+  </si>
+  <si>
+    <t>键为0时立即获得1个随机的键</t>
+  </si>
+  <si>
+    <t>脚底抹油</t>
+  </si>
+  <si>
+    <t>交锋胜利随机获得1个随机的键</t>
+  </si>
+  <si>
+    <t>体低于一半时回合开始额外获得1个随机的键</t>
+  </si>
+  <si>
+    <t>毅定风波</t>
+  </si>
+  <si>
+    <t>每回合首次受到直接攻击的伤害后获得1个随机的键</t>
+  </si>
+  <si>
+    <t>战斗中首次键为0时补充随机的键到达持有上限</t>
+  </si>
+  <si>
+    <t>驻位机关造物</t>
+  </si>
+  <si>
+    <t>回合开始，消耗刚炁与玄炁中最高的一项0.5%：1补充随机的键到达持有上限。刚炁与玄炁皆为0时直接进入击破状态。无法自然恢复炁。</t>
+  </si>
+  <si>
+    <t>强攻防护机关</t>
+  </si>
+  <si>
+    <t>豁免每回合首次受到的威力大于100的杀式直接伤害</t>
+  </si>
+  <si>
+    <t>自衍式机关造物</t>
+  </si>
+  <si>
+    <t>每息刚炁+3，玄炁+3，获得1个随机的键。</t>
+  </si>
+  <si>
+    <t>动炁感知</t>
+  </si>
+  <si>
+    <t>行动次数为0则在其余角色使用招式后获得1次行动次数，1回合至多触发1次。</t>
+  </si>
+  <si>
+    <t>机关造物</t>
+  </si>
+  <si>
+    <t>刚炁与玄炁皆为0时直接进入击破状态。无法自然恢复炁。</t>
+  </si>
+  <si>
+    <t>杀机无相</t>
+  </si>
+  <si>
+    <t>未成为敌手行动目标时不会暴露行动所在息与意图</t>
+  </si>
+  <si>
+    <t>力破万法</t>
+  </si>
+  <si>
+    <t>水骨不折</t>
+  </si>
+  <si>
+    <t>受到武杀式攻击后防+30%直到下次行动</t>
+  </si>
+  <si>
+    <t>载面</t>
+  </si>
+  <si>
+    <t>战斗开始获得戴面状态，每个回合首次获得戴面状态后在本回合获得1次行动次数</t>
+  </si>
+  <si>
+    <t>体低于一半时兽化身层数不会低于4层</t>
+  </si>
+  <si>
+    <t>累计经过4个回合后禽化身层数不会低于4层</t>
+  </si>
+  <si>
+    <t>累计有2人被击破时鬼化身层数不会低于4层</t>
+  </si>
+  <si>
+    <t>兽化身状态下不会被施加力衰、武衰状态</t>
+  </si>
+  <si>
+    <t>祖化身状态下不会被施加缓速、失衡状态</t>
+  </si>
+  <si>
+    <t>沉重吐息</t>
+  </si>
+  <si>
+    <t>行动后恢复10%刚炁</t>
+  </si>
+  <si>
+    <t>饱餍</t>
+  </si>
+  <si>
+    <t>每有一个角色被击破时恢复20%体并获得3层武增状态和3层力增状态</t>
+  </si>
+  <si>
+    <t>摆踱乘势</t>
+  </si>
+  <si>
+    <t>跮踱乘势</t>
+  </si>
+  <si>
+    <t>交锋成功/失败后获得一项增益状态（力增、武增、反击、迅速、巧增），每次行动后切换</t>
+  </si>
+  <si>
+    <t>收到单方面攻击后增加10+RG*1力</t>
+  </si>
+  <si>
+    <t>抢占先机</t>
+  </si>
+  <si>
+    <t>首次自然恢复刚炁时额外恢复10</t>
+  </si>
+  <si>
+    <t>未雨绸缪</t>
+  </si>
+  <si>
+    <t>首次自然恢复玄炁时额外恢复10</t>
+  </si>
+  <si>
+    <t>中瘴者</t>
+  </si>
+  <si>
+    <t>回合开始获得1层毒瘴状态，若毒瘴状态层数不少于5则还会获得一次行动次数，释放法咒式与杀式后对目标施加1层毒瘴状态，释放技御式后获得1层毒瘴状态</t>
+  </si>
+  <si>
+    <t>侵蚀</t>
+  </si>
+  <si>
+    <t>带有瘴毒的角色被击破时恢复100+RG*10体，每层增加10%</t>
+  </si>
+  <si>
+    <t>刺激肉体</t>
+  </si>
+  <si>
+    <t>每获得1层毒瘴状态后随机获得1个键并恢复10刚炁10玄炁</t>
+  </si>
+  <si>
+    <t>雨割</t>
+  </si>
+  <si>
+    <t>雨天时受到招式的直接伤害变为等量的体上限扣除，以杀式造成直接伤害时也会扣除目标等量的体上限</t>
+  </si>
+  <si>
+    <t>金城铁壁</t>
+  </si>
+  <si>
+    <t>回合开始获得1层岳环状态</t>
+  </si>
+  <si>
+    <t>战斗开始获得1层岳环状态，回合开始若回合数为5则获得1层岳环状态</t>
+  </si>
+  <si>
+    <t>每回合首次术杀式释放成功后若刚炁大于50则在下一息向目标释放玄炁消耗最低的术杀式并清空刚炁，</t>
+  </si>
+  <si>
+    <t>福鸿</t>
+  </si>
+  <si>
+    <t>战斗开始时获得1层藏身状态和1层隐魂状态</t>
+  </si>
+  <si>
+    <t>若本回合已行动，受到杀式攻击时距离上一次行动所在息超过2息则受到的伤害越低（从相隔三息开始0.9的次方）</t>
+  </si>
+  <si>
+    <t>北帝先玄</t>
+  </si>
+  <si>
+    <t>刚炁可以作为玄炁使用</t>
+  </si>
+  <si>
+    <t>引电甲</t>
+  </si>
+  <si>
+    <t>受到攻击后若行动次数为0则对攻击者造成%术的伤害（距离上一次行动所在息越远则伤害越高，至多在5息到达2.5倍）</t>
+  </si>
+  <si>
+    <t>回合内行过1次加快至少1息的行动，则在下次受到攻击时获得1层反击状态。该效果每次触发的条件将在触发后增加1息，反之若进行过不满足加快程度的行动则减少1息（雾天减少2息）</t>
+  </si>
+  <si>
+    <t>刚炁消耗减少不会低于3，回合开始时切换为玄炁消耗减少</t>
+  </si>
+  <si>
+    <t>昂膀</t>
+  </si>
+  <si>
+    <t>受到攻击后在本回合增加15+GR*1.5力</t>
+  </si>
+  <si>
+    <t>水生之道</t>
+  </si>
+  <si>
+    <t>受到武杀式攻击后下个回合开始获得1层迅速状态</t>
+  </si>
+  <si>
+    <t>梦为自如真</t>
+  </si>
+  <si>
+    <t>累计进行5次非决定的行动后获得3层武增3层术增状态，清除醉气状态获得等量迅速状态层数，并在下一息向随机敌手使用武杀式：惊鸿</t>
+  </si>
+  <si>
+    <t>酒痴</t>
+  </si>
+  <si>
+    <t>战斗外若存在酒类增益状态，战斗开始获得3层醉气状态并使酒类增益状态效果加倍。</t>
+  </si>
+  <si>
+    <t>武师职能</t>
+  </si>
+  <si>
+    <t>术士职能</t>
+  </si>
+  <si>
+    <t>玄炁越多，炁拶类术杀式伤害越高（30~100+，伤害1~2倍）</t>
+  </si>
+  <si>
+    <t>铁卫职能</t>
+  </si>
+  <si>
+    <t>承受行动目标的杀式攻击或杀式命中以自身为目标的敌手增加1层交鸣，杀式与杀式交锋则额外增加1层交鸣</t>
+  </si>
+  <si>
+    <t>影候职能</t>
+  </si>
+  <si>
+    <t>刚炁恢复额外增加10，玄炁不会自然恢复</t>
+  </si>
+  <si>
+    <t>艺者职能</t>
+  </si>
+  <si>
+    <t>玄炁恢复额外增加10，刚炁不会自然恢复</t>
+  </si>
+  <si>
+    <t>卸功拆招·丁</t>
+  </si>
+  <si>
+    <t>每个杀式交锋过1次对其增加承受该招式时破+50%防+50%的效果，至多2层。</t>
+  </si>
+  <si>
+    <t>卸功拆招·丙</t>
+  </si>
+  <si>
+    <t>每个杀式承受过1次对其增加承受该招式时破+30%防+30%的效果，至多2层。</t>
+  </si>
+  <si>
+    <t>卸功拆招·乙</t>
+  </si>
+  <si>
+    <t>每个杀式交锋或承受过1次对其增加承受该招式时破+20%防+20%的效果，至多4层。</t>
+  </si>
+  <si>
+    <t>卸功拆招·甲</t>
+  </si>
+  <si>
+    <t>破+50%防+50%</t>
+  </si>
+  <si>
+    <t>常时架势·御守</t>
+  </si>
+  <si>
+    <t>行动结束获得御守架势状态</t>
+  </si>
+  <si>
+    <t>妙术三手</t>
+  </si>
+  <si>
+    <t>每个回合首次使用物品后在本回合获得1次行动次数</t>
+  </si>
+  <si>
+    <t>以战养战</t>
+  </si>
+  <si>
+    <t>日反暂明</t>
+  </si>
+  <si>
+    <t>回合开始时若体低于一半在本回合获得1次行动次数</t>
+  </si>
+  <si>
+    <t>鏖军百炼</t>
+  </si>
+  <si>
+    <t>回合开始时若回合超过4则在本回合获得1次行动次数</t>
+  </si>
+  <si>
+    <t>一气如雷</t>
+  </si>
+  <si>
+    <t>回合开始时若回合不超过3则在本回合获得1次行动次数</t>
+  </si>
+  <si>
+    <t>无往蹈锋</t>
+  </si>
+  <si>
+    <t>回合结束时若本回合有角色被击破过则在下回合获得1次行动次数</t>
+  </si>
+  <si>
+    <t>入武·巧劲</t>
+  </si>
+  <si>
+    <t>每回合首次释放武杀式加成提高5的百分比</t>
+  </si>
+  <si>
+    <t>入武·巧功</t>
+  </si>
+  <si>
+    <t>每回合首次释放武杀式加成提高10的百分比</t>
+  </si>
+  <si>
+    <t>入术·巧法</t>
+  </si>
+  <si>
+    <t>每回合首次释放术杀式加成提高5的百分比</t>
+  </si>
+  <si>
+    <t>入术·巧咒</t>
+  </si>
+  <si>
+    <t>每回合首次释放术杀式加成提高10的百分比</t>
+  </si>
+  <si>
+    <t>入武·下级</t>
+  </si>
+  <si>
+    <t>武杀式加成提高5的百分比</t>
+  </si>
+  <si>
+    <t>入武·上级</t>
+  </si>
+  <si>
+    <t>武杀式加成提高10的百分比</t>
+  </si>
+  <si>
+    <t>入术·下级</t>
+  </si>
+  <si>
+    <t>术杀式加成提高5的百分比</t>
+  </si>
+  <si>
+    <t>入术·上级</t>
+  </si>
+  <si>
+    <t>术杀式加成提高10的百分比</t>
+  </si>
+  <si>
+    <t>徐疾百踪</t>
+  </si>
+  <si>
+    <t>回合开始时获得1层迅速或缓速，速额外增加x（20+0.66*GR）</t>
+  </si>
+  <si>
+    <t>千招</t>
+  </si>
+  <si>
+    <t>累加三次不同式的行动使下一次行动的杀式威力提高10的百分比</t>
+  </si>
+  <si>
+    <t>百式</t>
+  </si>
+  <si>
+    <t>全部招式携带的技巧点占用减少1</t>
+  </si>
+  <si>
+    <t>武宗</t>
+  </si>
+  <si>
+    <t>武杀式的技巧点占用减少1，刚炁消耗减少2</t>
+  </si>
+  <si>
+    <t>术宗</t>
+  </si>
+  <si>
+    <t>术杀式的技巧点占用减少1，玄炁消耗减少2</t>
+  </si>
+  <si>
+    <t>入武·炁炼</t>
+  </si>
+  <si>
+    <t>行动决定后若刚炁超过50获得1~2层武增</t>
+  </si>
+  <si>
+    <t>入术·炁炼</t>
+  </si>
+  <si>
+    <t>行动决定后若玄炁超过50获得1~2层术增</t>
+  </si>
+  <si>
+    <t>翱涟</t>
+  </si>
+  <si>
+    <t>每有1层交鸣，武杀式加成提高5的百分比</t>
+  </si>
+  <si>
+    <t>遁形</t>
+  </si>
+  <si>
+    <t>即将受到使体低于30%的伤害时防+200%破+200%，触发后从下一回合开始无法再触发</t>
+  </si>
+  <si>
+    <t>碧月藏空</t>
+  </si>
+  <si>
+    <t>胜气·缓息</t>
+  </si>
+  <si>
+    <t>交锋胜利体+x（30+3*GR）</t>
+  </si>
+  <si>
+    <t>胜气·缓势</t>
+  </si>
+  <si>
+    <t>交锋胜利固定增加4刚炁</t>
+  </si>
+  <si>
+    <t>胜气·缓神</t>
+  </si>
+  <si>
+    <t>交锋胜利固定增加4玄炁</t>
+  </si>
+  <si>
+    <t>展锋</t>
+  </si>
+  <si>
+    <t>烙魂</t>
+  </si>
+  <si>
+    <t>术杀式直接伤害额外增加x（30+3*GR）</t>
+  </si>
+  <si>
+    <t>暴虎</t>
+  </si>
+  <si>
+    <t>武杀式直接伤害额外增加10%</t>
+  </si>
+  <si>
+    <t>ParamEx</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(list#sep=,),float</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>额外参数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.3,1,0,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10009</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.5,0.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10012</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,25,25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.5,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.05</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10017</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,20,0.66</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>50,1,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10032</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.3,2,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>体低于一半时受到攻击获得1层隐匿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>30,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>允许2个药力增益状态的存在</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4,0.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10060</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10,0.33</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10071</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3,8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>200008</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10083</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回合开始时向全部敌手施加2层妖毒状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5,-5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10090</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10092</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10096</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.3,0.3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10097</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10099</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>单方面攻击后目标未带有力衰状态则施加1层力衰状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回合开始时刚炁至少100则获得1次行动次数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10101</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10108</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10104</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3,3,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.5,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10121</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10123</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>禽化身状态下不会被施加技衰、术衰状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10126</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.2,3,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10127</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10130</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10,0.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴躁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,5,1,1,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10134</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100,10,0.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10135</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,10,10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,5,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10141</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>杀式命中时目标未带有破绽则施加1层</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第一回合首次行动，武杀式：投掷的伤害与施加的效果双倍</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10146</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15,1.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5,3,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10153</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3,0.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10016</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刚炁越多，炁拶类武杀式伤害越高（30~100+，伤害1~2倍）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武杀式直接伤害额外增加x（30+3*GR）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>允许装配相同键的招式，使用时随机释放其一</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10044</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10047</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>与行动的目标交锋成功后随机扣除目标一个键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>洞爻八象</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>体上限+60%，进入战斗时命扣除70%以上的部分</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10064</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>只会在回合其中一息受到直接伤害，每回合变化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>只会受到敌手在单个回合连续第4次行动所造成的伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>敌手无法通过状态、招式、心法效果获得键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10105</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回合开始若有过未所用招式的行动则获得次数等量的迅速</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.5,0.5,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.3,0.3,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.2,0.2,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10038</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10043</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1001,0.15,0.15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10055</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10056</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.6,0.7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10065</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10077</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10067</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>敌手一次移除了超过4层的妖毒状态或妖毒侵蚀状态则在本回合获得1次行动次数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>满欲</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-4,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不遂之躯</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10089</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-2,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10093</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10088</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>勾牌人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>存在其余友方角色时每回合首次被破招后获得1次行动次数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>行动意图揭示，交锋时若威力相同则视为交锋胜利</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,3,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10102</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用招式直接恢复体时额外恢复5%技的体</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10111</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.005</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10112</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10114</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10150</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>交锋失败时若存在猊煞变状态，则消耗1层抵免破招效果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10142</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>命中行动已揭示的敌手获得随机增益（迅速/力增/技增/术增/武增/巧增）或一个随机的键或者5刚炁或者5玄炁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>200009,1,5,5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10143</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>以武杀式交锋时也不会被实际伤害低于自身的招式破招</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.2,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每累计损失x（20%面板基础）体时在本回合获得1次行动次数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10149</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>交锋成功/失败后获得一项增益状态（力增、武增、反击、迅速、巧增），效果每回合切换</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>200010</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在场角色的宝器都不会生效，行动所在息外敌手使用招式获得炁、键或是使用道具则对其施加2层残缺状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10095</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10106</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5,15,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>键的上限变为5。消耗键后消耗全部的键然后补充到上限。累计获得15个键后在本回合获得1次行动次数。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10136</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10073</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10072</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>虚无缥缈·丙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10075</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,2,0.2,0.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>防+200%破+200%，受到攻击后各减少20%至回合结束</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>虚无缥缈·丁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>不会受到武杀式/术杀式的直接伤害，每回合变化</t>
-  </si>
-  <si>
-    <t>失重</t>
-  </si>
-  <si>
-    <t>妖毒</t>
-  </si>
-  <si>
-    <t>污覆·甲</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.2,1.2,0.2,0.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>防+120%破+120%，受击时攻击的敌手每有1层妖毒侵蚀状态穿透20%防20%破</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10079</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>只会受到未消耗妖毒污染的键的招式造成的伤害</t>
-  </si>
-  <si>
-    <t>污覆·乙</t>
-  </si>
-  <si>
-    <t>防+120%破+120%，受击时攻击的敌手每有1层妖毒侵蚀状态穿透20%防20%破</t>
-  </si>
-  <si>
-    <t>污覆·丙</t>
-  </si>
-  <si>
-    <t>污覆·丁</t>
-  </si>
-  <si>
-    <t>毒雾弥漫</t>
-  </si>
-  <si>
-    <t>回合开始时向全部敌手随机施加一种毒向状态</t>
-  </si>
-  <si>
-    <t>玄窍</t>
-  </si>
-  <si>
-    <t>增加玄炁上限5</t>
-  </si>
-  <si>
-    <t>月华玄功</t>
-  </si>
-  <si>
-    <t>增加玄炁上限5减少刚炁上限5</t>
-  </si>
-  <si>
-    <t>蛟血之体</t>
-  </si>
-  <si>
-    <t>玄炁永远不会低于10</t>
-  </si>
-  <si>
-    <t>满欲</t>
-  </si>
-  <si>
-    <t>敌手一次移除了超过4层的妖毒状态或妖毒侵蚀状态则在本回合获得1次行动次数</t>
-  </si>
-  <si>
-    <t>勾牌人</t>
-  </si>
-  <si>
-    <t>存在其余友方角色时每回合首次被破招后获得1次行动次数</t>
-  </si>
-  <si>
-    <t>不遂之躯</t>
-  </si>
-  <si>
-    <t>不存在其余友方角色时进入击破状态</t>
-  </si>
-  <si>
-    <t>登台子午相</t>
-  </si>
-  <si>
-    <t>进入战斗时获得的键从10个随机的键变为不同方向的键各2个，回合开始时获得3个随机的键变为获得4个不同方向的键</t>
-  </si>
-  <si>
-    <t>庄家</t>
-  </si>
-  <si>
-    <t>行动意图揭示，交锋时若威力相同则视为交锋胜利</t>
-  </si>
-  <si>
-    <t>捕醉仙</t>
-  </si>
-  <si>
-    <t>非决定的杀式行动威力增加10</t>
-  </si>
-  <si>
-    <t>异体</t>
-  </si>
-  <si>
-    <t>自身存在的状态无法重复获得，每个回合首次行动减缓0~2息</t>
-  </si>
-  <si>
-    <t>大妖</t>
-  </si>
-  <si>
-    <t>回合开始获得1次行动次数，3个回合内只能被施加1次招式限制类状态且至多1层（6类）</t>
-  </si>
-  <si>
-    <t>抓千</t>
-  </si>
-  <si>
-    <t>在场角色的宝器都不会生效，行动所在息外敌手使用招式获得炁、键或是使用道具则对其施加2层残缺状态</t>
-  </si>
-  <si>
-    <t>处于未行动的息时防+30%破+30%</t>
-  </si>
-  <si>
-    <t>每回合首次行动次数耗尽后获得1层回避状态</t>
-  </si>
-  <si>
-    <t>无垢之体</t>
-  </si>
-  <si>
-    <t>回合结束时清除全部增益状态和异常状态</t>
-  </si>
-  <si>
-    <t>烈阳经</t>
-  </si>
-  <si>
-    <t>增加刚炁上限5</t>
-  </si>
-  <si>
-    <t>阳满待盈</t>
-  </si>
-  <si>
-    <t>使用招式直接恢复体时额外恢复5%技的体</t>
-  </si>
-  <si>
-    <t>阴满待凝</t>
-  </si>
-  <si>
-    <t>回合开始时玄炁至少100则获得1次行动次数</t>
-  </si>
-  <si>
-    <t>键为0时立即获得1个随机的键</t>
-  </si>
-  <si>
-    <t>脚底抹油</t>
-  </si>
-  <si>
-    <t>键的上限变为5。消耗键后消耗全部的键然后补充到上限。累计获得15个键后在本回合获得1次行动次数。</t>
-  </si>
-  <si>
-    <t>交锋胜利随机获得1个随机的键</t>
-  </si>
-  <si>
-    <t>体低于一半时回合开始额外获得1个随机的键</t>
-  </si>
-  <si>
-    <t>毅定风波</t>
-  </si>
-  <si>
-    <t>每回合首次受到直接攻击的伤害后获得1个随机的键</t>
-  </si>
-  <si>
-    <t>战斗中首次键为0时补充随机的键到达持有上限</t>
-  </si>
-  <si>
-    <t>驻位机关造物</t>
-  </si>
-  <si>
-    <t>回合开始，消耗刚炁与玄炁中最高的一项0.5%：1补充随机的键到达持有上限。刚炁与玄炁皆为0时直接进入击破状态。无法自然恢复炁。</t>
-  </si>
-  <si>
-    <t>强攻防护机关</t>
-  </si>
-  <si>
-    <t>豁免每回合首次受到的威力大于100的杀式直接伤害</t>
-  </si>
-  <si>
-    <t>自衍式机关造物</t>
-  </si>
-  <si>
-    <t>每息刚炁+3，玄炁+3，获得1个随机的键。</t>
-  </si>
-  <si>
-    <t>动炁感知</t>
-  </si>
-  <si>
-    <t>行动次数为0则在其余角色使用招式后获得1次行动次数，1回合至多触发1次。</t>
-  </si>
-  <si>
-    <t>机关造物</t>
-  </si>
-  <si>
-    <t>刚炁与玄炁皆为0时直接进入击破状态。无法自然恢复炁。</t>
-  </si>
-  <si>
-    <t>杀机无相</t>
-  </si>
-  <si>
-    <t>未成为敌手行动目标时不会暴露行动所在息与意图</t>
-  </si>
-  <si>
-    <t>力破万法</t>
-  </si>
-  <si>
-    <t>以武杀式交锋时也不会被实际伤害低于自身的招式破招</t>
-  </si>
-  <si>
-    <t>水骨不折</t>
-  </si>
-  <si>
-    <t>受到武杀式攻击后防+30%直到下次行动</t>
-  </si>
-  <si>
-    <t>载面</t>
-  </si>
-  <si>
-    <t>战斗开始获得戴面状态，每个回合首次获得戴面状态后在本回合获得1次行动次数</t>
-  </si>
-  <si>
-    <t>体低于一半时兽化身层数不会低于4层</t>
-  </si>
-  <si>
-    <t>累计经过4个回合后禽化身层数不会低于4层</t>
-  </si>
-  <si>
-    <t>累计有2人被击破时鬼化身层数不会低于4层</t>
-  </si>
-  <si>
-    <t>兽化身状态下不会被施加力衰、武衰状态</t>
-  </si>
-  <si>
-    <t>祖化身状态下不会被施加缓速、失衡状态</t>
-  </si>
-  <si>
-    <t>沉重吐息</t>
-  </si>
-  <si>
-    <t>行动后恢复10%刚炁</t>
-  </si>
-  <si>
-    <t>饱餍</t>
-  </si>
-  <si>
-    <t>每有一个角色被击破时恢复20%体并获得3层武增状态和3层力增状态</t>
-  </si>
-  <si>
-    <t>摆踱乘势</t>
-  </si>
-  <si>
-    <t>交锋成功/失败后获得一项增益状态（力增、武增、反击、迅速、巧增），效果每回合切换</t>
-  </si>
-  <si>
-    <t>跮踱乘势</t>
-  </si>
-  <si>
-    <t>交锋成功/失败后获得一项增益状态（力增、武增、反击、迅速、巧增），每次行动后切换</t>
-  </si>
-  <si>
-    <t>收到单方面攻击后增加10+RG*1力</t>
-  </si>
-  <si>
-    <t>抢占先机</t>
-  </si>
-  <si>
-    <t>首次自然恢复刚炁时额外恢复10</t>
-  </si>
-  <si>
-    <t>未雨绸缪</t>
-  </si>
-  <si>
-    <t>首次自然恢复玄炁时额外恢复10</t>
-  </si>
-  <si>
-    <t>中瘴者</t>
-  </si>
-  <si>
-    <t>回合开始获得1层毒瘴状态，若毒瘴状态层数不少于5则还会获得一次行动次数，释放法咒式与杀式后对目标施加1层毒瘴状态，释放技御式后获得1层毒瘴状态</t>
-  </si>
-  <si>
-    <t>侵蚀</t>
-  </si>
-  <si>
-    <t>带有瘴毒的角色被击破时恢复100+RG*10体，每层增加10%</t>
-  </si>
-  <si>
-    <t>刺激肉体</t>
-  </si>
-  <si>
-    <t>每获得1层毒瘴状态后随机获得1个键并恢复10刚炁10玄炁</t>
-  </si>
-  <si>
-    <t>雨割</t>
-  </si>
-  <si>
-    <t>雨天时受到招式的直接伤害变为等量的体上限扣除，以杀式造成直接伤害时也会扣除目标等量的体上限</t>
-  </si>
-  <si>
-    <t>金城铁壁</t>
-  </si>
-  <si>
-    <t>回合开始获得1层岳环状态</t>
-  </si>
-  <si>
-    <t>战斗开始获得1层岳环状态，回合开始若回合数为5则获得1层岳环状态</t>
-  </si>
-  <si>
-    <t>每回合首次术杀式释放成功后若刚炁大于50则在下一息向目标释放玄炁消耗最低的术杀式并清空刚炁，</t>
-  </si>
-  <si>
-    <t>福鸿</t>
-  </si>
-  <si>
-    <t>战斗开始时获得1层藏身状态和1层隐魂状态</t>
-  </si>
-  <si>
-    <t>命中行动已揭示的敌手获得随机增益（迅速/力增/技增/术增/武增/巧增）或一个随机的键或者5刚炁或者5玄炁</t>
-  </si>
-  <si>
-    <t>每累计损失x（20%面板基础）体时在本回合获得1次行动次数</t>
-  </si>
-  <si>
-    <t>若本回合已行动，受到杀式攻击时距离上一次行动所在息超过2息则受到的伤害越低（从相隔三息开始0.9的次方）</t>
-  </si>
-  <si>
-    <t>北帝先玄</t>
-  </si>
-  <si>
-    <t>刚炁可以作为玄炁使用</t>
-  </si>
-  <si>
-    <t>引电甲</t>
-  </si>
-  <si>
-    <t>受到攻击后若行动次数为0则对攻击者造成%术的伤害（距离上一次行动所在息越远则伤害越高，至多在5息到达2.5倍）</t>
-  </si>
-  <si>
-    <t>回合内行过1次加快至少1息的行动，则在下次受到攻击时获得1层反击状态。该效果每次触发的条件将在触发后增加1息，反之若进行过不满足加快程度的行动则减少1息（雾天减少2息）</t>
-  </si>
-  <si>
-    <t>交锋失败时若存在猊煞变状态，则消耗1层抵免破招效果</t>
-  </si>
-  <si>
-    <t>刚炁消耗减少不会低于3，回合开始时切换为玄炁消耗减少</t>
-  </si>
-  <si>
-    <t>昂膀</t>
-  </si>
-  <si>
-    <t>受到攻击后在本回合增加15+GR*1.5力</t>
-  </si>
-  <si>
-    <t>水生之道</t>
-  </si>
-  <si>
-    <t>受到武杀式攻击后下个回合开始获得1层迅速状态</t>
-  </si>
-  <si>
-    <t>梦为自如真</t>
-  </si>
-  <si>
-    <t>累计进行5次非决定的行动后获得3层武增3层术增状态，清除醉气状态获得等量迅速状态层数，并在下一息向随机敌手使用武杀式：惊鸿</t>
-  </si>
-  <si>
-    <t>酒痴</t>
-  </si>
-  <si>
-    <t>战斗外若存在酒类增益状态，战斗开始获得3层醉气状态并使酒类增益状态效果加倍。</t>
-  </si>
-  <si>
-    <t>武师职能</t>
-  </si>
-  <si>
-    <t>术士职能</t>
-  </si>
-  <si>
-    <t>玄炁越多，炁拶类术杀式伤害越高（30~100+，伤害1~2倍）</t>
-  </si>
-  <si>
-    <t>铁卫职能</t>
-  </si>
-  <si>
-    <t>承受行动目标的杀式攻击或杀式命中以自身为目标的敌手增加1层交鸣，杀式与杀式交锋则额外增加1层交鸣</t>
-  </si>
-  <si>
-    <t>影候职能</t>
-  </si>
-  <si>
-    <t>刚炁恢复额外增加10，玄炁不会自然恢复</t>
-  </si>
-  <si>
-    <t>艺者职能</t>
-  </si>
-  <si>
-    <t>玄炁恢复额外增加10，刚炁不会自然恢复</t>
-  </si>
-  <si>
-    <t>卸功拆招·丁</t>
-  </si>
-  <si>
-    <t>每个杀式交锋过1次对其增加承受该招式时破+50%防+50%的效果，至多2层。</t>
-  </si>
-  <si>
-    <t>卸功拆招·丙</t>
-  </si>
-  <si>
-    <t>每个杀式承受过1次对其增加承受该招式时破+30%防+30%的效果，至多2层。</t>
-  </si>
-  <si>
-    <t>卸功拆招·乙</t>
-  </si>
-  <si>
-    <t>每个杀式交锋或承受过1次对其增加承受该招式时破+20%防+20%的效果，至多4层。</t>
-  </si>
-  <si>
-    <t>卸功拆招·甲</t>
-  </si>
-  <si>
-    <t>破+50%防+50%</t>
-  </si>
-  <si>
-    <t>常时架势·御守</t>
-  </si>
-  <si>
-    <t>行动结束获得御守架势状态</t>
-  </si>
-  <si>
-    <t>妙术三手</t>
-  </si>
-  <si>
-    <t>每个回合首次使用物品后在本回合获得1次行动次数</t>
-  </si>
-  <si>
-    <t>以战养战</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10091</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10011</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>击破敌人获得1次行动次数并且玄炁+25、刚炁+25</t>
-  </si>
-  <si>
-    <t>日反暂明</t>
-  </si>
-  <si>
-    <t>回合开始时若体低于一半在本回合获得1次行动次数</t>
-  </si>
-  <si>
-    <t>鏖军百炼</t>
-  </si>
-  <si>
-    <t>回合开始时若回合超过4则在本回合获得1次行动次数</t>
-  </si>
-  <si>
-    <t>一气如雷</t>
-  </si>
-  <si>
-    <t>回合开始时若回合不超过3则在本回合获得1次行动次数</t>
-  </si>
-  <si>
-    <t>无往蹈锋</t>
-  </si>
-  <si>
-    <t>回合结束时若本回合有角色被击破过则在下回合获得1次行动次数</t>
-  </si>
-  <si>
-    <t>入武·巧劲</t>
-  </si>
-  <si>
-    <t>每回合首次释放武杀式加成提高5的百分比</t>
-  </si>
-  <si>
-    <t>入武·巧功</t>
-  </si>
-  <si>
-    <t>每回合首次释放武杀式加成提高10的百分比</t>
-  </si>
-  <si>
-    <t>入术·巧法</t>
-  </si>
-  <si>
-    <t>每回合首次释放术杀式加成提高5的百分比</t>
-  </si>
-  <si>
-    <t>入术·巧咒</t>
-  </si>
-  <si>
-    <t>每回合首次释放术杀式加成提高10的百分比</t>
-  </si>
-  <si>
-    <t>入武·下级</t>
-  </si>
-  <si>
-    <t>武杀式加成提高5的百分比</t>
-  </si>
-  <si>
-    <t>入武·上级</t>
-  </si>
-  <si>
-    <t>武杀式加成提高10的百分比</t>
-  </si>
-  <si>
-    <t>入术·下级</t>
-  </si>
-  <si>
-    <t>术杀式加成提高5的百分比</t>
-  </si>
-  <si>
-    <t>入术·上级</t>
-  </si>
-  <si>
-    <t>术杀式加成提高10的百分比</t>
-  </si>
-  <si>
-    <t>徐疾百踪</t>
-  </si>
-  <si>
-    <t>回合开始时获得1层迅速或缓速，速额外增加x（20+0.66*GR）</t>
-  </si>
-  <si>
-    <t>千招</t>
-  </si>
-  <si>
-    <t>累加三次不同式的行动使下一次行动的杀式威力提高10的百分比</t>
-  </si>
-  <si>
-    <t>百式</t>
-  </si>
-  <si>
-    <t>全部招式携带的技巧点占用减少1</t>
-  </si>
-  <si>
-    <t>武宗</t>
-  </si>
-  <si>
-    <t>武杀式的技巧点占用减少1，刚炁消耗减少2</t>
-  </si>
-  <si>
-    <t>术宗</t>
-  </si>
-  <si>
-    <t>术杀式的技巧点占用减少1，玄炁消耗减少2</t>
-  </si>
-  <si>
-    <t>入武·炁炼</t>
-  </si>
-  <si>
-    <t>行动决定后若刚炁超过50获得1~2层武增</t>
-  </si>
-  <si>
-    <t>入术·炁炼</t>
-  </si>
-  <si>
-    <t>行动决定后若玄炁超过50获得1~2层术增</t>
-  </si>
-  <si>
-    <t>翱涟</t>
-  </si>
-  <si>
-    <t>每有1层交鸣，武杀式加成提高5的百分比</t>
-  </si>
-  <si>
-    <t>遁形</t>
-  </si>
-  <si>
-    <t>即将受到使体低于30%的伤害时防+200%破+200%，触发后从下一回合开始无法再触发</t>
-  </si>
-  <si>
-    <t>碧月藏空</t>
-  </si>
-  <si>
-    <t>胜气·缓息</t>
-  </si>
-  <si>
-    <t>交锋胜利体+x（30+3*GR）</t>
-  </si>
-  <si>
-    <t>胜气·缓势</t>
-  </si>
-  <si>
-    <t>交锋胜利固定增加4刚炁</t>
-  </si>
-  <si>
-    <t>胜气·缓神</t>
-  </si>
-  <si>
-    <t>交锋胜利固定增加4玄炁</t>
-  </si>
-  <si>
-    <t>展锋</t>
-  </si>
-  <si>
-    <t>烙魂</t>
-  </si>
-  <si>
-    <t>术杀式直接伤害额外增加x（30+3*GR）</t>
-  </si>
-  <si>
-    <t>暴虎</t>
-  </si>
-  <si>
-    <t>武杀式直接伤害额外增加10%</t>
-  </si>
-  <si>
-    <t>ParamEx</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(list#sep=,),float</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>额外参数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.3,1,0,1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10009</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.5,0.5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10012</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,25,25</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.5,1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4,1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3,1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.05</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10017</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,20,0.66</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>50,1,2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10032</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.3,2,2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>体低于一半时受到攻击获得1层隐匿</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>30,3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>允许2个药力增益状态的存在</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4,0.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10060</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10,0.33</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10,1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10071</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3,8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>200008</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10083</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>回合开始时向全部敌手施加2层妖毒状态</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5,-5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10090</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10092</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10096</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.3,0.3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10097</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10099</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>单方面攻击后目标未带有力衰状态则施加1层力衰状态</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>回合开始时刚炁至少100则获得1次行动次数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>100,1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10101</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10108</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10104</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3,3,1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.5,4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10121</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4,4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2,4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10123</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>禽化身状态下不会被施加技衰、术衰状态</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10126</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.2,3,3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10127</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10130</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10,0.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>暴躁</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,5,1,1,1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10134</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>100,10,0.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10135</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,10,10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,5,1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10141</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>杀式命中时目标未带有破绽则施加1层</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>第一回合首次行动，武杀式：投掷的伤害与施加的效果双倍</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10146</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>15,1.5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5,3,3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10153</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3,0.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10016</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>刚炁越多，炁拶类武杀式伤害越高（30~100+，伤害1~2倍）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>武杀式直接伤害额外增加x（30+3*GR）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>允许装配相同键的招式，使用时随机释放其一</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10044</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10047</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>与行动的目标交锋成功后随机扣除目标一个键</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>洞爻八象</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>体上限+60%，进入战斗时命扣除70%以上的部分</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10064</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>只会在回合其中一息受到直接伤害，每回合变化</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>只会受到敌手在单个回合连续第4次行动所造成的伤害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>敌手无法通过状态、招式、心法效果获得键</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10105</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>回合开始若有过未所用招式的行动则获得次数等量的迅速</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.5,0.5,2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.3,0.3,2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.2,0.2,4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10038</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10043</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1262,7 +1435,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1272,12 +1445,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1308,7 +1475,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1322,9 +1489,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1665,7 +1829,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>264</v>
+        <v>243</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
@@ -1682,7 +1846,7 @@
         <v>6</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>265</v>
+        <v>244</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
@@ -1699,7 +1863,7 @@
         <v>9</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>266</v>
+        <v>245</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
@@ -1707,13 +1871,13 @@
         <v>10001</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>187</v>
+        <v>167</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>344</v>
+        <v>323</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>267</v>
+        <v>246</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
@@ -1721,13 +1885,13 @@
         <v>10002</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>188</v>
+        <v>168</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>267</v>
+        <v>246</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
@@ -1735,10 +1899,10 @@
         <v>10003</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>191</v>
+        <v>171</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
@@ -1746,13 +1910,13 @@
         <v>10004</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>192</v>
+        <v>172</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>193</v>
+        <v>173</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>268</v>
+        <v>247</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
@@ -1760,13 +1924,13 @@
         <v>10005</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>194</v>
+        <v>174</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>195</v>
+        <v>175</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>268</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
@@ -1774,13 +1938,13 @@
         <v>10006</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>196</v>
+        <v>176</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>197</v>
+        <v>177</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>358</v>
+        <v>337</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
@@ -1788,13 +1952,13 @@
         <v>10007</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>198</v>
+        <v>178</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>199</v>
+        <v>179</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>359</v>
+        <v>338</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
@@ -1802,27 +1966,27 @@
         <v>10008</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>201</v>
+        <v>181</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>360</v>
+        <v>339</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B12" s="1" t="s">
-        <v>269</v>
+        <v>248</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>202</v>
+        <v>182</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>270</v>
+        <v>249</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1830,38 +1994,41 @@
         <v>10010</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>204</v>
+        <v>184</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>205</v>
+        <v>185</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>271</v>
+        <v>250</v>
       </c>
     </row>
     <row r="14" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="2">
-        <v>10011</v>
+      <c r="B14" s="2" t="s">
+        <v>399</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>207</v>
+        <v>187</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B15" s="1" t="s">
-        <v>272</v>
+        <v>251</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>208</v>
+        <v>188</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>209</v>
+        <v>400</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>273</v>
+        <v>252</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
@@ -1869,13 +2036,13 @@
         <v>10013</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>210</v>
+        <v>189</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>211</v>
+        <v>190</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>274</v>
+        <v>253</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.2">
@@ -1883,13 +2050,13 @@
         <v>10014</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>212</v>
+        <v>191</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>213</v>
+        <v>192</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>275</v>
+        <v>254</v>
       </c>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.2">
@@ -1897,41 +2064,41 @@
         <v>10015</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>214</v>
+        <v>193</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>215</v>
+        <v>194</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>276</v>
+        <v>255</v>
       </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
-        <v>343</v>
+        <v>322</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>216</v>
+        <v>195</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>217</v>
+        <v>196</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>271</v>
+        <v>250</v>
       </c>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B20" s="1" t="s">
-        <v>279</v>
+        <v>258</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>218</v>
+        <v>197</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>219</v>
+        <v>198</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>277</v>
+        <v>256</v>
       </c>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.2">
@@ -1939,13 +2106,13 @@
         <v>10018</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>220</v>
+        <v>199</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>221</v>
+        <v>200</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>278</v>
+        <v>257</v>
       </c>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.2">
@@ -1953,13 +2120,13 @@
         <v>10019</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>222</v>
+        <v>201</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>223</v>
+        <v>202</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>277</v>
+        <v>256</v>
       </c>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.2">
@@ -1967,13 +2134,13 @@
         <v>10020</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>224</v>
+        <v>203</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>225</v>
+        <v>204</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>278</v>
+        <v>257</v>
       </c>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.2">
@@ -1981,13 +2148,13 @@
         <v>10021</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>226</v>
+        <v>205</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>227</v>
+        <v>206</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>277</v>
+        <v>256</v>
       </c>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.2">
@@ -1995,13 +2162,13 @@
         <v>10022</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>228</v>
+        <v>207</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>229</v>
+        <v>208</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>278</v>
+        <v>257</v>
       </c>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.2">
@@ -2009,13 +2176,13 @@
         <v>10023</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>230</v>
+        <v>209</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>231</v>
+        <v>210</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>277</v>
+        <v>256</v>
       </c>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.2">
@@ -2023,13 +2190,13 @@
         <v>10024</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>232</v>
+        <v>211</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>233</v>
+        <v>212</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>278</v>
+        <v>257</v>
       </c>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.2">
@@ -2037,27 +2204,27 @@
         <v>10025</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>234</v>
+        <v>213</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>235</v>
+        <v>214</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="29" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="4">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B29" s="3">
         <v>10026</v>
       </c>
-      <c r="C29" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>342</v>
+      <c r="C29" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="30" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2065,10 +2232,10 @@
         <v>10027</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>238</v>
+        <v>217</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>239</v>
+        <v>218</v>
       </c>
     </row>
     <row r="31" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2076,13 +2243,13 @@
         <v>10028</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>240</v>
+        <v>219</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>241</v>
+        <v>220</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>281</v>
+        <v>260</v>
       </c>
     </row>
     <row r="32" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2090,13 +2257,13 @@
         <v>10029</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>242</v>
+        <v>221</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>243</v>
+        <v>222</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>281</v>
+        <v>260</v>
       </c>
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.2">
@@ -2104,13 +2271,13 @@
         <v>10030</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>244</v>
+        <v>223</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>245</v>
+        <v>224</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>282</v>
+        <v>261</v>
       </c>
     </row>
     <row r="34" spans="2:5" x14ac:dyDescent="0.2">
@@ -2118,41 +2285,41 @@
         <v>10031</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>246</v>
+        <v>225</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>247</v>
+        <v>226</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>282</v>
+        <v>261</v>
       </c>
     </row>
     <row r="35" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B35" s="1" t="s">
-        <v>283</v>
+        <v>262</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>248</v>
+        <v>227</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>249</v>
+        <v>228</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="36" spans="2:5" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B36" s="3">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="36" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B36" s="1">
         <v>10033</v>
       </c>
-      <c r="C36" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>284</v>
+      <c r="C36" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="37" spans="2:5" x14ac:dyDescent="0.2">
@@ -2160,13 +2327,13 @@
         <v>10034</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>252</v>
+        <v>231</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>285</v>
+        <v>264</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>274</v>
+        <v>253</v>
       </c>
     </row>
     <row r="38" spans="2:5" x14ac:dyDescent="0.2">
@@ -2174,13 +2341,13 @@
         <v>10035</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>253</v>
+        <v>232</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>254</v>
+        <v>233</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>286</v>
+        <v>265</v>
       </c>
     </row>
     <row r="39" spans="2:5" x14ac:dyDescent="0.2">
@@ -2188,13 +2355,13 @@
         <v>10036</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>255</v>
+        <v>234</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>256</v>
+        <v>235</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>287</v>
+        <v>266</v>
       </c>
     </row>
     <row r="40" spans="2:5" x14ac:dyDescent="0.2">
@@ -2202,27 +2369,27 @@
         <v>10037</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>257</v>
+        <v>236</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>258</v>
+        <v>237</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>287</v>
+        <v>266</v>
       </c>
     </row>
     <row r="41" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B41" s="1" t="s">
-        <v>361</v>
+        <v>340</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>259</v>
+        <v>238</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>345</v>
+        <v>324</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>286</v>
+        <v>265</v>
       </c>
     </row>
     <row r="42" spans="2:5" x14ac:dyDescent="0.2">
@@ -2230,13 +2397,13 @@
         <v>10039</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>260</v>
+        <v>239</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>261</v>
+        <v>240</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>286</v>
+        <v>265</v>
       </c>
     </row>
     <row r="43" spans="2:5" x14ac:dyDescent="0.2">
@@ -2244,13 +2411,13 @@
         <v>10040</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>262</v>
+        <v>241</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>263</v>
+        <v>242</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>278</v>
+        <v>257</v>
       </c>
     </row>
     <row r="44" spans="2:5" x14ac:dyDescent="0.2">
@@ -2264,7 +2431,7 @@
         <v>11</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>278</v>
+        <v>257</v>
       </c>
     </row>
     <row r="45" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2280,27 +2447,27 @@
     </row>
     <row r="46" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B46" s="1" t="s">
-        <v>362</v>
+        <v>341</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>288</v>
+        <v>267</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>271</v>
+        <v>250</v>
       </c>
     </row>
     <row r="47" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B47" s="1" t="s">
-        <v>347</v>
+        <v>326</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>289</v>
+        <v>268</v>
       </c>
     </row>
     <row r="48" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2311,7 +2478,7 @@
         <v>16</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>346</v>
+        <v>325</v>
       </c>
     </row>
     <row r="49" spans="2:5" x14ac:dyDescent="0.2">
@@ -2325,29 +2492,32 @@
         <v>18</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="50" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B50" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="C50" s="2" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="50" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B50" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="C50" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D50" s="2" t="s">
+      <c r="D50" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E50" s="2" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="51" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B51" s="2">
+      <c r="E50" s="1" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="51" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B51" s="1">
         <v>10048</v>
       </c>
-      <c r="D51" s="2" t="s">
-        <v>349</v>
+      <c r="D51" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="52" spans="2:5" x14ac:dyDescent="0.2">
@@ -2358,7 +2528,7 @@
         <v>21</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>271</v>
+        <v>250</v>
       </c>
     </row>
     <row r="53" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2366,7 +2536,7 @@
         <v>10050</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>350</v>
+        <v>329</v>
       </c>
     </row>
     <row r="54" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2413,29 +2583,35 @@
         <v>29</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="58" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B58" s="2">
-        <v>10055</v>
-      </c>
-      <c r="C58" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="58" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B58" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="C58" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D58" s="2" t="s">
+      <c r="D58" s="1" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="59" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="2">
-        <v>10056</v>
-      </c>
-      <c r="C59" s="2" t="s">
+      <c r="E58" s="1" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="59" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B59" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="C59" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D59" s="2" t="s">
-        <v>351</v>
+      <c r="D59" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="60" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2457,25 +2633,25 @@
         <v>35</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="62" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B62" s="4">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="62" spans="2:5" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B62" s="3">
         <v>10059</v>
       </c>
-      <c r="D62" s="4" t="s">
+      <c r="D62" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="63" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B63" s="4" t="s">
-        <v>291</v>
-      </c>
-      <c r="C63" s="4" t="s">
+    <row r="63" spans="2:5" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B63" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="C63" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D63" s="4" t="s">
+      <c r="D63" s="3" t="s">
         <v>38</v>
       </c>
     </row>
@@ -2487,7 +2663,7 @@
         <v>39</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>292</v>
+        <v>271</v>
       </c>
     </row>
     <row r="65" spans="2:5" x14ac:dyDescent="0.2">
@@ -2501,58 +2677,64 @@
         <v>41</v>
       </c>
     </row>
-    <row r="66" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B66" s="5">
+    <row r="66" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B66" s="1">
         <v>10063</v>
       </c>
-      <c r="C66" s="5" t="s">
+      <c r="C66" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D66" s="5" t="s">
+      <c r="D66" s="1" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="67" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B67" s="5" t="s">
-        <v>352</v>
-      </c>
-      <c r="D67" s="5" t="s">
+      <c r="E66" s="1" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="67" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B67" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="D67" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E67" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="68" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B68" s="5">
-        <v>10065</v>
-      </c>
-      <c r="C68" s="5" t="s">
+      <c r="E67" s="1" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="68" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B68" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="C68" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D68" s="5" t="s">
+      <c r="D68" s="1" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="69" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B69" s="5">
+      <c r="E68" s="1" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="69" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B69" s="4">
         <v>10066</v>
       </c>
-      <c r="C69" s="5" t="s">
+      <c r="C69" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D69" s="5" t="s">
+      <c r="D69" s="4" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="70" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B70" s="5">
-        <v>10067</v>
-      </c>
-      <c r="C70" s="5" t="s">
+    <row r="70" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B70" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="C70" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D70" s="5" t="s">
+      <c r="D70" s="1" t="s">
         <v>50</v>
       </c>
     </row>
@@ -2567,7 +2749,7 @@
         <v>52</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>294</v>
+        <v>273</v>
       </c>
     </row>
     <row r="72" spans="2:5" x14ac:dyDescent="0.2">
@@ -2581,7 +2763,7 @@
         <v>54</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>289</v>
+        <v>268</v>
       </c>
     </row>
     <row r="73" spans="2:5" x14ac:dyDescent="0.2">
@@ -2595,12 +2777,12 @@
         <v>56</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>277</v>
+        <v>256</v>
       </c>
     </row>
     <row r="74" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B74" s="1" t="s">
-        <v>296</v>
+        <v>275</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>57</v>
@@ -2609,139 +2791,154 @@
         <v>58</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="75" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B75" s="5">
-        <v>10072</v>
-      </c>
-      <c r="C75" s="5" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="75" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B75" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="C75" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D75" s="5" t="s">
+      <c r="D75" s="1" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="76" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B76" s="5">
-        <v>10073</v>
-      </c>
-      <c r="C76" s="5" t="s">
+      <c r="E75" s="1" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="76" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B76" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="C76" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D76" s="5" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="77" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B77" s="5">
+      <c r="D76" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="77" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B77" s="1">
         <v>10074</v>
       </c>
-      <c r="C77" s="5" t="s">
+      <c r="C77" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D77" s="5" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="78" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B78" s="5">
-        <v>10075</v>
-      </c>
-      <c r="C78" s="5" t="s">
+      <c r="D77" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="78" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B78" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="79" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B79" s="1">
+        <v>10076</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="80" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B80" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="C80" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D78" s="5" t="s">
+      <c r="D80" s="1" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="81" spans="2:5" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B81" s="3">
+        <v>10078</v>
+      </c>
+      <c r="C81" s="3" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="79" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B79" s="5">
-        <v>10076</v>
-      </c>
-      <c r="C79" s="5" t="s">
+      <c r="D81" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="82" spans="2:5" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B82" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="C82" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D79" s="5" t="s">
+      <c r="D82" s="3" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="83" spans="2:5" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B83" s="3">
+        <v>10080</v>
+      </c>
+      <c r="C83" s="3" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="80" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B80" s="5">
-        <v>10077</v>
-      </c>
-      <c r="C80" s="5" t="s">
+      <c r="D83" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="84" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B84" s="4">
+        <v>10081</v>
+      </c>
+      <c r="C84" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="D80" s="5" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="81" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B81" s="4">
-        <v>10078</v>
-      </c>
-      <c r="C81" s="4" t="s">
+    </row>
+    <row r="85" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B85" s="4">
+        <v>10082</v>
+      </c>
+      <c r="C85" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="D81" s="4" t="s">
-        <v>300</v>
-      </c>
-      <c r="E81" s="4" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="82" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B82" s="5">
-        <v>10079</v>
-      </c>
-      <c r="C82" s="5" t="s">
+    </row>
+    <row r="86" spans="2:5" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B86" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="C86" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D82" s="5" t="s">
+      <c r="D86" s="3" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="83" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B83" s="5">
-        <v>10080</v>
-      </c>
-      <c r="C83" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D83" s="5" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="84" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B84" s="5">
-        <v>10081</v>
-      </c>
-      <c r="C84" s="5" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="85" spans="2:5" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B85" s="5">
-        <v>10082</v>
-      </c>
-      <c r="C85" s="5" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="86" spans="2:5" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B86" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="C86" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D86" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="E86" s="4" t="s">
-        <v>298</v>
+      <c r="E86" s="3" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="87" spans="2:5" x14ac:dyDescent="0.2">
@@ -2749,13 +2946,13 @@
         <v>10084</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>295</v>
+        <v>274</v>
       </c>
     </row>
     <row r="88" spans="2:5" x14ac:dyDescent="0.2">
@@ -2763,13 +2960,13 @@
         <v>10085</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>302</v>
+        <v>281</v>
       </c>
     </row>
     <row r="89" spans="2:5" x14ac:dyDescent="0.2">
@@ -2777,137 +2974,152 @@
         <v>10086</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="90" spans="2:5" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B90" s="3">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="90" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B90" s="1">
         <v>10087</v>
       </c>
-      <c r="C90" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="D90" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="91" spans="2:5" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B91" s="3">
-        <v>10088</v>
-      </c>
-      <c r="C91" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="D91" s="3" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="92" spans="2:5" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B92" s="3">
-        <v>10089</v>
-      </c>
-      <c r="C92" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D92" s="3" t="s">
-        <v>88</v>
+      <c r="C90" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="91" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B91" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="92" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B92" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="93" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B93" s="1" t="s">
-        <v>303</v>
+        <v>282</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="94" spans="2:5" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B94" s="3">
-        <v>10091</v>
-      </c>
-      <c r="C94" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="D94" s="3" t="s">
-        <v>92</v>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="94" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B94" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="95" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B95" s="1" t="s">
-        <v>304</v>
+        <v>283</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="96" spans="2:5" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B96" s="3">
-        <v>10093</v>
-      </c>
-      <c r="C96" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="D96" s="3" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="97" spans="2:5" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B97" s="3">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="96" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B96" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="97" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B97" s="1">
         <v>10094</v>
       </c>
-      <c r="C97" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="D97" s="3" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="98" spans="2:5" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B98" s="3">
-        <v>10095</v>
-      </c>
-      <c r="C98" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="D98" s="3" t="s">
-        <v>100</v>
+      <c r="C97" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="98" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B98" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="99" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B99" s="1" t="s">
-        <v>305</v>
+        <v>284</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>306</v>
+        <v>285</v>
       </c>
     </row>
     <row r="100" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B100" s="1" t="s">
-        <v>307</v>
+        <v>286</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>271</v>
+        <v>250</v>
       </c>
     </row>
     <row r="101" spans="2:5" x14ac:dyDescent="0.2">
@@ -2915,24 +3127,24 @@
         <v>10098</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
     </row>
     <row r="102" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B102" s="1" t="s">
-        <v>308</v>
+        <v>287</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>295</v>
+        <v>274</v>
       </c>
     </row>
     <row r="103" spans="2:5" x14ac:dyDescent="0.2">
@@ -2940,32 +3152,35 @@
         <v>10100</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>309</v>
+        <v>288</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>271</v>
+        <v>250</v>
       </c>
     </row>
     <row r="104" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B104" s="1" t="s">
-        <v>312</v>
+        <v>291</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>310</v>
+        <v>289</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="105" spans="2:5" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B105" s="3">
-        <v>10102</v>
-      </c>
-      <c r="D105" s="3" t="s">
-        <v>108</v>
+        <v>290</v>
+      </c>
+    </row>
+    <row r="105" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B105" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="106" spans="2:5" x14ac:dyDescent="0.2">
@@ -2973,43 +3188,46 @@
         <v>10103</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>271</v>
+        <v>250</v>
       </c>
     </row>
     <row r="107" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B107" s="1" t="s">
-        <v>314</v>
+        <v>293</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>271</v>
+        <v>250</v>
       </c>
     </row>
     <row r="108" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B108" s="1" t="s">
-        <v>356</v>
+        <v>335</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="109" spans="2:5" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B109" s="3">
-        <v>10106</v>
-      </c>
-      <c r="D109" s="3" t="s">
-        <v>113</v>
+        <v>336</v>
+      </c>
+    </row>
+    <row r="109" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B109" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>382</v>
       </c>
     </row>
     <row r="110" spans="2:5" x14ac:dyDescent="0.2">
@@ -3017,21 +3235,21 @@
         <v>10107</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>271</v>
+        <v>250</v>
       </c>
     </row>
     <row r="111" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B111" s="1" t="s">
-        <v>313</v>
+        <v>292</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>274</v>
+        <v>253</v>
       </c>
     </row>
     <row r="112" spans="2:5" x14ac:dyDescent="0.2">
@@ -3039,13 +3257,13 @@
         <v>10109</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>271</v>
+        <v>250</v>
       </c>
     </row>
     <row r="113" spans="2:5" x14ac:dyDescent="0.2">
@@ -3053,29 +3271,35 @@
         <v>10110</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="114" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B114" s="2">
-        <v>10111</v>
-      </c>
-      <c r="C114" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="D114" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="115" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B115" s="2">
-        <v>10112</v>
-      </c>
-      <c r="C115" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="D115" s="2" t="s">
-        <v>122</v>
+        <v>103</v>
+      </c>
+    </row>
+    <row r="114" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B114" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="115" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B115" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="116" spans="2:5" x14ac:dyDescent="0.2">
@@ -3083,24 +3307,24 @@
         <v>10113</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="117" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B117" s="2">
-        <v>10114</v>
-      </c>
-      <c r="C117" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="D117" s="2" t="s">
-        <v>126</v>
+        <v>294</v>
+      </c>
+    </row>
+    <row r="117" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B117" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="118" spans="2:5" x14ac:dyDescent="0.2">
@@ -3108,10 +3332,10 @@
         <v>10115</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
     </row>
     <row r="119" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3119,21 +3343,21 @@
         <v>10116</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="120" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B120" s="2">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="120" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B120" s="1">
         <v>10117</v>
       </c>
-      <c r="C120" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="D120" s="2" t="s">
-        <v>132</v>
+      <c r="C120" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>373</v>
       </c>
     </row>
     <row r="121" spans="2:5" x14ac:dyDescent="0.2">
@@ -3141,13 +3365,13 @@
         <v>10118</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>289</v>
+        <v>268</v>
       </c>
     </row>
     <row r="122" spans="2:5" x14ac:dyDescent="0.2">
@@ -3155,10 +3379,10 @@
         <v>10119</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
     </row>
     <row r="123" spans="2:5" x14ac:dyDescent="0.2">
@@ -3166,21 +3390,21 @@
         <v>10120</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>316</v>
+        <v>295</v>
       </c>
     </row>
     <row r="124" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B124" s="1" t="s">
-        <v>317</v>
+        <v>296</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>318</v>
+        <v>297</v>
       </c>
     </row>
     <row r="125" spans="2:5" x14ac:dyDescent="0.2">
@@ -3188,18 +3412,18 @@
         <v>10122</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>319</v>
+        <v>298</v>
       </c>
     </row>
     <row r="126" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B126" s="1" t="s">
-        <v>320</v>
+        <v>299</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>140</v>
+        <v>124</v>
       </c>
     </row>
     <row r="127" spans="2:5" x14ac:dyDescent="0.2">
@@ -3207,7 +3431,7 @@
         <v>10124</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>321</v>
+        <v>300</v>
       </c>
     </row>
     <row r="128" spans="2:5" x14ac:dyDescent="0.2">
@@ -3215,71 +3439,77 @@
         <v>10125</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>141</v>
+        <v>125</v>
       </c>
     </row>
     <row r="129" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B129" s="1" t="s">
-        <v>322</v>
+        <v>301</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>143</v>
+        <v>127</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>278</v>
+        <v>257</v>
       </c>
     </row>
     <row r="130" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B130" s="1" t="s">
-        <v>324</v>
+        <v>303</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>145</v>
+        <v>129</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="131" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B131" s="2">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="131" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B131" s="1">
         <v>10128</v>
       </c>
-      <c r="C131" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="D131" s="2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="132" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B132" s="2">
+      <c r="C131" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="E131" s="1" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="132" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B132" s="1">
         <v>10129</v>
       </c>
-      <c r="C132" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="D132" s="2" t="s">
-        <v>149</v>
+      <c r="C132" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E132" s="1" t="s">
+        <v>378</v>
       </c>
     </row>
     <row r="133" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B133" s="1" t="s">
-        <v>325</v>
+        <v>304</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>327</v>
+        <v>306</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>150</v>
+        <v>133</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>326</v>
+        <v>305</v>
       </c>
     </row>
     <row r="134" spans="2:5" x14ac:dyDescent="0.2">
@@ -3287,13 +3517,13 @@
         <v>10131</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>151</v>
+        <v>134</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>152</v>
+        <v>135</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>268</v>
+        <v>247</v>
       </c>
     </row>
     <row r="135" spans="2:5" x14ac:dyDescent="0.2">
@@ -3301,13 +3531,13 @@
         <v>10132</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>153</v>
+        <v>136</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>154</v>
+        <v>137</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>268</v>
+        <v>247</v>
       </c>
     </row>
     <row r="136" spans="2:5" x14ac:dyDescent="0.2">
@@ -3315,52 +3545,52 @@
         <v>10133</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>155</v>
+        <v>138</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>156</v>
+        <v>139</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>328</v>
+        <v>307</v>
       </c>
     </row>
     <row r="137" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B137" s="1" t="s">
-        <v>329</v>
+        <v>308</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>157</v>
+        <v>140</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>330</v>
+        <v>309</v>
       </c>
     </row>
     <row r="138" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B138" s="1" t="s">
-        <v>331</v>
+        <v>310</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>160</v>
+        <v>143</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="139" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B139" s="2">
-        <v>10136</v>
-      </c>
-      <c r="C139" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="D139" s="2" t="s">
-        <v>162</v>
+        <v>311</v>
+      </c>
+    </row>
+    <row r="139" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B139" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="140" spans="2:5" x14ac:dyDescent="0.2">
@@ -3368,13 +3598,13 @@
         <v>10137</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>163</v>
+        <v>146</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>164</v>
+        <v>147</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>271</v>
+        <v>250</v>
       </c>
     </row>
     <row r="141" spans="2:5" x14ac:dyDescent="0.2">
@@ -3382,13 +3612,13 @@
         <v>10138</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>163</v>
+        <v>146</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>165</v>
+        <v>148</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>333</v>
+        <v>312</v>
       </c>
     </row>
     <row r="142" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3396,7 +3626,7 @@
         <v>10139</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
     </row>
     <row r="143" spans="2:5" x14ac:dyDescent="0.2">
@@ -3404,40 +3634,46 @@
         <v>10140</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>167</v>
+        <v>150</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>168</v>
+        <v>151</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>334</v>
+        <v>313</v>
       </c>
     </row>
     <row r="144" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B144" s="1" t="s">
-        <v>335</v>
+        <v>314</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>336</v>
+        <v>315</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="145" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B145" s="2">
-        <v>10142</v>
-      </c>
-      <c r="D145" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="146" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B146" s="2">
-        <v>10143</v>
-      </c>
-      <c r="D146" s="2" t="s">
-        <v>170</v>
+        <v>250</v>
+      </c>
+    </row>
+    <row r="145" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B145" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="D145" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="E145" s="1" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="146" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B146" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="D146" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E146" s="1" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="147" spans="2:5" x14ac:dyDescent="0.2">
@@ -3445,7 +3681,7 @@
         <v>10144</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
     </row>
     <row r="148" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3453,18 +3689,18 @@
         <v>10145</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>337</v>
+        <v>316</v>
       </c>
     </row>
     <row r="149" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B149" s="1" t="s">
-        <v>338</v>
+        <v>317</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>172</v>
+        <v>153</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>173</v>
+        <v>154</v>
       </c>
     </row>
     <row r="150" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3472,10 +3708,10 @@
         <v>10147</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>174</v>
+        <v>155</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>175</v>
+        <v>156</v>
       </c>
     </row>
     <row r="151" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3483,23 +3719,29 @@
         <v>10148</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="152" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B152" s="2">
-        <v>10149</v>
-      </c>
-      <c r="D152" s="2" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="153" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B153" s="2">
-        <v>10150</v>
-      </c>
-      <c r="D153" s="2" t="s">
-        <v>178</v>
+        <v>157</v>
+      </c>
+    </row>
+    <row r="152" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B152" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="D152" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="E152" s="1" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="153" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B153" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="D153" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E153" s="1" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="154" spans="2:5" x14ac:dyDescent="0.2">
@@ -3507,13 +3749,13 @@
         <v>10151</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>339</v>
+        <v>318</v>
       </c>
     </row>
     <row r="155" spans="2:5" x14ac:dyDescent="0.2">
@@ -3521,27 +3763,27 @@
         <v>10152</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>182</v>
+        <v>162</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>271</v>
+        <v>250</v>
       </c>
     </row>
     <row r="156" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B156" s="1" t="s">
-        <v>341</v>
+        <v>320</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>183</v>
+        <v>163</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>184</v>
+        <v>164</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>340</v>
+        <v>319</v>
       </c>
     </row>
     <row r="157" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3549,10 +3791,10 @@
         <v>10154</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>186</v>
+        <v>166</v>
       </c>
     </row>
     <row r="158" spans="2:5" x14ac:dyDescent="0.2">

--- a/Luban/Config/Datas/#HeartMethodConfig.xlsx
+++ b/Luban/Config/Datas/#HeartMethodConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13BD1168-8878-4BC7-9151-C08E37C86B7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EAEB3BF-E0A4-4B76-ABA8-347030A9025D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-1110" yWindow="8850" windowWidth="35565" windowHeight="9315" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="540">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="543">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1831,6 +1831,18 @@
   </si>
   <si>
     <t>10058</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10119</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10147</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.4,5,2.5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4166,8 +4178,8 @@
       </c>
     </row>
     <row r="122" spans="2:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B122" s="2">
-        <v>10119</v>
+      <c r="B122" s="2" t="s">
+        <v>540</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>115</v>
@@ -4579,8 +4591,8 @@
       </c>
     </row>
     <row r="150" spans="2:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B150" s="2">
-        <v>10147</v>
+      <c r="B150" s="2" t="s">
+        <v>541</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>151</v>
@@ -4590,6 +4602,9 @@
       </c>
       <c r="E150" s="2" t="s">
         <v>537</v>
+      </c>
+      <c r="F150" s="2" t="s">
+        <v>542</v>
       </c>
     </row>
     <row r="151" spans="2:6" s="2" customFormat="1" x14ac:dyDescent="0.2">

--- a/Luban/Config/Datas/#HeartMethodConfig.xlsx
+++ b/Luban/Config/Datas/#HeartMethodConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EAEB3BF-E0A4-4B76-ABA8-347030A9025D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75D4F827-D1E8-4311-BD70-443BA7F3365E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="543">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="544">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -176,1673 +176,1683 @@
     <t>先发制人</t>
   </si>
   <si>
+    <t>强键</t>
+  </si>
+  <si>
+    <t>体+x（100+20*GR）</t>
+  </si>
+  <si>
+    <t>法然敷宵</t>
+  </si>
+  <si>
+    <t>敷宵剑状态不会扣除</t>
+  </si>
+  <si>
+    <t>护身剑</t>
+  </si>
+  <si>
+    <t>战斗开始时获得3层敷宵剑</t>
+  </si>
+  <si>
+    <t>傲锋</t>
+  </si>
+  <si>
+    <t>每回合首次行动决定后若为杀式，则本次行动在命中时增加30%伤害</t>
+  </si>
+  <si>
+    <t>锐心</t>
+  </si>
+  <si>
+    <t>与杀式交锋成功后根据二者威力差距5:1固定增加刚炁</t>
+  </si>
+  <si>
+    <t>百折不挠</t>
+  </si>
+  <si>
+    <t>鬼蜮</t>
+  </si>
+  <si>
+    <t>虚无缥缈·甲</t>
+  </si>
+  <si>
+    <t>虚无缥缈·乙</t>
+  </si>
+  <si>
+    <t>失重</t>
+  </si>
+  <si>
+    <t>妖毒</t>
+  </si>
+  <si>
+    <t>污覆·甲</t>
+  </si>
+  <si>
+    <t>污覆·乙</t>
+  </si>
+  <si>
+    <t>污覆·丙</t>
+  </si>
+  <si>
+    <t>污覆·丁</t>
+  </si>
+  <si>
+    <t>毒雾弥漫</t>
+  </si>
+  <si>
+    <t>回合开始时向全部敌手随机施加一种毒向状态</t>
+  </si>
+  <si>
+    <t>玄窍</t>
+  </si>
+  <si>
+    <t>增加玄炁上限5</t>
+  </si>
+  <si>
+    <t>月华玄功</t>
+  </si>
+  <si>
+    <t>增加玄炁上限5减少刚炁上限5</t>
+  </si>
+  <si>
+    <t>蛟血之体</t>
+  </si>
+  <si>
+    <t>玄炁永远不会低于10</t>
+  </si>
+  <si>
+    <t>不存在其余友方角色时进入击破状态</t>
+  </si>
+  <si>
+    <t>登台子午相</t>
+  </si>
+  <si>
+    <t>进入战斗时获得的键从10个随机的键变为不同方向的键各2个，回合开始时获得3个随机的键变为获得4个不同方向的键</t>
+  </si>
+  <si>
+    <t>庄家</t>
+  </si>
+  <si>
+    <t>捕醉仙</t>
+  </si>
+  <si>
+    <t>非决定的杀式行动威力增加10</t>
+  </si>
+  <si>
+    <t>异体</t>
+  </si>
+  <si>
+    <t>自身存在的状态无法重复获得，每个回合首次行动减缓0~2息</t>
+  </si>
+  <si>
+    <t>大妖</t>
+  </si>
+  <si>
+    <t>回合开始获得1次行动次数，3个回合内只能被施加1次招式限制类状态且至多1层（6类）</t>
+  </si>
+  <si>
+    <t>抓千</t>
+  </si>
+  <si>
+    <t>处于未行动的息时防+30%破+30%</t>
+  </si>
+  <si>
+    <t>每回合首次行动次数耗尽后获得1层回避状态</t>
+  </si>
+  <si>
+    <t>无垢之体</t>
+  </si>
+  <si>
+    <t>回合结束时清除全部增益状态和异常状态</t>
+  </si>
+  <si>
+    <t>烈阳经</t>
+  </si>
+  <si>
+    <t>增加刚炁上限5</t>
+  </si>
+  <si>
+    <t>阳满待盈</t>
+  </si>
+  <si>
+    <t>阴满待凝</t>
+  </si>
+  <si>
+    <t>回合开始时玄炁至少100则获得1次行动次数</t>
+  </si>
+  <si>
+    <t>键为0时立即获得1个随机的键</t>
+  </si>
+  <si>
+    <t>脚底抹油</t>
+  </si>
+  <si>
+    <t>交锋胜利随机获得1个随机的键</t>
+  </si>
+  <si>
+    <t>体低于一半时回合开始额外获得1个随机的键</t>
+  </si>
+  <si>
+    <t>毅定风波</t>
+  </si>
+  <si>
+    <t>每回合首次受到直接攻击的伤害后获得1个随机的键</t>
+  </si>
+  <si>
+    <t>驻位机关造物</t>
+  </si>
+  <si>
+    <t>回合开始，消耗刚炁与玄炁中最高的一项0.5%：1补充随机的键到达持有上限。刚炁与玄炁皆为0时直接进入击破状态。无法自然恢复炁。</t>
+  </si>
+  <si>
+    <t>强攻防护机关</t>
+  </si>
+  <si>
+    <t>豁免每回合首次受到的威力大于100的杀式直接伤害</t>
+  </si>
+  <si>
+    <t>自衍式机关造物</t>
+  </si>
+  <si>
+    <t>动炁感知</t>
+  </si>
+  <si>
+    <t>行动次数为0则在其余角色使用招式后获得1次行动次数，1回合至多触发1次。</t>
+  </si>
+  <si>
+    <t>机关造物</t>
+  </si>
+  <si>
+    <t>刚炁与玄炁皆为0时直接进入击破状态。无法自然恢复炁。</t>
+  </si>
+  <si>
+    <t>杀机无相</t>
+  </si>
+  <si>
+    <t>未成为敌手行动目标时不会暴露行动所在息与意图</t>
+  </si>
+  <si>
+    <t>力破万法</t>
+  </si>
+  <si>
+    <t>水骨不折</t>
+  </si>
+  <si>
+    <t>受到武杀式攻击后防+30%直到下次行动</t>
+  </si>
+  <si>
+    <t>载面</t>
+  </si>
+  <si>
+    <t>战斗开始获得戴面状态，每个回合首次获得戴面状态后在本回合获得1次行动次数</t>
+  </si>
+  <si>
+    <t>体低于一半时兽化身层数不会低于4层</t>
+  </si>
+  <si>
+    <t>累计经过4个回合后禽化身层数不会低于4层</t>
+  </si>
+  <si>
+    <t>累计有2人被击破时鬼化身层数不会低于4层</t>
+  </si>
+  <si>
+    <t>兽化身状态下不会被施加力衰、武衰状态</t>
+  </si>
+  <si>
+    <t>祖化身状态下不会被施加缓速、失衡状态</t>
+  </si>
+  <si>
+    <t>沉重吐息</t>
+  </si>
+  <si>
+    <t>行动后恢复10%刚炁</t>
+  </si>
+  <si>
+    <t>饱餍</t>
+  </si>
+  <si>
+    <t>每有一个角色被击破时恢复20%体并获得3层武增状态和3层力增状态</t>
+  </si>
+  <si>
+    <t>摆踱乘势</t>
+  </si>
+  <si>
+    <t>跮踱乘势</t>
+  </si>
+  <si>
+    <t>交锋成功/失败后获得一项增益状态（力增、武增、反击、迅速、巧增），每次行动后切换</t>
+  </si>
+  <si>
+    <t>收到单方面攻击后增加10+RG*1力</t>
+  </si>
+  <si>
+    <t>抢占先机</t>
+  </si>
+  <si>
+    <t>首次自然恢复刚炁时额外恢复10</t>
+  </si>
+  <si>
+    <t>未雨绸缪</t>
+  </si>
+  <si>
+    <t>首次自然恢复玄炁时额外恢复10</t>
+  </si>
+  <si>
+    <t>中瘴者</t>
+  </si>
+  <si>
+    <t>回合开始获得1层毒瘴状态，若毒瘴状态层数不少于5则还会获得一次行动次数，释放法咒式与杀式后对目标施加1层毒瘴状态，释放技御式后获得1层毒瘴状态</t>
+  </si>
+  <si>
+    <t>侵蚀</t>
+  </si>
+  <si>
+    <t>带有瘴毒的角色被击破时恢复100+RG*10体，每层增加10%</t>
+  </si>
+  <si>
+    <t>刺激肉体</t>
+  </si>
+  <si>
+    <t>雨割</t>
+  </si>
+  <si>
+    <t>雨天时受到招式的直接伤害变为等量的体上限扣除，以杀式造成直接伤害时也会扣除目标等量的体上限</t>
+  </si>
+  <si>
+    <t>金城铁壁</t>
+  </si>
+  <si>
+    <t>回合开始获得1层岳环状态</t>
+  </si>
+  <si>
+    <t>战斗开始获得1层岳环状态，回合开始若回合数为5则获得1层岳环状态</t>
+  </si>
+  <si>
+    <t>每回合首次术杀式释放成功后若刚炁大于50则在下一息向目标释放玄炁消耗最低的术杀式并清空刚炁，</t>
+  </si>
+  <si>
+    <t>福鸿</t>
+  </si>
+  <si>
+    <t>战斗开始时获得1层藏身状态和1层隐魂状态</t>
+  </si>
+  <si>
+    <t>若本回合已行动，受到杀式攻击时距离上一次行动所在息超过2息则受到的伤害越低（从相隔三息开始0.9的次方）</t>
+  </si>
+  <si>
+    <t>北帝先玄</t>
+  </si>
+  <si>
+    <t>刚炁可以作为玄炁使用</t>
+  </si>
+  <si>
+    <t>引电甲</t>
+  </si>
+  <si>
+    <t>受到攻击后若行动次数为0则对攻击者造成%术的伤害（距离上一次行动所在息越远则伤害越高，至多在5息到达2.5倍）</t>
+  </si>
+  <si>
+    <t>回合内行过1次加快至少1息的行动，则在下次受到攻击时获得1层反击状态。该效果每次触发的条件将在触发后增加1息，反之若进行过不满足加快程度的行动则减少1息（雾天减少2息）</t>
+  </si>
+  <si>
+    <t>刚炁消耗减少不会低于3，回合开始时切换为玄炁消耗减少</t>
+  </si>
+  <si>
+    <t>昂膀</t>
+  </si>
+  <si>
+    <t>受到攻击后在本回合增加15+GR*1.5力</t>
+  </si>
+  <si>
+    <t>水生之道</t>
+  </si>
+  <si>
+    <t>受到武杀式攻击后下个回合开始获得1层迅速状态</t>
+  </si>
+  <si>
+    <t>梦为自如真</t>
+  </si>
+  <si>
+    <t>累计进行5次非决定的行动后获得3层武增3层术增状态，清除醉气状态获得等量迅速状态层数，并在下一息向随机敌手使用武杀式：惊鸿</t>
+  </si>
+  <si>
+    <t>酒痴</t>
+  </si>
+  <si>
+    <t>战斗外若存在酒类增益状态，战斗开始获得3层醉气状态并使酒类增益状态效果加倍。</t>
+  </si>
+  <si>
+    <t>武师职能</t>
+  </si>
+  <si>
+    <t>术士职能</t>
+  </si>
+  <si>
+    <t>玄炁越多，炁拶类术杀式伤害越高（30~100+，伤害1~2倍）</t>
+  </si>
+  <si>
+    <t>铁卫职能</t>
+  </si>
+  <si>
+    <t>承受行动目标的杀式攻击或杀式命中以自身为目标的敌手增加1层交鸣，杀式与杀式交锋则额外增加1层交鸣</t>
+  </si>
+  <si>
+    <t>影候职能</t>
+  </si>
+  <si>
+    <t>刚炁恢复额外增加10，玄炁不会自然恢复</t>
+  </si>
+  <si>
+    <t>艺者职能</t>
+  </si>
+  <si>
+    <t>玄炁恢复额外增加10，刚炁不会自然恢复</t>
+  </si>
+  <si>
+    <t>卸功拆招·丁</t>
+  </si>
+  <si>
+    <t>每个杀式交锋过1次对其增加承受该招式时破+50%防+50%的效果，至多2层。</t>
+  </si>
+  <si>
+    <t>卸功拆招·丙</t>
+  </si>
+  <si>
+    <t>每个杀式承受过1次对其增加承受该招式时破+30%防+30%的效果，至多2层。</t>
+  </si>
+  <si>
+    <t>卸功拆招·乙</t>
+  </si>
+  <si>
+    <t>每个杀式交锋或承受过1次对其增加承受该招式时破+20%防+20%的效果，至多4层。</t>
+  </si>
+  <si>
+    <t>卸功拆招·甲</t>
+  </si>
+  <si>
+    <t>破+50%防+50%</t>
+  </si>
+  <si>
+    <t>常时架势·御守</t>
+  </si>
+  <si>
+    <t>行动结束获得御守架势状态</t>
+  </si>
+  <si>
+    <t>妙术三手</t>
+  </si>
+  <si>
+    <t>以战养战</t>
+  </si>
+  <si>
+    <t>日反暂明</t>
+  </si>
+  <si>
+    <t>回合开始时若体低于一半在本回合获得1次行动次数</t>
+  </si>
+  <si>
+    <t>鏖军百炼</t>
+  </si>
+  <si>
+    <t>回合开始时若回合超过4则在本回合获得1次行动次数</t>
+  </si>
+  <si>
+    <t>一气如雷</t>
+  </si>
+  <si>
+    <t>回合开始时若回合不超过3则在本回合获得1次行动次数</t>
+  </si>
+  <si>
+    <t>无往蹈锋</t>
+  </si>
+  <si>
+    <t>入武·巧劲</t>
+  </si>
+  <si>
+    <t>每回合首次释放武杀式加成提高5的百分比</t>
+  </si>
+  <si>
+    <t>入武·巧功</t>
+  </si>
+  <si>
+    <t>每回合首次释放武杀式加成提高10的百分比</t>
+  </si>
+  <si>
+    <t>入术·巧法</t>
+  </si>
+  <si>
+    <t>每回合首次释放术杀式加成提高5的百分比</t>
+  </si>
+  <si>
+    <t>入术·巧咒</t>
+  </si>
+  <si>
+    <t>每回合首次释放术杀式加成提高10的百分比</t>
+  </si>
+  <si>
+    <t>入武·下级</t>
+  </si>
+  <si>
+    <t>武杀式加成提高5的百分比</t>
+  </si>
+  <si>
+    <t>入武·上级</t>
+  </si>
+  <si>
+    <t>武杀式加成提高10的百分比</t>
+  </si>
+  <si>
+    <t>入术·下级</t>
+  </si>
+  <si>
+    <t>术杀式加成提高5的百分比</t>
+  </si>
+  <si>
+    <t>入术·上级</t>
+  </si>
+  <si>
+    <t>术杀式加成提高10的百分比</t>
+  </si>
+  <si>
+    <t>徐疾百踪</t>
+  </si>
+  <si>
+    <t>回合开始时获得1层迅速或缓速，速额外增加x（20+0.66*GR）</t>
+  </si>
+  <si>
+    <t>千招</t>
+  </si>
+  <si>
+    <t>累加三次不同式的行动使下一次行动的杀式威力提高10的百分比</t>
+  </si>
+  <si>
+    <t>百式</t>
+  </si>
+  <si>
+    <t>全部招式携带的技巧点占用减少1</t>
+  </si>
+  <si>
+    <t>武宗</t>
+  </si>
+  <si>
+    <t>武杀式的技巧点占用减少1，刚炁消耗减少2</t>
+  </si>
+  <si>
+    <t>术宗</t>
+  </si>
+  <si>
+    <t>术杀式的技巧点占用减少1，玄炁消耗减少2</t>
+  </si>
+  <si>
+    <t>入武·炁炼</t>
+  </si>
+  <si>
+    <t>行动决定后若刚炁超过50获得1~2层武增</t>
+  </si>
+  <si>
+    <t>入术·炁炼</t>
+  </si>
+  <si>
+    <t>行动决定后若玄炁超过50获得1~2层术增</t>
+  </si>
+  <si>
+    <t>翱涟</t>
+  </si>
+  <si>
+    <t>每有1层交鸣，武杀式加成提高5的百分比</t>
+  </si>
+  <si>
+    <t>遁形</t>
+  </si>
+  <si>
+    <t>即将受到使体低于30%的伤害时防+200%破+200%，触发后从下一回合开始无法再触发</t>
+  </si>
+  <si>
+    <t>碧月藏空</t>
+  </si>
+  <si>
+    <t>胜气·缓息</t>
+  </si>
+  <si>
+    <t>交锋胜利体+x（30+3*GR）</t>
+  </si>
+  <si>
+    <t>胜气·缓势</t>
+  </si>
+  <si>
+    <t>交锋胜利固定增加4刚炁</t>
+  </si>
+  <si>
+    <t>胜气·缓神</t>
+  </si>
+  <si>
+    <t>交锋胜利固定增加4玄炁</t>
+  </si>
+  <si>
+    <t>展锋</t>
+  </si>
+  <si>
+    <t>烙魂</t>
+  </si>
+  <si>
+    <t>术杀式直接伤害额外增加x（30+3*GR）</t>
+  </si>
+  <si>
+    <t>暴虎</t>
+  </si>
+  <si>
+    <t>武杀式直接伤害额外增加10%</t>
+  </si>
+  <si>
+    <t>ParamEx</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(list#sep=,),float</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>额外参数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.3,1,0,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10009</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.5,0.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10012</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,25,25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.5,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.05</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10017</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,20,0.66</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>50,1,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10032</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.3,2,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>体低于一半时受到攻击获得1层隐匿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>30,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>允许2个药力增益状态的存在</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4,0.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10060</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10,0.33</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10071</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3,8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>200008</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10083</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回合开始时向全部敌手施加2层妖毒状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5,-5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10090</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10092</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10096</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.3,0.3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10097</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10099</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>单方面攻击后目标未带有力衰状态则施加1层力衰状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回合开始时刚炁至少100则获得1次行动次数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10101</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10108</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10104</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3,3,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.5,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10121</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10123</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>禽化身状态下不会被施加技衰、术衰状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10126</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.2,3,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10127</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10130</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10,0.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴躁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,5,1,1,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10134</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100,10,0.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10135</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,10,10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,5,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10141</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>杀式命中时目标未带有破绽则施加1层</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第一回合首次行动，武杀式：投掷的伤害与施加的效果双倍</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10146</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15,1.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5,3,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10153</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3,0.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10016</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刚炁越多，炁拶类武杀式伤害越高（30~100+，伤害1~2倍）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武杀式直接伤害额外增加x（30+3*GR）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>允许装配相同键的招式，使用时随机释放其一</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10044</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10047</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>与行动的目标交锋成功后随机扣除目标一个键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>洞爻八象</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>体上限+60%，进入战斗时命扣除70%以上的部分</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10064</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>只会在回合其中一息受到直接伤害，每回合变化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>只会受到敌手在单个回合连续第4次行动所造成的伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>敌手无法通过状态、招式、心法效果获得键</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10105</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回合开始若有过未所用招式的行动则获得次数等量的迅速</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.5,0.5,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.3,0.3,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.2,0.2,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10038</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10043</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1001,0.15,0.15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10055</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10056</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.6,0.7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10065</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10077</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10067</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>敌手一次移除了超过4层的妖毒状态或妖毒侵蚀状态则在本回合获得1次行动次数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>满欲</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-4,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不遂之躯</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10089</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-2,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10093</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10088</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>勾牌人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>存在其余友方角色时每回合首次被破招后获得1次行动次数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>行动意图揭示，交锋时若威力相同则视为交锋胜利</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,3,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10102</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用招式直接恢复体时额外恢复5%技的体</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10111</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.005</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10112</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10114</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10150</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>交锋失败时若存在猊煞变状态，则消耗1层抵免破招效果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10142</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>命中行动已揭示的敌手获得随机增益（迅速/力增/技增/术增/武增/巧增）或一个随机的键或者5刚炁或者5玄炁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>200009,1,5,5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10143</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>以武杀式交锋时也不会被实际伤害低于自身的招式破招</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.2,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每累计损失x（20%面板基础）体时在本回合获得1次行动次数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10149</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>交锋成功/失败后获得一项增益状态（力增、武增、反击、迅速、巧增），效果每回合切换</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>200010</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在场角色的宝器都不会生效，行动所在息外敌手使用招式获得炁、键或是使用道具则对其施加2层残缺状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10095</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10106</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5,15,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>键的上限变为5。消耗键后消耗全部的键然后补充到上限。累计获得15个键后在本回合获得1次行动次数。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10136</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10073</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10072</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>虚无缥缈·丙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10075</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,2,0.2,0.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>防+200%破+200%，受到攻击后各减少20%至回合结束</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>虚无缥缈·丁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不会受到武杀式/术杀式的直接伤害，每回合变化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.2,1.2,0.2,0.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>防+120%破+120%，受击时攻击的敌手每有1层妖毒侵蚀状态穿透20%防20%破</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10079</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>只会受到未消耗妖毒污染的键的招式造成的伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10091</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10011</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>击破敌人获得1次行动次数并且玄炁+25、刚炁+25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>战斗中首次键为0时补充随机的键到达持有上限</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10116</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每个回合首次使用物品后在本回合获得1次行动次数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10053</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Script</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Desc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>脚本</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HeartMethod10001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HeartMethod10002</t>
+  </si>
+  <si>
+    <t>HeartMethod10003</t>
+  </si>
+  <si>
+    <t>HeartMethod10004</t>
+  </si>
+  <si>
+    <t>HeartMethod10005</t>
+  </si>
+  <si>
+    <t>HeartMethod10006</t>
+  </si>
+  <si>
+    <t>HeartMethod10007</t>
+  </si>
+  <si>
+    <t>HeartMethod10008</t>
+  </si>
+  <si>
+    <t>HeartMethod10009</t>
+  </si>
+  <si>
+    <t>HeartMethod10010</t>
+  </si>
+  <si>
+    <t>HeartMethod10011</t>
+  </si>
+  <si>
+    <t>HeartMethod10012</t>
+  </si>
+  <si>
+    <t>HeartMethod10013</t>
+  </si>
+  <si>
+    <t>HeartMethod10014</t>
+  </si>
+  <si>
+    <t>HeartMethod10015</t>
+  </si>
+  <si>
+    <t>HeartMethod10016</t>
+  </si>
+  <si>
+    <t>HeartMethod10017</t>
+  </si>
+  <si>
+    <t>HeartMethod10018</t>
+  </si>
+  <si>
+    <t>HeartMethod10019</t>
+  </si>
+  <si>
+    <t>HeartMethod10020</t>
+  </si>
+  <si>
+    <t>HeartMethod10021</t>
+  </si>
+  <si>
+    <t>HeartMethod10022</t>
+  </si>
+  <si>
+    <t>HeartMethod10023</t>
+  </si>
+  <si>
+    <t>HeartMethod10024</t>
+  </si>
+  <si>
+    <t>HeartMethod10025</t>
+  </si>
+  <si>
+    <t>HeartMethod10026</t>
+  </si>
+  <si>
+    <t>HeartMethod10028</t>
+  </si>
+  <si>
+    <t>HeartMethod10029</t>
+  </si>
+  <si>
+    <t>HeartMethod10030</t>
+  </si>
+  <si>
+    <t>HeartMethod10031</t>
+  </si>
+  <si>
+    <t>HeartMethod10032</t>
+  </si>
+  <si>
+    <t>HeartMethod10033</t>
+  </si>
+  <si>
+    <t>HeartMethod10034</t>
+  </si>
+  <si>
+    <t>HeartMethod10035</t>
+  </si>
+  <si>
+    <t>HeartMethod10036</t>
+  </si>
+  <si>
+    <t>HeartMethod10037</t>
+  </si>
+  <si>
+    <t>HeartMethod10038</t>
+  </si>
+  <si>
+    <t>HeartMethod10039</t>
+  </si>
+  <si>
+    <t>HeartMethod10040</t>
+  </si>
+  <si>
+    <t>HeartMethod10041</t>
+  </si>
+  <si>
+    <t>HeartMethod10043</t>
+  </si>
+  <si>
+    <t>HeartMethod10044</t>
+  </si>
+  <si>
+    <t>HeartMethod10046</t>
+  </si>
+  <si>
+    <t>HeartMethod10047</t>
+  </si>
+  <si>
+    <t>HeartMethod10048</t>
+  </si>
+  <si>
+    <t>HeartMethod10049</t>
+  </si>
+  <si>
+    <t>HeartMethod10054</t>
+  </si>
+  <si>
+    <t>HeartMethod10055</t>
+  </si>
+  <si>
+    <t>HeartMethod10056</t>
+  </si>
+  <si>
+    <t>HeartMethod10058</t>
+  </si>
+  <si>
+    <t>HeartMethod10059</t>
+  </si>
+  <si>
+    <t>HeartMethod10060</t>
+  </si>
+  <si>
+    <t>HeartMethod10061</t>
+  </si>
+  <si>
+    <t>HeartMethod10062</t>
+  </si>
+  <si>
+    <t>HeartMethod10063</t>
+  </si>
+  <si>
+    <t>HeartMethod10064</t>
+  </si>
+  <si>
+    <t>HeartMethod10068</t>
+  </si>
+  <si>
+    <t>HeartMethod10069</t>
+  </si>
+  <si>
+    <t>HeartMethod10070</t>
+  </si>
+  <si>
+    <t>HeartMethod10071</t>
+  </si>
+  <si>
+    <t>HeartMethod10072</t>
+  </si>
+  <si>
+    <t>HeartMethod10073</t>
+  </si>
+  <si>
+    <t>HeartMethod10074</t>
+  </si>
+  <si>
+    <t>HeartMethod10075</t>
+  </si>
+  <si>
+    <t>HeartMethod10076</t>
+  </si>
+  <si>
+    <t>HeartMethod10077</t>
+  </si>
+  <si>
+    <t>HeartMethod10078</t>
+  </si>
+  <si>
+    <t>HeartMethod10079</t>
+  </si>
+  <si>
+    <t>HeartMethod10080</t>
+  </si>
+  <si>
+    <t>HeartMethod10083</t>
+  </si>
+  <si>
+    <t>HeartMethod10084</t>
+  </si>
+  <si>
+    <t>HeartMethod10085</t>
+  </si>
+  <si>
+    <t>HeartMethod10086</t>
+  </si>
+  <si>
+    <t>HeartMethod10087</t>
+  </si>
+  <si>
+    <t>HeartMethod10088</t>
+  </si>
+  <si>
+    <t>HeartMethod10089</t>
+  </si>
+  <si>
+    <t>HeartMethod10090</t>
+  </si>
+  <si>
+    <t>HeartMethod10091</t>
+  </si>
+  <si>
+    <t>HeartMethod10092</t>
+  </si>
+  <si>
+    <t>HeartMethod10093</t>
+  </si>
+  <si>
+    <t>HeartMethod10094</t>
+  </si>
+  <si>
+    <t>HeartMethod10095</t>
+  </si>
+  <si>
+    <t>HeartMethod10096</t>
+  </si>
+  <si>
+    <t>HeartMethod10097</t>
+  </si>
+  <si>
+    <t>HeartMethod10098</t>
+  </si>
+  <si>
+    <t>HeartMethod10099</t>
+  </si>
+  <si>
+    <t>HeartMethod10100</t>
+  </si>
+  <si>
+    <t>HeartMethod10101</t>
+  </si>
+  <si>
+    <t>HeartMethod10102</t>
+  </si>
+  <si>
+    <t>HeartMethod10103</t>
+  </si>
+  <si>
+    <t>HeartMethod10104</t>
+  </si>
+  <si>
+    <t>HeartMethod10105</t>
+  </si>
+  <si>
+    <t>HeartMethod10106</t>
+  </si>
+  <si>
+    <t>HeartMethod10107</t>
+  </si>
+  <si>
+    <t>HeartMethod10108</t>
+  </si>
+  <si>
+    <t>HeartMethod10109</t>
+  </si>
+  <si>
+    <t>HeartMethod10110</t>
+  </si>
+  <si>
+    <t>HeartMethod10111</t>
+  </si>
+  <si>
+    <t>HeartMethod10112</t>
+  </si>
+  <si>
+    <t>HeartMethod10113</t>
+  </si>
+  <si>
+    <t>HeartMethod10114</t>
+  </si>
+  <si>
+    <t>HeartMethod10115</t>
+  </si>
+  <si>
+    <t>HeartMethod10117</t>
+  </si>
+  <si>
+    <t>HeartMethod10118</t>
+  </si>
+  <si>
+    <t>HeartMethod10120</t>
+  </si>
+  <si>
+    <t>HeartMethod10121</t>
+  </si>
+  <si>
+    <t>HeartMethod10122</t>
+  </si>
+  <si>
+    <t>HeartMethod10123</t>
+  </si>
+  <si>
+    <t>HeartMethod10124</t>
+  </si>
+  <si>
+    <t>HeartMethod10125</t>
+  </si>
+  <si>
+    <t>HeartMethod10126</t>
+  </si>
+  <si>
+    <t>HeartMethod10127</t>
+  </si>
+  <si>
+    <t>HeartMethod10128</t>
+  </si>
+  <si>
+    <t>HeartMethod10129</t>
+  </si>
+  <si>
+    <t>HeartMethod10130</t>
+  </si>
+  <si>
+    <t>HeartMethod10131</t>
+  </si>
+  <si>
+    <t>HeartMethod10132</t>
+  </si>
+  <si>
+    <t>HeartMethod10133</t>
+  </si>
+  <si>
+    <t>HeartMethod10134</t>
+  </si>
+  <si>
+    <t>HeartMethod10135</t>
+  </si>
+  <si>
+    <t>HeartMethod10137</t>
+  </si>
+  <si>
+    <t>HeartMethod10138</t>
+  </si>
+  <si>
+    <t>HeartMethod10140</t>
+  </si>
+  <si>
+    <t>HeartMethod10141</t>
+  </si>
+  <si>
+    <t>HeartMethod10142</t>
+  </si>
+  <si>
+    <t>HeartMethod10143</t>
+  </si>
+  <si>
+    <t>HeartMethod10146</t>
+  </si>
+  <si>
+    <t>HeartMethod10149</t>
+  </si>
+  <si>
+    <t>HeartMethod10150</t>
+  </si>
+  <si>
+    <t>HeartMethod10151</t>
+  </si>
+  <si>
+    <t>HeartMethod10152</t>
+  </si>
+  <si>
+    <t>HeartMethod10153</t>
+  </si>
+  <si>
+    <t>HeartMethodBase</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>交锋失败后下次刚炁或玄炁恢复额外增加3~8，该效果不可叠加</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10058</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10119</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10147</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.4,5,2.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回合结束时若本回合有角色被击破过则在下回合获得1次行动次数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HeartMethod10065</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>预先行动阶段决定的行动至少会加快1息</t>
-  </si>
-  <si>
-    <t>强键</t>
-  </si>
-  <si>
-    <t>体+x（100+20*GR）</t>
-  </si>
-  <si>
-    <t>法然敷宵</t>
-  </si>
-  <si>
-    <t>敷宵剑状态不会扣除</t>
-  </si>
-  <si>
-    <t>护身剑</t>
-  </si>
-  <si>
-    <t>战斗开始时获得3层敷宵剑</t>
-  </si>
-  <si>
-    <t>傲锋</t>
-  </si>
-  <si>
-    <t>每回合首次行动决定后若为杀式，则本次行动在命中时增加30%伤害</t>
-  </si>
-  <si>
-    <t>锐心</t>
-  </si>
-  <si>
-    <t>与杀式交锋成功后根据二者威力差距5:1固定增加刚炁</t>
-  </si>
-  <si>
-    <t>百折不挠</t>
-  </si>
-  <si>
-    <t>鬼蜮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>每息首个行动的敌手根据其行动的类型及其最后一个键给予对应的留劲状态，在敌手每回合首次获得留劲状态时在本回合获得1次行动次数</t>
-  </si>
-  <si>
-    <t>虚无缥缈·甲</t>
-  </si>
-  <si>
-    <t>虚无缥缈·乙</t>
-  </si>
-  <si>
-    <t>失重</t>
-  </si>
-  <si>
-    <t>妖毒</t>
-  </si>
-  <si>
-    <t>污覆·甲</t>
-  </si>
-  <si>
-    <t>污覆·乙</t>
-  </si>
-  <si>
-    <t>污覆·丙</t>
-  </si>
-  <si>
-    <t>污覆·丁</t>
-  </si>
-  <si>
-    <t>毒雾弥漫</t>
-  </si>
-  <si>
-    <t>回合开始时向全部敌手随机施加一种毒向状态</t>
-  </si>
-  <si>
-    <t>玄窍</t>
-  </si>
-  <si>
-    <t>增加玄炁上限5</t>
-  </si>
-  <si>
-    <t>月华玄功</t>
-  </si>
-  <si>
-    <t>增加玄炁上限5减少刚炁上限5</t>
-  </si>
-  <si>
-    <t>蛟血之体</t>
-  </si>
-  <si>
-    <t>玄炁永远不会低于10</t>
-  </si>
-  <si>
-    <t>不存在其余友方角色时进入击破状态</t>
-  </si>
-  <si>
-    <t>登台子午相</t>
-  </si>
-  <si>
-    <t>进入战斗时获得的键从10个随机的键变为不同方向的键各2个，回合开始时获得3个随机的键变为获得4个不同方向的键</t>
-  </si>
-  <si>
-    <t>庄家</t>
-  </si>
-  <si>
-    <t>捕醉仙</t>
-  </si>
-  <si>
-    <t>非决定的杀式行动威力增加10</t>
-  </si>
-  <si>
-    <t>异体</t>
-  </si>
-  <si>
-    <t>自身存在的状态无法重复获得，每个回合首次行动减缓0~2息</t>
-  </si>
-  <si>
-    <t>大妖</t>
-  </si>
-  <si>
-    <t>回合开始获得1次行动次数，3个回合内只能被施加1次招式限制类状态且至多1层（6类）</t>
-  </si>
-  <si>
-    <t>抓千</t>
-  </si>
-  <si>
-    <t>处于未行动的息时防+30%破+30%</t>
-  </si>
-  <si>
-    <t>每回合首次行动次数耗尽后获得1层回避状态</t>
-  </si>
-  <si>
-    <t>无垢之体</t>
-  </si>
-  <si>
-    <t>回合结束时清除全部增益状态和异常状态</t>
-  </si>
-  <si>
-    <t>烈阳经</t>
-  </si>
-  <si>
-    <t>增加刚炁上限5</t>
-  </si>
-  <si>
-    <t>阳满待盈</t>
-  </si>
-  <si>
-    <t>阴满待凝</t>
-  </si>
-  <si>
-    <t>回合开始时玄炁至少100则获得1次行动次数</t>
-  </si>
-  <si>
-    <t>键为0时立即获得1个随机的键</t>
-  </si>
-  <si>
-    <t>脚底抹油</t>
-  </si>
-  <si>
-    <t>交锋胜利随机获得1个随机的键</t>
-  </si>
-  <si>
-    <t>体低于一半时回合开始额外获得1个随机的键</t>
-  </si>
-  <si>
-    <t>毅定风波</t>
-  </si>
-  <si>
-    <t>每回合首次受到直接攻击的伤害后获得1个随机的键</t>
-  </si>
-  <si>
-    <t>驻位机关造物</t>
-  </si>
-  <si>
-    <t>回合开始，消耗刚炁与玄炁中最高的一项0.5%：1补充随机的键到达持有上限。刚炁与玄炁皆为0时直接进入击破状态。无法自然恢复炁。</t>
-  </si>
-  <si>
-    <t>强攻防护机关</t>
-  </si>
-  <si>
-    <t>豁免每回合首次受到的威力大于100的杀式直接伤害</t>
-  </si>
-  <si>
-    <t>自衍式机关造物</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10107</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>每息刚炁+3，玄炁+3，获得1个随机的键。</t>
-  </si>
-  <si>
-    <t>动炁感知</t>
-  </si>
-  <si>
-    <t>行动次数为0则在其余角色使用招式后获得1次行动次数，1回合至多触发1次。</t>
-  </si>
-  <si>
-    <t>机关造物</t>
-  </si>
-  <si>
-    <t>刚炁与玄炁皆为0时直接进入击破状态。无法自然恢复炁。</t>
-  </si>
-  <si>
-    <t>杀机无相</t>
-  </si>
-  <si>
-    <t>未成为敌手行动目标时不会暴露行动所在息与意图</t>
-  </si>
-  <si>
-    <t>力破万法</t>
-  </si>
-  <si>
-    <t>水骨不折</t>
-  </si>
-  <si>
-    <t>受到武杀式攻击后防+30%直到下次行动</t>
-  </si>
-  <si>
-    <t>载面</t>
-  </si>
-  <si>
-    <t>战斗开始获得戴面状态，每个回合首次获得戴面状态后在本回合获得1次行动次数</t>
-  </si>
-  <si>
-    <t>体低于一半时兽化身层数不会低于4层</t>
-  </si>
-  <si>
-    <t>累计经过4个回合后禽化身层数不会低于4层</t>
-  </si>
-  <si>
-    <t>累计有2人被击破时鬼化身层数不会低于4层</t>
-  </si>
-  <si>
-    <t>兽化身状态下不会被施加力衰、武衰状态</t>
-  </si>
-  <si>
-    <t>祖化身状态下不会被施加缓速、失衡状态</t>
-  </si>
-  <si>
-    <t>沉重吐息</t>
-  </si>
-  <si>
-    <t>行动后恢复10%刚炁</t>
-  </si>
-  <si>
-    <t>饱餍</t>
-  </si>
-  <si>
-    <t>每有一个角色被击破时恢复20%体并获得3层武增状态和3层力增状态</t>
-  </si>
-  <si>
-    <t>摆踱乘势</t>
-  </si>
-  <si>
-    <t>跮踱乘势</t>
-  </si>
-  <si>
-    <t>交锋成功/失败后获得一项增益状态（力增、武增、反击、迅速、巧增），每次行动后切换</t>
-  </si>
-  <si>
-    <t>收到单方面攻击后增加10+RG*1力</t>
-  </si>
-  <si>
-    <t>抢占先机</t>
-  </si>
-  <si>
-    <t>首次自然恢复刚炁时额外恢复10</t>
-  </si>
-  <si>
-    <t>未雨绸缪</t>
-  </si>
-  <si>
-    <t>首次自然恢复玄炁时额外恢复10</t>
-  </si>
-  <si>
-    <t>中瘴者</t>
-  </si>
-  <si>
-    <t>回合开始获得1层毒瘴状态，若毒瘴状态层数不少于5则还会获得一次行动次数，释放法咒式与杀式后对目标施加1层毒瘴状态，释放技御式后获得1层毒瘴状态</t>
-  </si>
-  <si>
-    <t>侵蚀</t>
-  </si>
-  <si>
-    <t>带有瘴毒的角色被击破时恢复100+RG*10体，每层增加10%</t>
-  </si>
-  <si>
-    <t>刺激肉体</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>每获得1层毒瘴状态后随机获得1个键并恢复10刚炁10玄炁</t>
-  </si>
-  <si>
-    <t>雨割</t>
-  </si>
-  <si>
-    <t>雨天时受到招式的直接伤害变为等量的体上限扣除，以杀式造成直接伤害时也会扣除目标等量的体上限</t>
-  </si>
-  <si>
-    <t>金城铁壁</t>
-  </si>
-  <si>
-    <t>回合开始获得1层岳环状态</t>
-  </si>
-  <si>
-    <t>战斗开始获得1层岳环状态，回合开始若回合数为5则获得1层岳环状态</t>
-  </si>
-  <si>
-    <t>每回合首次术杀式释放成功后若刚炁大于50则在下一息向目标释放玄炁消耗最低的术杀式并清空刚炁，</t>
-  </si>
-  <si>
-    <t>福鸿</t>
-  </si>
-  <si>
-    <t>战斗开始时获得1层藏身状态和1层隐魂状态</t>
-  </si>
-  <si>
-    <t>若本回合已行动，受到杀式攻击时距离上一次行动所在息超过2息则受到的伤害越低（从相隔三息开始0.9的次方）</t>
-  </si>
-  <si>
-    <t>北帝先玄</t>
-  </si>
-  <si>
-    <t>刚炁可以作为玄炁使用</t>
-  </si>
-  <si>
-    <t>引电甲</t>
-  </si>
-  <si>
-    <t>受到攻击后若行动次数为0则对攻击者造成%术的伤害（距离上一次行动所在息越远则伤害越高，至多在5息到达2.5倍）</t>
-  </si>
-  <si>
-    <t>回合内行过1次加快至少1息的行动，则在下次受到攻击时获得1层反击状态。该效果每次触发的条件将在触发后增加1息，反之若进行过不满足加快程度的行动则减少1息（雾天减少2息）</t>
-  </si>
-  <si>
-    <t>刚炁消耗减少不会低于3，回合开始时切换为玄炁消耗减少</t>
-  </si>
-  <si>
-    <t>昂膀</t>
-  </si>
-  <si>
-    <t>受到攻击后在本回合增加15+GR*1.5力</t>
-  </si>
-  <si>
-    <t>水生之道</t>
-  </si>
-  <si>
-    <t>受到武杀式攻击后下个回合开始获得1层迅速状态</t>
-  </si>
-  <si>
-    <t>梦为自如真</t>
-  </si>
-  <si>
-    <t>累计进行5次非决定的行动后获得3层武增3层术增状态，清除醉气状态获得等量迅速状态层数，并在下一息向随机敌手使用武杀式：惊鸿</t>
-  </si>
-  <si>
-    <t>酒痴</t>
-  </si>
-  <si>
-    <t>战斗外若存在酒类增益状态，战斗开始获得3层醉气状态并使酒类增益状态效果加倍。</t>
-  </si>
-  <si>
-    <t>武师职能</t>
-  </si>
-  <si>
-    <t>术士职能</t>
-  </si>
-  <si>
-    <t>玄炁越多，炁拶类术杀式伤害越高（30~100+，伤害1~2倍）</t>
-  </si>
-  <si>
-    <t>铁卫职能</t>
-  </si>
-  <si>
-    <t>承受行动目标的杀式攻击或杀式命中以自身为目标的敌手增加1层交鸣，杀式与杀式交锋则额外增加1层交鸣</t>
-  </si>
-  <si>
-    <t>影候职能</t>
-  </si>
-  <si>
-    <t>刚炁恢复额外增加10，玄炁不会自然恢复</t>
-  </si>
-  <si>
-    <t>艺者职能</t>
-  </si>
-  <si>
-    <t>玄炁恢复额外增加10，刚炁不会自然恢复</t>
-  </si>
-  <si>
-    <t>卸功拆招·丁</t>
-  </si>
-  <si>
-    <t>每个杀式交锋过1次对其增加承受该招式时破+50%防+50%的效果，至多2层。</t>
-  </si>
-  <si>
-    <t>卸功拆招·丙</t>
-  </si>
-  <si>
-    <t>每个杀式承受过1次对其增加承受该招式时破+30%防+30%的效果，至多2层。</t>
-  </si>
-  <si>
-    <t>卸功拆招·乙</t>
-  </si>
-  <si>
-    <t>每个杀式交锋或承受过1次对其增加承受该招式时破+20%防+20%的效果，至多4层。</t>
-  </si>
-  <si>
-    <t>卸功拆招·甲</t>
-  </si>
-  <si>
-    <t>破+50%防+50%</t>
-  </si>
-  <si>
-    <t>常时架势·御守</t>
-  </si>
-  <si>
-    <t>行动结束获得御守架势状态</t>
-  </si>
-  <si>
-    <t>妙术三手</t>
-  </si>
-  <si>
-    <t>以战养战</t>
-  </si>
-  <si>
-    <t>日反暂明</t>
-  </si>
-  <si>
-    <t>回合开始时若体低于一半在本回合获得1次行动次数</t>
-  </si>
-  <si>
-    <t>鏖军百炼</t>
-  </si>
-  <si>
-    <t>回合开始时若回合超过4则在本回合获得1次行动次数</t>
-  </si>
-  <si>
-    <t>一气如雷</t>
-  </si>
-  <si>
-    <t>回合开始时若回合不超过3则在本回合获得1次行动次数</t>
-  </si>
-  <si>
-    <t>无往蹈锋</t>
-  </si>
-  <si>
-    <t>回合结束时若本回合有角色被击破过则在下回合获得1次行动次数</t>
-  </si>
-  <si>
-    <t>入武·巧劲</t>
-  </si>
-  <si>
-    <t>每回合首次释放武杀式加成提高5的百分比</t>
-  </si>
-  <si>
-    <t>入武·巧功</t>
-  </si>
-  <si>
-    <t>每回合首次释放武杀式加成提高10的百分比</t>
-  </si>
-  <si>
-    <t>入术·巧法</t>
-  </si>
-  <si>
-    <t>每回合首次释放术杀式加成提高5的百分比</t>
-  </si>
-  <si>
-    <t>入术·巧咒</t>
-  </si>
-  <si>
-    <t>每回合首次释放术杀式加成提高10的百分比</t>
-  </si>
-  <si>
-    <t>入武·下级</t>
-  </si>
-  <si>
-    <t>武杀式加成提高5的百分比</t>
-  </si>
-  <si>
-    <t>入武·上级</t>
-  </si>
-  <si>
-    <t>武杀式加成提高10的百分比</t>
-  </si>
-  <si>
-    <t>入术·下级</t>
-  </si>
-  <si>
-    <t>术杀式加成提高5的百分比</t>
-  </si>
-  <si>
-    <t>入术·上级</t>
-  </si>
-  <si>
-    <t>术杀式加成提高10的百分比</t>
-  </si>
-  <si>
-    <t>徐疾百踪</t>
-  </si>
-  <si>
-    <t>回合开始时获得1层迅速或缓速，速额外增加x（20+0.66*GR）</t>
-  </si>
-  <si>
-    <t>千招</t>
-  </si>
-  <si>
-    <t>累加三次不同式的行动使下一次行动的杀式威力提高10的百分比</t>
-  </si>
-  <si>
-    <t>百式</t>
-  </si>
-  <si>
-    <t>全部招式携带的技巧点占用减少1</t>
-  </si>
-  <si>
-    <t>武宗</t>
-  </si>
-  <si>
-    <t>武杀式的技巧点占用减少1，刚炁消耗减少2</t>
-  </si>
-  <si>
-    <t>术宗</t>
-  </si>
-  <si>
-    <t>术杀式的技巧点占用减少1，玄炁消耗减少2</t>
-  </si>
-  <si>
-    <t>入武·炁炼</t>
-  </si>
-  <si>
-    <t>行动决定后若刚炁超过50获得1~2层武增</t>
-  </si>
-  <si>
-    <t>入术·炁炼</t>
-  </si>
-  <si>
-    <t>行动决定后若玄炁超过50获得1~2层术增</t>
-  </si>
-  <si>
-    <t>翱涟</t>
-  </si>
-  <si>
-    <t>每有1层交鸣，武杀式加成提高5的百分比</t>
-  </si>
-  <si>
-    <t>遁形</t>
-  </si>
-  <si>
-    <t>即将受到使体低于30%的伤害时防+200%破+200%，触发后从下一回合开始无法再触发</t>
-  </si>
-  <si>
-    <t>碧月藏空</t>
-  </si>
-  <si>
-    <t>胜气·缓息</t>
-  </si>
-  <si>
-    <t>交锋胜利体+x（30+3*GR）</t>
-  </si>
-  <si>
-    <t>胜气·缓势</t>
-  </si>
-  <si>
-    <t>交锋胜利固定增加4刚炁</t>
-  </si>
-  <si>
-    <t>胜气·缓神</t>
-  </si>
-  <si>
-    <t>交锋胜利固定增加4玄炁</t>
-  </si>
-  <si>
-    <t>展锋</t>
-  </si>
-  <si>
-    <t>烙魂</t>
-  </si>
-  <si>
-    <t>术杀式直接伤害额外增加x（30+3*GR）</t>
-  </si>
-  <si>
-    <t>暴虎</t>
-  </si>
-  <si>
-    <t>武杀式直接伤害额外增加10%</t>
-  </si>
-  <si>
-    <t>ParamEx</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(list#sep=,),float</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>额外参数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.3,1,0,1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10009</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.5,0.5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10012</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,25,25</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.5,1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4,1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3,1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.05</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10017</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,20,0.66</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>50,1,2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10032</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.3,2,2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>体低于一半时受到攻击获得1层隐匿</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>30,3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>允许2个药力增益状态的存在</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4,0.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10060</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10,0.33</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10,1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10071</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3,8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>200008</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10083</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>回合开始时向全部敌手施加2层妖毒状态</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5,-5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10090</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10092</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10096</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.3,0.3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10097</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10099</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>单方面攻击后目标未带有力衰状态则施加1层力衰状态</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>回合开始时刚炁至少100则获得1次行动次数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>100,1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10101</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10108</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10104</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3,3,1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.5,4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10121</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4,4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2,4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10123</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>禽化身状态下不会被施加技衰、术衰状态</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10126</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.2,3,3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10127</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10130</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10,0.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>暴躁</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,5,1,1,1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10134</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>100,10,0.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10135</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,10,10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,5,1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10141</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>杀式命中时目标未带有破绽则施加1层</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>第一回合首次行动，武杀式：投掷的伤害与施加的效果双倍</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10146</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>15,1.5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5,3,3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10153</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3,0.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10016</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>刚炁越多，炁拶类武杀式伤害越高（30~100+，伤害1~2倍）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>武杀式直接伤害额外增加x（30+3*GR）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>允许装配相同键的招式，使用时随机释放其一</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10044</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10047</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>与行动的目标交锋成功后随机扣除目标一个键</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>洞爻八象</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>体上限+60%，进入战斗时命扣除70%以上的部分</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10064</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>只会在回合其中一息受到直接伤害，每回合变化</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>只会受到敌手在单个回合连续第4次行动所造成的伤害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>敌手无法通过状态、招式、心法效果获得键</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10105</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>回合开始若有过未所用招式的行动则获得次数等量的迅速</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.5,0.5,2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.3,0.3,2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.2,0.2,4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10038</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10043</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1001,0.15,0.15</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10055</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10056</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.6,0.7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10065</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10077</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10067</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>敌手一次移除了超过4层的妖毒状态或妖毒侵蚀状态则在本回合获得1次行动次数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>满欲</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>-4,1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>不遂之躯</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10089</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>-2,0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10093</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10088</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>勾牌人</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>存在其余友方角色时每回合首次被破招后获得1次行动次数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>行动意图揭示，交锋时若威力相同则视为交锋胜利</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,3,1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10102</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>使用招式直接恢复体时额外恢复5%技的体</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10111</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.005</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10112</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10114</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10150</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>交锋失败时若存在猊煞变状态，则消耗1层抵免破招效果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10142</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>命中行动已揭示的敌手获得随机增益（迅速/力增/技增/术增/武增/巧增）或一个随机的键或者5刚炁或者5玄炁</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>200009,1,5,5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10143</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>以武杀式交锋时也不会被实际伤害低于自身的招式破招</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.2,1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>每累计损失x（20%面板基础）体时在本回合获得1次行动次数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10149</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>交锋成功/失败后获得一项增益状态（力增、武增、反击、迅速、巧增），效果每回合切换</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>200010</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>在场角色的宝器都不会生效，行动所在息外敌手使用招式获得炁、键或是使用道具则对其施加2层残缺状态</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10095</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10106</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5,15,1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>键的上限变为5。消耗键后消耗全部的键然后补充到上限。累计获得15个键后在本回合获得1次行动次数。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10136</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10073</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10072</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>虚无缥缈·丙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10075</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2,2,0.2,0.2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>防+200%破+200%，受到攻击后各减少20%至回合结束</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>虚无缥缈·丁</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>不会受到武杀式/术杀式的直接伤害，每回合变化</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.2,1.2,0.2,0.2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>防+120%破+120%，受击时攻击的敌手每有1层妖毒侵蚀状态穿透20%防20%破</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10079</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>只会受到未消耗妖毒污染的键的招式造成的伤害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10091</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10011</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>击破敌人获得1次行动次数并且玄炁+25、刚炁+25</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>战斗中首次键为0时补充随机的键到达持有上限</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10116</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>每个回合首次使用物品后在本回合获得1次行动次数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10053</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Script</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Desc</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Name</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>脚本</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>HeartMethod10001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>HeartMethod10002</t>
-  </si>
-  <si>
-    <t>HeartMethod10003</t>
-  </si>
-  <si>
-    <t>HeartMethod10004</t>
-  </si>
-  <si>
-    <t>HeartMethod10005</t>
-  </si>
-  <si>
-    <t>HeartMethod10006</t>
-  </si>
-  <si>
-    <t>HeartMethod10007</t>
-  </si>
-  <si>
-    <t>HeartMethod10008</t>
-  </si>
-  <si>
-    <t>HeartMethod10009</t>
-  </si>
-  <si>
-    <t>HeartMethod10010</t>
-  </si>
-  <si>
-    <t>HeartMethod10011</t>
-  </si>
-  <si>
-    <t>HeartMethod10012</t>
-  </si>
-  <si>
-    <t>HeartMethod10013</t>
-  </si>
-  <si>
-    <t>HeartMethod10014</t>
-  </si>
-  <si>
-    <t>HeartMethod10015</t>
-  </si>
-  <si>
-    <t>HeartMethod10016</t>
-  </si>
-  <si>
-    <t>HeartMethod10017</t>
-  </si>
-  <si>
-    <t>HeartMethod10018</t>
-  </si>
-  <si>
-    <t>HeartMethod10019</t>
-  </si>
-  <si>
-    <t>HeartMethod10020</t>
-  </si>
-  <si>
-    <t>HeartMethod10021</t>
-  </si>
-  <si>
-    <t>HeartMethod10022</t>
-  </si>
-  <si>
-    <t>HeartMethod10023</t>
-  </si>
-  <si>
-    <t>HeartMethod10024</t>
-  </si>
-  <si>
-    <t>HeartMethod10025</t>
-  </si>
-  <si>
-    <t>HeartMethod10026</t>
-  </si>
-  <si>
-    <t>HeartMethod10028</t>
-  </si>
-  <si>
-    <t>HeartMethod10029</t>
-  </si>
-  <si>
-    <t>HeartMethod10030</t>
-  </si>
-  <si>
-    <t>HeartMethod10031</t>
-  </si>
-  <si>
-    <t>HeartMethod10032</t>
-  </si>
-  <si>
-    <t>HeartMethod10033</t>
-  </si>
-  <si>
-    <t>HeartMethod10034</t>
-  </si>
-  <si>
-    <t>HeartMethod10035</t>
-  </si>
-  <si>
-    <t>HeartMethod10036</t>
-  </si>
-  <si>
-    <t>HeartMethod10037</t>
-  </si>
-  <si>
-    <t>HeartMethod10038</t>
-  </si>
-  <si>
-    <t>HeartMethod10039</t>
-  </si>
-  <si>
-    <t>HeartMethod10040</t>
-  </si>
-  <si>
-    <t>HeartMethod10041</t>
-  </si>
-  <si>
-    <t>HeartMethod10043</t>
-  </si>
-  <si>
-    <t>HeartMethod10044</t>
-  </si>
-  <si>
-    <t>HeartMethod10046</t>
-  </si>
-  <si>
-    <t>HeartMethod10047</t>
-  </si>
-  <si>
-    <t>HeartMethod10048</t>
-  </si>
-  <si>
-    <t>HeartMethod10049</t>
-  </si>
-  <si>
-    <t>HeartMethod10054</t>
-  </si>
-  <si>
-    <t>HeartMethod10055</t>
-  </si>
-  <si>
-    <t>HeartMethod10056</t>
-  </si>
-  <si>
-    <t>HeartMethod10058</t>
-  </si>
-  <si>
-    <t>HeartMethod10059</t>
-  </si>
-  <si>
-    <t>HeartMethod10060</t>
-  </si>
-  <si>
-    <t>HeartMethod10061</t>
-  </si>
-  <si>
-    <t>HeartMethod10062</t>
-  </si>
-  <si>
-    <t>HeartMethod10063</t>
-  </si>
-  <si>
-    <t>HeartMethod10064</t>
-  </si>
-  <si>
-    <t>HeartMethod10065</t>
-  </si>
-  <si>
-    <t>HeartMethod10068</t>
-  </si>
-  <si>
-    <t>HeartMethod10069</t>
-  </si>
-  <si>
-    <t>HeartMethod10070</t>
-  </si>
-  <si>
-    <t>HeartMethod10071</t>
-  </si>
-  <si>
-    <t>HeartMethod10072</t>
-  </si>
-  <si>
-    <t>HeartMethod10073</t>
-  </si>
-  <si>
-    <t>HeartMethod10074</t>
-  </si>
-  <si>
-    <t>HeartMethod10075</t>
-  </si>
-  <si>
-    <t>HeartMethod10076</t>
-  </si>
-  <si>
-    <t>HeartMethod10077</t>
-  </si>
-  <si>
-    <t>HeartMethod10078</t>
-  </si>
-  <si>
-    <t>HeartMethod10079</t>
-  </si>
-  <si>
-    <t>HeartMethod10080</t>
-  </si>
-  <si>
-    <t>HeartMethod10083</t>
-  </si>
-  <si>
-    <t>HeartMethod10084</t>
-  </si>
-  <si>
-    <t>HeartMethod10085</t>
-  </si>
-  <si>
-    <t>HeartMethod10086</t>
-  </si>
-  <si>
-    <t>HeartMethod10087</t>
-  </si>
-  <si>
-    <t>HeartMethod10088</t>
-  </si>
-  <si>
-    <t>HeartMethod10089</t>
-  </si>
-  <si>
-    <t>HeartMethod10090</t>
-  </si>
-  <si>
-    <t>HeartMethod10091</t>
-  </si>
-  <si>
-    <t>HeartMethod10092</t>
-  </si>
-  <si>
-    <t>HeartMethod10093</t>
-  </si>
-  <si>
-    <t>HeartMethod10094</t>
-  </si>
-  <si>
-    <t>HeartMethod10095</t>
-  </si>
-  <si>
-    <t>HeartMethod10096</t>
-  </si>
-  <si>
-    <t>HeartMethod10097</t>
-  </si>
-  <si>
-    <t>HeartMethod10098</t>
-  </si>
-  <si>
-    <t>HeartMethod10099</t>
-  </si>
-  <si>
-    <t>HeartMethod10100</t>
-  </si>
-  <si>
-    <t>HeartMethod10101</t>
-  </si>
-  <si>
-    <t>HeartMethod10102</t>
-  </si>
-  <si>
-    <t>HeartMethod10103</t>
-  </si>
-  <si>
-    <t>HeartMethod10104</t>
-  </si>
-  <si>
-    <t>HeartMethod10105</t>
-  </si>
-  <si>
-    <t>HeartMethod10106</t>
-  </si>
-  <si>
-    <t>HeartMethod10107</t>
-  </si>
-  <si>
-    <t>HeartMethod10108</t>
-  </si>
-  <si>
-    <t>HeartMethod10109</t>
-  </si>
-  <si>
-    <t>HeartMethod10110</t>
-  </si>
-  <si>
-    <t>HeartMethod10111</t>
-  </si>
-  <si>
-    <t>HeartMethod10112</t>
-  </si>
-  <si>
-    <t>HeartMethod10113</t>
-  </si>
-  <si>
-    <t>HeartMethod10114</t>
-  </si>
-  <si>
-    <t>HeartMethod10115</t>
-  </si>
-  <si>
-    <t>HeartMethod10117</t>
-  </si>
-  <si>
-    <t>HeartMethod10118</t>
-  </si>
-  <si>
-    <t>HeartMethod10120</t>
-  </si>
-  <si>
-    <t>HeartMethod10121</t>
-  </si>
-  <si>
-    <t>HeartMethod10122</t>
-  </si>
-  <si>
-    <t>HeartMethod10123</t>
-  </si>
-  <si>
-    <t>HeartMethod10124</t>
-  </si>
-  <si>
-    <t>HeartMethod10125</t>
-  </si>
-  <si>
-    <t>HeartMethod10126</t>
-  </si>
-  <si>
-    <t>HeartMethod10127</t>
-  </si>
-  <si>
-    <t>HeartMethod10128</t>
-  </si>
-  <si>
-    <t>HeartMethod10129</t>
-  </si>
-  <si>
-    <t>HeartMethod10130</t>
-  </si>
-  <si>
-    <t>HeartMethod10131</t>
-  </si>
-  <si>
-    <t>HeartMethod10132</t>
-  </si>
-  <si>
-    <t>HeartMethod10133</t>
-  </si>
-  <si>
-    <t>HeartMethod10134</t>
-  </si>
-  <si>
-    <t>HeartMethod10135</t>
-  </si>
-  <si>
-    <t>HeartMethod10137</t>
-  </si>
-  <si>
-    <t>HeartMethod10138</t>
-  </si>
-  <si>
-    <t>HeartMethod10140</t>
-  </si>
-  <si>
-    <t>HeartMethod10141</t>
-  </si>
-  <si>
-    <t>HeartMethod10142</t>
-  </si>
-  <si>
-    <t>HeartMethod10143</t>
-  </si>
-  <si>
-    <t>HeartMethod10146</t>
-  </si>
-  <si>
-    <t>HeartMethod10149</t>
-  </si>
-  <si>
-    <t>HeartMethod10150</t>
-  </si>
-  <si>
-    <t>HeartMethod10151</t>
-  </si>
-  <si>
-    <t>HeartMethod10152</t>
-  </si>
-  <si>
-    <t>HeartMethod10153</t>
-  </si>
-  <si>
-    <t>HeartMethodBase</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>交锋失败后下次刚炁或玄炁恢复额外增加3~8，该效果不可叠加</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10058</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10119</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10147</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.4,5,2.5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2263,16 +2273,16 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -2292,7 +2302,7 @@
         <v>4</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -2309,10 +2319,10 @@
         <v>7</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -2320,16 +2330,16 @@
         <v>10001</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -2337,16 +2347,16 @@
         <v>10002</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -2354,13 +2364,13 @@
         <v>10003</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
@@ -2368,16 +2378,16 @@
         <v>10004</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
@@ -2385,16 +2395,16 @@
         <v>10005</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
@@ -2402,16 +2412,16 @@
         <v>10006</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
@@ -2419,16 +2429,16 @@
         <v>10007</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
@@ -2436,33 +2446,33 @@
         <v>10008</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B12" s="1" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2470,50 +2480,50 @@
         <v>10010</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B15" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
@@ -2521,16 +2531,16 @@
         <v>10013</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.2">
@@ -2538,16 +2548,16 @@
         <v>10014</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.2">
@@ -2555,50 +2565,50 @@
         <v>10015</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>191</v>
+        <v>537</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B20" s="1" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
@@ -2606,16 +2616,16 @@
         <v>10018</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
@@ -2623,16 +2633,16 @@
         <v>10019</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.2">
@@ -2640,16 +2650,16 @@
         <v>10020</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.2">
@@ -2657,16 +2667,16 @@
         <v>10021</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.2">
@@ -2674,16 +2684,16 @@
         <v>10022</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.2">
@@ -2691,16 +2701,16 @@
         <v>10023</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.2">
@@ -2708,16 +2718,16 @@
         <v>10024</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.2">
@@ -2725,16 +2735,16 @@
         <v>10025</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
     </row>
     <row r="29" spans="2:6" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -2742,16 +2752,16 @@
         <v>10026</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
     </row>
     <row r="30" spans="2:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2759,13 +2769,13 @@
         <v>10027</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
     </row>
     <row r="31" spans="2:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2773,16 +2783,16 @@
         <v>10028</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
     </row>
     <row r="32" spans="2:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2790,16 +2800,16 @@
         <v>10029</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.2">
@@ -2807,16 +2817,16 @@
         <v>10030</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.2">
@@ -2824,33 +2834,33 @@
         <v>10031</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B35" s="1" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.2">
@@ -2858,16 +2868,16 @@
         <v>10033</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
@@ -2875,16 +2885,16 @@
         <v>10034</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
@@ -2892,16 +2902,16 @@
         <v>10035</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.2">
@@ -2909,16 +2919,16 @@
         <v>10036</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.2">
@@ -2926,33 +2936,33 @@
         <v>10037</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B41" s="1" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -2960,16 +2970,16 @@
         <v>10039</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
     </row>
     <row r="43" spans="2:6" x14ac:dyDescent="0.2">
@@ -2977,16 +2987,16 @@
         <v>10040</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
     </row>
     <row r="44" spans="2:6" x14ac:dyDescent="0.2">
@@ -3000,10 +3010,10 @@
         <v>9</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
     </row>
     <row r="45" spans="2:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3017,38 +3027,38 @@
         <v>11</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="1" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B47" s="1" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
     </row>
     <row r="48" spans="2:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3059,10 +3069,10 @@
         <v>14</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
     </row>
     <row r="49" spans="2:6" x14ac:dyDescent="0.2">
@@ -3076,15 +3086,15 @@
         <v>16</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>17</v>
@@ -3093,10 +3103,10 @@
         <v>18</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -3104,13 +3114,13 @@
         <v>10048</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
@@ -3121,10 +3131,10 @@
         <v>19</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
     </row>
     <row r="53" spans="2:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3132,10 +3142,10 @@
         <v>10050</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
     </row>
     <row r="54" spans="2:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3149,7 +3159,7 @@
         <v>21</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
     </row>
     <row r="55" spans="2:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3163,12 +3173,12 @@
         <v>23</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B56" s="1" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>24</v>
@@ -3177,7 +3187,7 @@
         <v>25</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.2">
@@ -3191,15 +3201,15 @@
         <v>27</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>28</v>
@@ -3208,27 +3218,27 @@
         <v>29</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
     </row>
     <row r="59" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B59" s="1" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
     </row>
     <row r="60" spans="2:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3239,12 +3249,12 @@
         <v>31</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
     </row>
     <row r="61" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B61" s="1" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>32</v>
@@ -3253,10 +3263,10 @@
         <v>33</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
     </row>
     <row r="62" spans="2:6" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -3267,12 +3277,12 @@
         <v>34</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
     </row>
     <row r="63" spans="2:6" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B63" s="3" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>35</v>
@@ -3281,7 +3291,7 @@
         <v>36</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.2">
@@ -3292,10 +3302,10 @@
         <v>37</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.2">
@@ -3309,7 +3319,7 @@
         <v>39</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.2">
@@ -3323,41 +3333,41 @@
         <v>41</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
     </row>
     <row r="67" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B67" s="1" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>42</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
     </row>
     <row r="68" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B68" s="1" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>44</v>
+        <v>539</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>460</v>
+        <v>538</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
     </row>
     <row r="69" spans="2:6" s="4" customFormat="1" x14ac:dyDescent="0.2">
@@ -3365,27 +3375,27 @@
         <v>10066</v>
       </c>
       <c r="C69" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D69" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D69" s="4" t="s">
-        <v>46</v>
-      </c>
       <c r="E69" s="4" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B70" s="1" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="C70" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D70" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D70" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="E70" s="1" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.2">
@@ -3393,16 +3403,16 @@
         <v>10068</v>
       </c>
       <c r="C71" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D71" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D71" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="E71" s="1" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.2">
@@ -3410,16 +3420,16 @@
         <v>10069</v>
       </c>
       <c r="C72" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D72" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D72" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="E72" s="1" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
     </row>
     <row r="73" spans="2:6" x14ac:dyDescent="0.2">
@@ -3427,67 +3437,67 @@
         <v>10070</v>
       </c>
       <c r="C73" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D73" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D73" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="E73" s="1" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
     </row>
     <row r="74" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B74" s="1" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
     </row>
     <row r="75" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B75" s="1" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>57</v>
+        <v>540</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B76" s="1" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
     </row>
     <row r="77" spans="2:6" x14ac:dyDescent="0.2">
@@ -3495,33 +3505,33 @@
         <v>10074</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
     </row>
     <row r="78" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B78" s="1" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
     </row>
     <row r="79" spans="2:6" x14ac:dyDescent="0.2">
@@ -3529,27 +3539,27 @@
         <v>10076</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B80" s="1" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
     </row>
     <row r="81" spans="2:6" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -3557,30 +3567,30 @@
         <v>10078</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
     </row>
     <row r="82" spans="2:6" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B82" s="3" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
     </row>
     <row r="83" spans="2:6" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -3588,16 +3598,16 @@
         <v>10080</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
     </row>
     <row r="84" spans="2:6" s="4" customFormat="1" x14ac:dyDescent="0.2">
@@ -3605,10 +3615,10 @@
         <v>10081</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
     </row>
     <row r="85" spans="2:6" s="4" customFormat="1" x14ac:dyDescent="0.2">
@@ -3616,27 +3626,27 @@
         <v>10082</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
     </row>
     <row r="86" spans="2:6" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B86" s="3" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
     </row>
     <row r="87" spans="2:6" x14ac:dyDescent="0.2">
@@ -3644,16 +3654,16 @@
         <v>10084</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
     </row>
     <row r="88" spans="2:6" x14ac:dyDescent="0.2">
@@ -3661,16 +3671,16 @@
         <v>10085</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
     </row>
     <row r="89" spans="2:6" x14ac:dyDescent="0.2">
@@ -3678,16 +3688,16 @@
         <v>10086</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
     </row>
     <row r="90" spans="2:6" x14ac:dyDescent="0.2">
@@ -3695,109 +3705,109 @@
         <v>10087</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
     </row>
     <row r="91" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B91" s="1" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
     </row>
     <row r="92" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B92" s="1" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
     </row>
     <row r="93" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B93" s="1" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
     </row>
     <row r="94" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B94" s="1" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
     </row>
     <row r="95" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B95" s="1" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
     </row>
     <row r="96" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B96" s="1" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
     </row>
     <row r="97" spans="2:6" x14ac:dyDescent="0.2">
@@ -3805,61 +3815,61 @@
         <v>10094</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
     </row>
     <row r="98" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B98" s="1" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
     </row>
     <row r="99" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B99" s="1" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
     </row>
     <row r="100" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B100" s="1" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
     </row>
     <row r="101" spans="2:6" x14ac:dyDescent="0.2">
@@ -3867,30 +3877,30 @@
         <v>10098</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
     </row>
     <row r="102" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B102" s="1" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
     </row>
     <row r="103" spans="2:6" x14ac:dyDescent="0.2">
@@ -3898,44 +3908,44 @@
         <v>10100</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
     </row>
     <row r="104" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B104" s="1" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
     </row>
     <row r="105" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B105" s="1" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
     </row>
     <row r="106" spans="2:6" x14ac:dyDescent="0.2">
@@ -3943,86 +3953,86 @@
         <v>10103</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
     </row>
     <row r="107" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B107" s="1" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
     </row>
     <row r="108" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B108" s="1" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
     </row>
     <row r="109" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B109" s="1" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
     </row>
     <row r="110" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B110" s="1">
-        <v>10107</v>
+      <c r="B110" s="1" t="s">
+        <v>541</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
     </row>
     <row r="111" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B111" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
     </row>
     <row r="112" spans="2:6" x14ac:dyDescent="0.2">
@@ -4030,16 +4040,16 @@
         <v>10109</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
     </row>
     <row r="113" spans="2:6" x14ac:dyDescent="0.2">
@@ -4047,44 +4057,44 @@
         <v>10110</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
     </row>
     <row r="114" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B114" s="1" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
     </row>
     <row r="115" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B115" s="1" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
     </row>
     <row r="116" spans="2:6" x14ac:dyDescent="0.2">
@@ -4092,30 +4102,33 @@
         <v>10113</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>105</v>
+        <v>542</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
     </row>
     <row r="117" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B117" s="1" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>505</v>
+        <v>499</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="118" spans="2:6" x14ac:dyDescent="0.2">
@@ -4123,27 +4136,27 @@
         <v>10115</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
     </row>
     <row r="119" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B119" s="1" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
     </row>
     <row r="120" spans="2:6" x14ac:dyDescent="0.2">
@@ -4151,13 +4164,13 @@
         <v>10117</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
     </row>
     <row r="121" spans="2:6" x14ac:dyDescent="0.2">
@@ -4165,30 +4178,30 @@
         <v>10118</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
     </row>
     <row r="122" spans="2:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B122" s="2" t="s">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
     </row>
     <row r="123" spans="2:6" x14ac:dyDescent="0.2">
@@ -4196,27 +4209,27 @@
         <v>10120</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
     </row>
     <row r="124" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B124" s="1" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
     </row>
     <row r="125" spans="2:6" x14ac:dyDescent="0.2">
@@ -4224,24 +4237,24 @@
         <v>10122</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
     </row>
     <row r="126" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B126" s="1" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>512</v>
+        <v>506</v>
       </c>
     </row>
     <row r="127" spans="2:6" x14ac:dyDescent="0.2">
@@ -4249,10 +4262,10 @@
         <v>10124</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>513</v>
+        <v>507</v>
       </c>
     </row>
     <row r="128" spans="2:6" x14ac:dyDescent="0.2">
@@ -4260,44 +4273,44 @@
         <v>10125</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
     </row>
     <row r="129" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B129" s="1" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
     </row>
     <row r="130" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B130" s="1" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
     </row>
     <row r="131" spans="2:6" x14ac:dyDescent="0.2">
@@ -4305,16 +4318,16 @@
         <v>10128</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
     </row>
     <row r="132" spans="2:6" x14ac:dyDescent="0.2">
@@ -4322,33 +4335,33 @@
         <v>10129</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
     </row>
     <row r="133" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B133" s="1" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
     </row>
     <row r="134" spans="2:6" x14ac:dyDescent="0.2">
@@ -4356,16 +4369,16 @@
         <v>10131</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
     </row>
     <row r="135" spans="2:6" x14ac:dyDescent="0.2">
@@ -4373,16 +4386,16 @@
         <v>10132</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
     </row>
     <row r="136" spans="2:6" x14ac:dyDescent="0.2">
@@ -4390,64 +4403,64 @@
         <v>10133</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
     </row>
     <row r="137" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B137" s="1" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
     </row>
     <row r="138" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B138" s="1" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>139</v>
+        <v>543</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
     </row>
     <row r="139" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B139" s="1" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
     </row>
     <row r="140" spans="2:6" x14ac:dyDescent="0.2">
@@ -4455,16 +4468,16 @@
         <v>10137</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
     </row>
     <row r="141" spans="2:6" x14ac:dyDescent="0.2">
@@ -4472,16 +4485,16 @@
         <v>10138</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
     </row>
     <row r="142" spans="2:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -4489,10 +4502,10 @@
         <v>10139</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
     </row>
     <row r="143" spans="2:6" x14ac:dyDescent="0.2">
@@ -4500,58 +4513,58 @@
         <v>10140</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
     </row>
     <row r="144" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B144" s="1" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
     </row>
     <row r="145" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B145" s="1" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
     </row>
     <row r="146" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B146" s="1" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
     </row>
     <row r="147" spans="2:6" x14ac:dyDescent="0.2">
@@ -4559,10 +4572,10 @@
         <v>10144</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
     </row>
     <row r="148" spans="2:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -4570,41 +4583,41 @@
         <v>10145</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
     </row>
     <row r="149" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B149" s="1" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
     </row>
     <row r="150" spans="2:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B150" s="2" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
     </row>
     <row r="151" spans="2:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -4612,38 +4625,38 @@
         <v>10148</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
     </row>
     <row r="152" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B152" s="1" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
     </row>
     <row r="153" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B153" s="1" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
     </row>
     <row r="154" spans="2:6" x14ac:dyDescent="0.2">
@@ -4651,16 +4664,16 @@
         <v>10151</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
     </row>
     <row r="155" spans="2:6" x14ac:dyDescent="0.2">
@@ -4668,33 +4681,33 @@
         <v>10152</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
     </row>
     <row r="156" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B156" s="1" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
     </row>
     <row r="157" spans="2:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -4702,13 +4715,13 @@
         <v>10154</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
     </row>
     <row r="158" spans="2:6" x14ac:dyDescent="0.2">

--- a/Luban/Config/Datas/#HeartMethodConfig.xlsx
+++ b/Luban/Config/Datas/#HeartMethodConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75D4F827-D1E8-4311-BD70-443BA7F3365E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87DCF28E-6CDE-4A1B-9CDD-71F3DBD6758A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Luban/Config/Datas/#HeartMethodConfig.xlsx
+++ b/Luban/Config/Datas/#HeartMethodConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87DCF28E-6CDE-4A1B-9CDD-71F3DBD6758A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{019CD2E0-6749-41D3-B5AA-0FFD2B87EFC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="544">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="543">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1172,10 +1172,6 @@
   </si>
   <si>
     <t>满欲</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>-4,1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2273,13 +2269,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>233</v>
@@ -2319,7 +2315,7 @@
         <v>7</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>235</v>
@@ -2336,7 +2332,7 @@
         <v>313</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>236</v>
@@ -2353,7 +2349,7 @@
         <v>161</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>236</v>
@@ -2370,7 +2366,7 @@
         <v>163</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
@@ -2384,7 +2380,7 @@
         <v>165</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>237</v>
@@ -2401,7 +2397,7 @@
         <v>167</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>237</v>
@@ -2418,7 +2414,7 @@
         <v>169</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>327</v>
@@ -2435,7 +2431,7 @@
         <v>171</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>328</v>
@@ -2452,7 +2448,7 @@
         <v>173</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>329</v>
@@ -2469,7 +2465,7 @@
         <v>175</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>239</v>
@@ -2486,7 +2482,7 @@
         <v>177</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>240</v>
@@ -2494,16 +2490,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>178</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>240</v>
@@ -2517,10 +2513,10 @@
         <v>179</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>242</v>
@@ -2537,7 +2533,7 @@
         <v>181</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>243</v>
@@ -2554,7 +2550,7 @@
         <v>183</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>244</v>
@@ -2571,7 +2567,7 @@
         <v>185</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>245</v>
@@ -2585,10 +2581,10 @@
         <v>186</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>240</v>
@@ -2605,7 +2601,7 @@
         <v>188</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>246</v>
@@ -2622,7 +2618,7 @@
         <v>190</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>247</v>
@@ -2639,7 +2635,7 @@
         <v>192</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>246</v>
@@ -2656,7 +2652,7 @@
         <v>194</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>247</v>
@@ -2673,7 +2669,7 @@
         <v>196</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>246</v>
@@ -2690,7 +2686,7 @@
         <v>198</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>247</v>
@@ -2707,7 +2703,7 @@
         <v>200</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>246</v>
@@ -2724,7 +2720,7 @@
         <v>202</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>247</v>
@@ -2741,7 +2737,7 @@
         <v>204</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>249</v>
@@ -2758,7 +2754,7 @@
         <v>206</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>311</v>
@@ -2775,7 +2771,7 @@
         <v>208</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="31" spans="2:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -2789,7 +2785,7 @@
         <v>210</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>250</v>
@@ -2806,7 +2802,7 @@
         <v>212</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>250</v>
@@ -2823,7 +2819,7 @@
         <v>214</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>251</v>
@@ -2840,7 +2836,7 @@
         <v>216</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>251</v>
@@ -2857,7 +2853,7 @@
         <v>218</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>246</v>
@@ -2874,7 +2870,7 @@
         <v>220</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>253</v>
@@ -2891,7 +2887,7 @@
         <v>254</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>243</v>
@@ -2908,7 +2904,7 @@
         <v>223</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>255</v>
@@ -2925,7 +2921,7 @@
         <v>225</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>256</v>
@@ -2942,7 +2938,7 @@
         <v>227</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>256</v>
@@ -2959,7 +2955,7 @@
         <v>314</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>255</v>
@@ -2976,7 +2972,7 @@
         <v>230</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>255</v>
@@ -2993,7 +2989,7 @@
         <v>232</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>247</v>
@@ -3010,7 +3006,7 @@
         <v>9</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>247</v>
@@ -3027,7 +3023,7 @@
         <v>11</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
@@ -3041,7 +3037,7 @@
         <v>257</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>240</v>
@@ -3055,7 +3051,7 @@
         <v>13</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>258</v>
@@ -3072,7 +3068,7 @@
         <v>315</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="49" spans="2:6" x14ac:dyDescent="0.2">
@@ -3086,7 +3082,7 @@
         <v>16</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>246</v>
@@ -3103,7 +3099,7 @@
         <v>18</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>240</v>
@@ -3117,7 +3113,7 @@
         <v>318</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>240</v>
@@ -3131,7 +3127,7 @@
         <v>19</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>240</v>
@@ -3145,7 +3141,7 @@
         <v>319</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="54" spans="2:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3159,7 +3155,7 @@
         <v>21</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="55" spans="2:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -3173,12 +3169,12 @@
         <v>23</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B56" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>24</v>
@@ -3187,7 +3183,7 @@
         <v>25</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.2">
@@ -3201,7 +3197,7 @@
         <v>27</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>259</v>
@@ -3218,7 +3214,7 @@
         <v>29</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>332</v>
@@ -3235,7 +3231,7 @@
         <v>320</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>335</v>
@@ -3249,12 +3245,12 @@
         <v>31</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="61" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B61" s="1" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>32</v>
@@ -3263,7 +3259,7 @@
         <v>33</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>240</v>
@@ -3277,7 +3273,7 @@
         <v>34</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="63" spans="2:6" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -3291,7 +3287,7 @@
         <v>36</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.2">
@@ -3302,7 +3298,7 @@
         <v>37</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>261</v>
@@ -3319,7 +3315,7 @@
         <v>39</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.2">
@@ -3333,7 +3329,7 @@
         <v>41</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>240</v>
@@ -3347,7 +3343,7 @@
         <v>42</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>262</v>
@@ -3361,10 +3357,10 @@
         <v>43</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>240</v>
@@ -3381,7 +3377,7 @@
         <v>45</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.2">
@@ -3395,7 +3391,7 @@
         <v>47</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.2">
@@ -3409,7 +3405,7 @@
         <v>49</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>263</v>
@@ -3426,7 +3422,7 @@
         <v>51</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>258</v>
@@ -3443,7 +3439,7 @@
         <v>53</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>246</v>
@@ -3457,10 +3453,10 @@
         <v>54</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>266</v>
@@ -3468,16 +3464,16 @@
     </row>
     <row r="75" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B75" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>240</v>
@@ -3485,7 +3481,7 @@
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B76" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>56</v>
@@ -3494,10 +3490,10 @@
         <v>322</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="77" spans="2:6" x14ac:dyDescent="0.2">
@@ -3511,7 +3507,7 @@
         <v>323</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>256</v>
@@ -3519,19 +3515,19 @@
     </row>
     <row r="78" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B78" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="F78" s="1" t="s">
         <v>379</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>378</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="E78" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="F78" s="1" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="79" spans="2:6" x14ac:dyDescent="0.2">
@@ -3539,13 +3535,13 @@
         <v>10076</v>
       </c>
       <c r="C79" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="D79" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="D79" s="1" t="s">
-        <v>383</v>
-      </c>
       <c r="E79" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.2">
@@ -3559,7 +3555,7 @@
         <v>324</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="81" spans="2:6" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -3573,7 +3569,7 @@
         <v>269</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="F81" s="3" t="s">
         <v>270</v>
@@ -3581,16 +3577,16 @@
     </row>
     <row r="82" spans="2:6" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B82" s="3" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C82" s="3" t="s">
         <v>60</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="83" spans="2:6" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -3601,13 +3597,13 @@
         <v>61</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="84" spans="2:6" s="4" customFormat="1" x14ac:dyDescent="0.2">
@@ -3618,7 +3614,7 @@
         <v>62</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="85" spans="2:6" s="4" customFormat="1" x14ac:dyDescent="0.2">
@@ -3629,7 +3625,7 @@
         <v>63</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="86" spans="2:6" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -3643,7 +3639,7 @@
         <v>65</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="F86" s="3" t="s">
         <v>267</v>
@@ -3660,7 +3656,7 @@
         <v>67</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>264</v>
@@ -3677,7 +3673,7 @@
         <v>69</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>271</v>
@@ -3694,7 +3690,7 @@
         <v>71</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>237</v>
@@ -3711,24 +3707,24 @@
         <v>339</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>341</v>
+        <v>244</v>
       </c>
     </row>
     <row r="91" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B91" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="C91" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="C91" s="1" t="s">
+      <c r="D91" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="D91" s="1" t="s">
-        <v>348</v>
-      </c>
       <c r="E91" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>240</v>
@@ -3736,16 +3732,16 @@
     </row>
     <row r="92" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B92" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D92" s="1" t="s">
         <v>72</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="93" spans="2:6" x14ac:dyDescent="0.2">
@@ -3759,21 +3755,21 @@
         <v>74</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="94" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B94" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>75</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="95" spans="2:6" x14ac:dyDescent="0.2">
@@ -3787,7 +3783,7 @@
         <v>77</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>247</v>
@@ -3795,7 +3791,7 @@
     </row>
     <row r="96" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B96" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>78</v>
@@ -3804,10 +3800,10 @@
         <v>79</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="97" spans="2:6" x14ac:dyDescent="0.2">
@@ -3821,24 +3817,24 @@
         <v>81</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="98" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B98" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>270</v>
@@ -3852,7 +3848,7 @@
         <v>83</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>275</v>
@@ -3866,7 +3862,7 @@
         <v>84</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>240</v>
@@ -3883,7 +3879,7 @@
         <v>86</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="102" spans="2:6" x14ac:dyDescent="0.2">
@@ -3897,7 +3893,7 @@
         <v>88</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>264</v>
@@ -3911,7 +3907,7 @@
         <v>278</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>240</v>
@@ -3928,7 +3924,7 @@
         <v>279</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>280</v>
@@ -3936,13 +3932,13 @@
     </row>
     <row r="105" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B105" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="D105" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="D105" s="1" t="s">
-        <v>352</v>
-      </c>
       <c r="E105" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>246</v>
@@ -3959,7 +3955,7 @@
         <v>91</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>240</v>
@@ -3973,7 +3969,7 @@
         <v>92</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>240</v>
@@ -3990,32 +3986,32 @@
         <v>326</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="109" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B109" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="F109" s="1" t="s">
         <v>371</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="E109" s="1" t="s">
-        <v>491</v>
-      </c>
-      <c r="F109" s="1" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="110" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B110" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D110" s="1" t="s">
         <v>94</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>240</v>
@@ -4029,7 +4025,7 @@
         <v>95</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>243</v>
@@ -4046,7 +4042,7 @@
         <v>97</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>240</v>
@@ -4057,15 +4053,15 @@
         <v>10110</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="114" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B114" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>98</v>
@@ -4074,15 +4070,15 @@
         <v>99</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="115" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B115" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>100</v>
@@ -4091,7 +4087,7 @@
         <v>101</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>240</v>
@@ -4105,10 +4101,10 @@
         <v>102</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>284</v>
@@ -4116,7 +4112,7 @@
     </row>
     <row r="117" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B117" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>103</v>
@@ -4125,7 +4121,7 @@
         <v>104</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>240</v>
@@ -4142,12 +4138,12 @@
         <v>106</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="119" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B119" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>107</v>
@@ -4156,7 +4152,7 @@
         <v>108</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="120" spans="2:6" x14ac:dyDescent="0.2">
@@ -4167,10 +4163,10 @@
         <v>109</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="121" spans="2:6" x14ac:dyDescent="0.2">
@@ -4184,7 +4180,7 @@
         <v>111</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>258</v>
@@ -4192,7 +4188,7 @@
     </row>
     <row r="122" spans="2:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B122" s="2" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>112</v>
@@ -4201,7 +4197,7 @@
         <v>113</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="123" spans="2:6" x14ac:dyDescent="0.2">
@@ -4212,7 +4208,7 @@
         <v>114</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>285</v>
@@ -4226,7 +4222,7 @@
         <v>115</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>287</v>
@@ -4240,7 +4236,7 @@
         <v>116</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>288</v>
@@ -4254,7 +4250,7 @@
         <v>117</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="127" spans="2:6" x14ac:dyDescent="0.2">
@@ -4265,7 +4261,7 @@
         <v>290</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="128" spans="2:6" x14ac:dyDescent="0.2">
@@ -4276,7 +4272,7 @@
         <v>118</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="129" spans="2:6" x14ac:dyDescent="0.2">
@@ -4290,7 +4286,7 @@
         <v>120</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>247</v>
@@ -4307,7 +4303,7 @@
         <v>122</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>292</v>
@@ -4321,13 +4317,13 @@
         <v>123</v>
       </c>
       <c r="D131" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="E131" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="F131" s="1" t="s">
         <v>367</v>
-      </c>
-      <c r="E131" s="1" t="s">
-        <v>511</v>
-      </c>
-      <c r="F131" s="1" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="132" spans="2:6" x14ac:dyDescent="0.2">
@@ -4341,10 +4337,10 @@
         <v>125</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="133" spans="2:6" x14ac:dyDescent="0.2">
@@ -4358,7 +4354,7 @@
         <v>126</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>295</v>
@@ -4375,7 +4371,7 @@
         <v>128</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>237</v>
@@ -4392,7 +4388,7 @@
         <v>130</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>237</v>
@@ -4409,7 +4405,7 @@
         <v>132</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>297</v>
@@ -4426,7 +4422,7 @@
         <v>134</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>299</v>
@@ -4440,10 +4436,10 @@
         <v>135</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>301</v>
@@ -4451,7 +4447,7 @@
     </row>
     <row r="139" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B139" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>136</v>
@@ -4460,7 +4456,7 @@
         <v>137</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="140" spans="2:6" x14ac:dyDescent="0.2">
@@ -4474,7 +4470,7 @@
         <v>139</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>240</v>
@@ -4491,7 +4487,7 @@
         <v>140</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>302</v>
@@ -4505,7 +4501,7 @@
         <v>141</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="143" spans="2:6" x14ac:dyDescent="0.2">
@@ -4519,7 +4515,7 @@
         <v>143</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>303</v>
@@ -4533,7 +4529,7 @@
         <v>305</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>240</v>
@@ -4541,30 +4537,30 @@
     </row>
     <row r="145" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B145" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="D145" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="D145" s="1" t="s">
+      <c r="E145" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="F145" s="1" t="s">
         <v>360</v>
-      </c>
-      <c r="E145" s="1" t="s">
-        <v>523</v>
-      </c>
-      <c r="F145" s="1" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="146" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B146" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="147" spans="2:6" x14ac:dyDescent="0.2">
@@ -4575,7 +4571,7 @@
         <v>144</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="148" spans="2:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -4586,7 +4582,7 @@
         <v>306</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="149" spans="2:6" x14ac:dyDescent="0.2">
@@ -4600,12 +4596,12 @@
         <v>146</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="150" spans="2:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B150" s="2" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>147</v>
@@ -4614,10 +4610,10 @@
         <v>148</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="151" spans="2:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -4628,18 +4624,18 @@
         <v>149</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="152" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B152" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>240</v>
@@ -4647,13 +4643,13 @@
     </row>
     <row r="153" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B153" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D153" s="1" t="s">
         <v>150</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>263</v>
@@ -4670,7 +4666,7 @@
         <v>152</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>308</v>
@@ -4687,7 +4683,7 @@
         <v>154</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>240</v>
@@ -4704,7 +4700,7 @@
         <v>156</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>309</v>
@@ -4721,7 +4717,7 @@
         <v>158</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="158" spans="2:6" x14ac:dyDescent="0.2">
